--- a/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
+++ b/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\llm-goal-scope\data\qa_dataset\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27400293-DC08-492D-97CC-9A6F3C701853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD800F8-F15E-4E6C-99E3-0B5C24299C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="279">
   <si>
     <t>Sentence</t>
   </si>
@@ -57,27 +57,15 @@
     <t>Dataset Type</t>
   </si>
   <si>
-    <t>RAG</t>
-  </si>
-  <si>
     <t>ML model predicted True_otherChemical but the humans predicted No True_otherChemical.</t>
   </si>
   <si>
-    <t>systemBoundaryQA</t>
-  </si>
-  <si>
     <t>original</t>
   </si>
   <si>
-    <t>no rag</t>
-  </si>
-  <si>
     <t>ML model predicted kg liveweight/head but the humans predicted No kg liveweight/head.</t>
   </si>
   <si>
-    <t>functionalUnitQA</t>
-  </si>
-  <si>
     <t>ML model predicted No kg cold carcass weight/head but the humans predicted kg cold carcass weight/head.</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>ML model predicted none required but the humans predicted No none required.</t>
   </si>
   <si>
-    <t>allocationQA</t>
-  </si>
-  <si>
     <t>ML model predicted economic but the humans predicted No economic.</t>
   </si>
   <si>
@@ -168,9 +153,6 @@
     <t>ML model predicted No Dairy cattle, calf but the humans predicted Dairy cattle, calf.</t>
   </si>
   <si>
-    <t>productQA</t>
-  </si>
-  <si>
     <t>ML model predicted Dairy cattle, cow but the humans predicted No Dairy cattle, cow.</t>
   </si>
   <si>
@@ -210,12 +192,6 @@
     <t>ML model predicted No True_excreta but the humans predicted True_excreta.</t>
   </si>
   <si>
-    <t>recalculated</t>
-  </si>
-  <si>
-    <t>rag</t>
-  </si>
-  <si>
     <t>ML model predicted True_transport but the humans predicted No True_transport.</t>
   </si>
   <si>
@@ -880,6 +856,27 @@
   </si>
   <si>
     <t>Unclear why % is applied to hides</t>
+  </si>
+  <si>
+    <t>standardized</t>
+  </si>
+  <si>
+    <t>Without RAG</t>
+  </si>
+  <si>
+    <t>System Boundary</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Allocation</t>
+  </si>
+  <si>
+    <t>Functional Unit</t>
+  </si>
+  <si>
+    <t>With RAG</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1213,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1234,24 +1231,24 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1260,13 +1257,13 @@
         <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H2">
         <v>1.1000000000000001</v>
@@ -1278,10 +1275,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1290,13 +1287,13 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H3">
         <v>1.1000000000000001</v>
@@ -1308,10 +1305,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1320,13 +1317,13 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H4">
         <v>1.1000000000000001</v>
@@ -1338,10 +1335,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1350,13 +1347,13 @@
         <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H5">
         <v>1.1000000000000001</v>
@@ -1368,10 +1365,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1380,13 +1377,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H6">
         <v>1.1000000000000001</v>
@@ -1398,10 +1395,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1410,13 +1407,13 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H7">
         <v>1.1000000000000001</v>
@@ -1428,10 +1425,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1440,13 +1437,13 @@
         <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H8">
         <v>1.1000000000000001</v>
@@ -1458,10 +1455,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1470,13 +1467,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H9">
         <v>1.1000000000000001</v>
@@ -1488,10 +1485,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1500,13 +1497,13 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H10">
         <v>1.1000000000000001</v>
@@ -1518,10 +1515,10 @@
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1530,13 +1527,13 @@
         <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H11">
         <v>1.1000000000000001</v>
@@ -1548,10 +1545,10 @@
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1560,13 +1557,13 @@
         <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H12">
         <v>1.1000000000000001</v>
@@ -1578,10 +1575,10 @@
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1590,13 +1587,13 @@
         <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H13">
         <v>1.1000000000000001</v>
@@ -1608,10 +1605,10 @@
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1620,13 +1617,13 @@
         <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H14">
         <v>1.1000000000000001</v>
@@ -1638,10 +1635,10 @@
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1650,13 +1647,13 @@
         <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H15">
         <v>1.1000000000000001</v>
@@ -1668,10 +1665,10 @@
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1680,13 +1677,13 @@
         <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H16">
         <v>1.1000000000000001</v>
@@ -1698,10 +1695,10 @@
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1710,13 +1707,13 @@
         <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H17">
         <v>1.1000000000000001</v>
@@ -1728,10 +1725,10 @@
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1740,13 +1737,13 @@
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H18">
         <v>1.1000000000000001</v>
@@ -1758,10 +1755,10 @@
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1770,13 +1767,13 @@
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H19">
         <v>1.1000000000000001</v>
@@ -1788,10 +1785,10 @@
     </row>
     <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <v>0.240963855421686</v>
@@ -1800,13 +1797,13 @@
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H20">
         <v>1.2</v>
@@ -1818,10 +1815,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>0.48192771084337299</v>
@@ -1830,13 +1827,13 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H21">
         <v>1.2</v>
@@ -1848,10 +1845,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>0.48192771084337299</v>
@@ -1860,13 +1857,13 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H22">
         <v>1.2</v>
@@ -1878,10 +1875,10 @@
     </row>
     <row r="23" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>0.48192771084337299</v>
@@ -1890,13 +1887,13 @@
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H23">
         <v>1.2</v>
@@ -1908,10 +1905,10 @@
     </row>
     <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>0.48192771084337299</v>
@@ -1920,13 +1917,13 @@
         <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H24">
         <v>1.2</v>
@@ -1938,10 +1935,10 @@
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>0.48192771084337299</v>
@@ -1950,13 +1947,13 @@
         <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H25">
         <v>1.2</v>
@@ -1968,10 +1965,10 @@
     </row>
     <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C26">
         <v>1.44578313253012</v>
@@ -1980,13 +1977,13 @@
         <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H26">
         <v>1.2</v>
@@ -1998,10 +1995,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>1.6867469879518</v>
@@ -2010,13 +2007,13 @@
         <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H27">
         <v>1.2</v>
@@ -2028,10 +2025,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>1.6867469879518</v>
@@ -2040,13 +2037,13 @@
         <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H28">
         <v>1.2</v>
@@ -2058,10 +2055,10 @@
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>1.6867469879518</v>
@@ -2070,13 +2067,13 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H29">
         <v>1.2</v>
@@ -2088,10 +2085,10 @@
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>54.4578313253012</v>
@@ -2100,13 +2097,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H30">
         <v>8.1</v>
@@ -2116,15 +2113,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J30" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>2.6506024096385499</v>
@@ -2133,13 +2130,13 @@
         <v>79</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H31">
         <v>1.2</v>
@@ -2151,10 +2148,10 @@
     </row>
     <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C32">
         <v>2.6506024096385499</v>
@@ -2163,13 +2160,13 @@
         <v>79</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H32">
         <v>1.2</v>
@@ -2181,10 +2178,10 @@
     </row>
     <row r="33" spans="1:10" ht="195" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C33">
         <v>3.13253012048192</v>
@@ -2193,13 +2190,13 @@
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G33" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H33">
         <v>1.2</v>
@@ -2211,10 +2208,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>3.13253012048192</v>
@@ -2223,13 +2220,13 @@
         <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G34" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H34">
         <v>1.2</v>
@@ -2241,10 +2238,10 @@
     </row>
     <row r="35" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>3.13253012048192</v>
@@ -2253,13 +2250,13 @@
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H35">
         <v>1.2</v>
@@ -2271,10 +2268,10 @@
     </row>
     <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C36">
         <v>3.13253012048192</v>
@@ -2283,13 +2280,13 @@
         <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H36">
         <v>1.2</v>
@@ -2301,10 +2298,10 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C37">
         <v>3.13253012048192</v>
@@ -2313,13 +2310,13 @@
         <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G37" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H37">
         <v>1.2</v>
@@ -2331,10 +2328,10 @@
     </row>
     <row r="38" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>3.13253012048192</v>
@@ -2343,13 +2340,13 @@
         <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H38">
         <v>1.2</v>
@@ -2361,10 +2358,10 @@
     </row>
     <row r="39" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C39">
         <v>3.13253012048192</v>
@@ -2373,13 +2370,13 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H39">
         <v>1.2</v>
@@ -2391,10 +2388,10 @@
     </row>
     <row r="40" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>54.4578313253012</v>
@@ -2403,13 +2400,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H40">
         <v>8.1</v>
@@ -2419,15 +2416,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J40" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>16.867469879518001</v>
@@ -2436,13 +2433,13 @@
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H41">
         <v>8.1999999999999993</v>
@@ -2452,15 +2449,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J41" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>16.867469879518001</v>
@@ -2469,13 +2466,13 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G42" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H42">
         <v>8.1999999999999993</v>
@@ -2485,15 +2482,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J42" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C43">
         <v>95.301204819277103</v>
@@ -2502,13 +2499,13 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H43">
         <v>1.4</v>
@@ -2520,10 +2517,10 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C44">
         <v>4.96815286624203</v>
@@ -2532,13 +2529,13 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G44" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H44">
         <v>1.2</v>
@@ -2550,10 +2547,10 @@
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>4.96815286624203</v>
@@ -2562,13 +2559,13 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G45" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H45">
         <v>1.2</v>
@@ -2580,10 +2577,10 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C46">
         <v>4.96815286624203</v>
@@ -2592,13 +2589,13 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G46" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H46">
         <v>1.2</v>
@@ -2610,10 +2607,10 @@
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>4.96815286624203</v>
@@ -2622,13 +2619,13 @@
         <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G47" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H47">
         <v>1.2</v>
@@ -2640,10 +2637,10 @@
     </row>
     <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C48">
         <v>5.4216867469879499</v>
@@ -2652,13 +2649,13 @@
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G48" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H48">
         <v>1.3</v>
@@ -2670,10 +2667,10 @@
     </row>
     <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C49">
         <v>5.4216867469879499</v>
@@ -2682,13 +2679,13 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H49">
         <v>1.3</v>
@@ -2700,10 +2697,10 @@
     </row>
     <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C50">
         <v>5.4216867469879499</v>
@@ -2712,13 +2709,13 @@
         <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H50">
         <v>1.3</v>
@@ -2730,10 +2727,10 @@
     </row>
     <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <v>5.4216867469879499</v>
@@ -2742,13 +2739,13 @@
         <v>79</v>
       </c>
       <c r="E51" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H51">
         <v>1.3</v>
@@ -2760,10 +2757,10 @@
     </row>
     <row r="52" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C52">
         <v>5.4216867469879499</v>
@@ -2772,13 +2769,13 @@
         <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H52">
         <v>1.3</v>
@@ -2790,10 +2787,10 @@
     </row>
     <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C53">
         <v>5.4216867469879499</v>
@@ -2802,13 +2799,13 @@
         <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H53">
         <v>1.3</v>
@@ -2820,10 +2817,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C54">
         <v>6.6242038216560504</v>
@@ -2832,13 +2829,13 @@
         <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G54" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H54">
         <v>1.3</v>
@@ -2850,10 +2847,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C55">
         <v>6.6242038216560504</v>
@@ -2862,13 +2859,13 @@
         <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G55" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H55">
         <v>1.3</v>
@@ -2880,10 +2877,10 @@
     </row>
     <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C56">
         <v>8.0254777070063703</v>
@@ -2892,13 +2889,13 @@
         <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G56" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H56">
         <v>1.3</v>
@@ -2910,10 +2907,10 @@
     </row>
     <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C57">
         <v>8.19277108433735</v>
@@ -2922,13 +2919,13 @@
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H57">
         <v>1.3</v>
@@ -2940,10 +2937,10 @@
     </row>
     <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C58">
         <v>8.19277108433735</v>
@@ -2952,13 +2949,13 @@
         <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H58">
         <v>1.3</v>
@@ -2970,10 +2967,10 @@
     </row>
     <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C59">
         <v>8.19277108433735</v>
@@ -2982,13 +2979,13 @@
         <v>93</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G59" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H59">
         <v>1.3</v>
@@ -3000,10 +2997,10 @@
     </row>
     <row r="60" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>8.19277108433735</v>
@@ -3012,13 +3009,13 @@
         <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G60" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H60">
         <v>1.3</v>
@@ -3030,10 +3027,10 @@
     </row>
     <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C61">
         <v>8.19277108433735</v>
@@ -3042,13 +3039,13 @@
         <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G61" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H61">
         <v>1.3</v>
@@ -3060,10 +3057,10 @@
     </row>
     <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C62">
         <v>8.19277108433735</v>
@@ -3072,13 +3069,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G62" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H62">
         <v>1.3</v>
@@ -3090,10 +3087,10 @@
     </row>
     <row r="63" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C63">
         <v>8.6746987951807206</v>
@@ -3102,13 +3099,13 @@
         <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G63" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H63">
         <v>1.3</v>
@@ -3120,10 +3117,10 @@
     </row>
     <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C64">
         <v>8.6746987951807206</v>
@@ -3132,13 +3129,13 @@
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G64" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H64">
         <v>1.3</v>
@@ -3150,10 +3147,10 @@
     </row>
     <row r="65" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C65">
         <v>8.6746987951807206</v>
@@ -3162,13 +3159,13 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H65">
         <v>1.3</v>
@@ -3180,10 +3177,10 @@
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C66">
         <v>8.6746987951807206</v>
@@ -3192,13 +3189,13 @@
         <v>84</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H66">
         <v>1.3</v>
@@ -3210,10 +3207,10 @@
     </row>
     <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C67">
         <v>8.9171974522292992</v>
@@ -3222,13 +3219,13 @@
         <v>53</v>
       </c>
       <c r="E67" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F67" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G67" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H67">
         <v>1.3</v>
@@ -3240,10 +3237,10 @@
     </row>
     <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C68">
         <v>8.9171974522292992</v>
@@ -3252,13 +3249,13 @@
         <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G68" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H68">
         <v>1.3</v>
@@ -3270,10 +3267,10 @@
     </row>
     <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C69">
         <v>8.9171974522292992</v>
@@ -3282,13 +3279,13 @@
         <v>70</v>
       </c>
       <c r="E69" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G69" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H69">
         <v>1.3</v>
@@ -3300,10 +3297,10 @@
     </row>
     <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C70">
         <v>8.9171974522292992</v>
@@ -3312,13 +3309,13 @@
         <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F70" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G70" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H70">
         <v>1.3</v>
@@ -3330,10 +3327,10 @@
     </row>
     <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C71">
         <v>8.9171974522292992</v>
@@ -3342,13 +3339,14 @@
         <v>58</v>
       </c>
       <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>56</v>
+        <v>274</v>
+      </c>
+      <c r="F71" t="str">
+        <f>$F$7</f>
+        <v>standardized</v>
       </c>
       <c r="G71" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H71">
         <v>1.3</v>
@@ -3360,10 +3358,10 @@
     </row>
     <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C72">
         <v>8.9171974522292992</v>
@@ -3372,13 +3370,13 @@
         <v>59</v>
       </c>
       <c r="E72" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F72" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G72" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H72">
         <v>1.3</v>
@@ -3390,10 +3388,10 @@
     </row>
     <row r="73" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C73">
         <v>54.4578313253012</v>
@@ -3402,13 +3400,13 @@
         <v>25</v>
       </c>
       <c r="E73" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G73" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H73">
         <v>8.1</v>
@@ -3420,10 +3418,10 @@
     </row>
     <row r="74" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -3432,13 +3430,13 @@
         <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G74" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H74">
         <v>4</v>
@@ -3450,10 +3448,10 @@
     </row>
     <row r="75" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C75">
         <v>95.301204819277103</v>
@@ -3462,13 +3460,13 @@
         <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F75" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G75" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H75">
         <v>1.4</v>
@@ -3480,10 +3478,10 @@
     </row>
     <row r="76" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C76">
         <v>54.4578313253012</v>
@@ -3492,13 +3490,13 @@
         <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G76" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H76">
         <v>8.1</v>
@@ -3508,15 +3506,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J76" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C77">
         <v>16.867469879518001</v>
@@ -3525,13 +3523,13 @@
         <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G77" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H77">
         <v>8.1999999999999993</v>
@@ -3541,15 +3539,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J77" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C78">
         <v>54.4578313253012</v>
@@ -3558,13 +3556,13 @@
         <v>41</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G78" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H78">
         <v>8.1</v>
@@ -3576,10 +3574,10 @@
     </row>
     <row r="79" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C79">
         <v>4.6987951807228896</v>
@@ -3588,13 +3586,13 @@
         <v>54</v>
       </c>
       <c r="E79" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G79" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H79">
         <v>1.2</v>
@@ -3606,10 +3604,10 @@
     </row>
     <row r="80" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C80">
         <v>54.4578313253012</v>
@@ -3618,13 +3616,13 @@
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H80">
         <v>8.1</v>
@@ -3636,10 +3634,10 @@
     </row>
     <row r="81" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C81">
         <v>16.867469879518001</v>
@@ -3648,13 +3646,13 @@
         <v>33</v>
       </c>
       <c r="E81" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G81" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H81">
         <v>8.1999999999999993</v>
@@ -3666,10 +3664,10 @@
     </row>
     <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -3678,13 +3676,13 @@
         <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G82" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H82">
         <v>4</v>
@@ -3696,10 +3694,10 @@
     </row>
     <row r="83" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C83">
         <v>18.2165605095541</v>
@@ -3708,13 +3706,13 @@
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G83" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H83">
         <v>8.1999999999999993</v>
@@ -3726,10 +3724,10 @@
     </row>
     <row r="84" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C84">
         <v>18.2165605095541</v>
@@ -3738,13 +3736,13 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F84" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G84" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H84">
         <v>8.1</v>
@@ -3756,10 +3754,10 @@
     </row>
     <row r="85" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C85">
         <v>56.8152866242038</v>
@@ -3768,13 +3766,13 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G85" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H85">
         <v>8.1</v>
@@ -3786,10 +3784,10 @@
     </row>
     <row r="86" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C86">
         <v>18.2165605095541</v>
@@ -3798,13 +3796,13 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G86" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H86">
         <v>8.1999999999999993</v>
@@ -3816,10 +3814,10 @@
     </row>
     <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C87">
         <v>56.8152866242038</v>
@@ -3828,13 +3826,13 @@
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F87" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G87" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H87">
         <v>8.1</v>
@@ -3844,15 +3842,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J87" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C88">
         <v>18.2165605095541</v>
@@ -3861,13 +3859,13 @@
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G88" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H88">
         <v>8.1</v>
@@ -3879,10 +3877,10 @@
     </row>
     <row r="89" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C89">
         <v>56.8152866242038</v>
@@ -3891,13 +3889,13 @@
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G89" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H89">
         <v>8.1</v>
@@ -3909,10 +3907,10 @@
     </row>
     <row r="90" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C90">
         <v>56.8152866242038</v>
@@ -3921,13 +3919,13 @@
         <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G90" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H90">
         <v>8.1</v>
@@ -3939,10 +3937,10 @@
     </row>
     <row r="91" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C91">
         <v>54.4578313253012</v>
@@ -3951,13 +3949,13 @@
         <v>41</v>
       </c>
       <c r="E91" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G91" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H91">
         <v>8.1</v>
@@ -3969,10 +3967,10 @@
     </row>
     <row r="92" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C92">
         <v>11.084337349397501</v>
@@ -3981,13 +3979,13 @@
         <v>54</v>
       </c>
       <c r="E92" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F92" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G92" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -3997,15 +3995,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J92" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C93">
         <v>95.301204819277103</v>
@@ -4014,13 +4012,13 @@
         <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H93">
         <v>1.4</v>
@@ -4032,10 +4030,10 @@
     </row>
     <row r="94" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C94">
         <v>16.867469879518001</v>
@@ -4044,13 +4042,13 @@
         <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G94" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H94">
         <v>8.1999999999999993</v>
@@ -4060,15 +4058,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J94" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C95">
         <v>16.867469879518001</v>
@@ -4077,13 +4075,13 @@
         <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G95" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H95">
         <v>8.1</v>
@@ -4095,10 +4093,10 @@
     </row>
     <row r="96" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C96">
         <v>54.4578313253012</v>
@@ -4107,13 +4105,13 @@
         <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G96" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H96">
         <v>8.1</v>
@@ -4125,10 +4123,10 @@
     </row>
     <row r="97" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C97">
         <v>4.6987951807228896</v>
@@ -4137,13 +4135,13 @@
         <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G97" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H97">
         <v>1.2</v>
@@ -4155,10 +4153,10 @@
     </row>
     <row r="98" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C98">
         <v>11.084337349397501</v>
@@ -4167,13 +4165,13 @@
         <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G98" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H98">
         <v>5</v>
@@ -4183,15 +4181,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J98" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C99">
         <v>95.301204819277103</v>
@@ -4200,13 +4198,13 @@
         <v>54</v>
       </c>
       <c r="E99" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G99" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H99">
         <v>1.4</v>
@@ -4218,10 +4216,10 @@
     </row>
     <row r="100" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C100">
         <v>54.4578313253012</v>
@@ -4230,13 +4228,13 @@
         <v>58</v>
       </c>
       <c r="E100" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G100" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H100">
         <v>8.1</v>
@@ -4248,10 +4246,10 @@
     </row>
     <row r="101" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C101">
         <v>13.6144578313253</v>
@@ -4260,13 +4258,13 @@
         <v>79</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G101" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H101">
         <v>4</v>
@@ -4278,10 +4276,10 @@
     </row>
     <row r="102" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C102">
         <v>13.6144578313253</v>
@@ -4290,13 +4288,13 @@
         <v>79</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G102" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H102">
         <v>4</v>
@@ -4308,10 +4306,10 @@
     </row>
     <row r="103" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C103">
         <v>13.975903614457801</v>
@@ -4320,13 +4318,13 @@
         <v>41</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G103" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H103">
         <v>7</v>
@@ -4336,15 +4334,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J103" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C104">
         <v>13.975903614457801</v>
@@ -4353,13 +4351,13 @@
         <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G104" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H104">
         <v>2.1</v>
@@ -4369,15 +4367,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J104" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C105">
         <v>13.975903614457801</v>
@@ -4386,13 +4384,13 @@
         <v>48</v>
       </c>
       <c r="E105" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G105" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H105">
         <v>2.1</v>
@@ -4402,15 +4400,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J105" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C106">
         <v>13.975903614457801</v>
@@ -4419,13 +4417,13 @@
         <v>48</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H106">
         <v>7</v>
@@ -4435,15 +4433,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J106" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C107">
         <v>13.975903614457801</v>
@@ -4452,13 +4450,13 @@
         <v>60</v>
       </c>
       <c r="E107" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G107" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H107">
         <v>2.2000000000000002</v>
@@ -4468,15 +4466,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J107" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C108">
         <v>13.975903614457801</v>
@@ -4485,13 +4483,13 @@
         <v>84</v>
       </c>
       <c r="E108" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G108" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H108">
         <v>2.1</v>
@@ -4501,15 +4499,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J108" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C109">
         <v>13.975903614457801</v>
@@ -4518,13 +4516,13 @@
         <v>95</v>
       </c>
       <c r="E109" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G109" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H109">
         <v>2.2000000000000002</v>
@@ -4534,15 +4532,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J109" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C110">
         <v>13.975903614457801</v>
@@ -4551,13 +4549,13 @@
         <v>100</v>
       </c>
       <c r="E110" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G110" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H110">
         <v>2.2000000000000002</v>
@@ -4567,15 +4565,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J110" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C111">
         <v>13.975903614457801</v>
@@ -4584,13 +4582,13 @@
         <v>84</v>
       </c>
       <c r="E111" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G111" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H111">
         <v>2.1</v>
@@ -4602,10 +4600,10 @@
     </row>
     <row r="112" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C112">
         <v>13.975903614457801</v>
@@ -4614,13 +4612,13 @@
         <v>95</v>
       </c>
       <c r="E112" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G112" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H112">
         <v>2.2000000000000002</v>
@@ -4632,10 +4630,10 @@
     </row>
     <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C113">
         <v>10</v>
@@ -4644,13 +4642,13 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F113" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G113" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -4660,15 +4658,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J113" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C114">
         <v>11.084337349397501</v>
@@ -4677,13 +4675,13 @@
         <v>63</v>
       </c>
       <c r="E114" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G114" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H114">
         <v>4</v>
@@ -4693,15 +4691,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J114" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C115">
         <v>16.867469879518001</v>
@@ -4710,13 +4708,13 @@
         <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F115" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G115" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H115">
         <v>8.1999999999999993</v>
@@ -4728,10 +4726,10 @@
     </row>
     <row r="116" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C116">
         <v>10</v>
@@ -4740,13 +4738,13 @@
         <v>60</v>
       </c>
       <c r="E116" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G116" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -4756,15 +4754,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J116" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C117">
         <v>11.084337349397501</v>
@@ -4773,13 +4771,13 @@
         <v>63</v>
       </c>
       <c r="E117" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F117" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G117" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H117">
         <v>4</v>
@@ -4789,15 +4787,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J117" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C118">
         <v>16.867469879518001</v>
@@ -4806,13 +4804,13 @@
         <v>66</v>
       </c>
       <c r="E118" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G118" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H118">
         <v>8.1999999999999993</v>
@@ -4824,10 +4822,10 @@
     </row>
     <row r="119" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -4836,13 +4834,13 @@
         <v>68</v>
       </c>
       <c r="E119" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G119" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H119">
         <v>4</v>
@@ -4854,10 +4852,10 @@
     </row>
     <row r="120" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C120">
         <v>11.084337349397501</v>
@@ -4866,13 +4864,13 @@
         <v>68</v>
       </c>
       <c r="E120" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F120" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G120" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H120">
         <v>4</v>
@@ -4884,10 +4882,10 @@
     </row>
     <row r="121" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C121">
         <v>11.084337349397501</v>
@@ -4896,13 +4894,13 @@
         <v>73</v>
       </c>
       <c r="E121" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F121" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G121" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H121">
         <v>5</v>
@@ -4912,15 +4910,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J121" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -4929,13 +4927,13 @@
         <v>68</v>
       </c>
       <c r="E122" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G122" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H122">
         <v>5</v>
@@ -4945,15 +4943,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J122" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C123">
         <v>56.8152866242038</v>
@@ -4962,13 +4960,13 @@
         <v>31</v>
       </c>
       <c r="E123" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F123" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G123" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H123">
         <v>8.1</v>
@@ -4980,10 +4978,10 @@
     </row>
     <row r="124" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C124">
         <v>18.2165605095541</v>
@@ -4992,13 +4990,13 @@
         <v>35</v>
       </c>
       <c r="E124" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F124" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G124" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H124">
         <v>8.1999999999999993</v>
@@ -5010,10 +5008,10 @@
     </row>
     <row r="125" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C125">
         <v>56.8152866242038</v>
@@ -5022,13 +5020,13 @@
         <v>36</v>
       </c>
       <c r="E125" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F125" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G125" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H125">
         <v>8.1</v>
@@ -5040,10 +5038,10 @@
     </row>
     <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C126">
         <v>10.191082802547699</v>
@@ -5052,13 +5050,13 @@
         <v>38</v>
       </c>
       <c r="E126" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F126" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G126" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H126">
         <v>5</v>
@@ -5068,15 +5066,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J126" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C127">
         <v>56.8152866242038</v>
@@ -5085,13 +5083,13 @@
         <v>38</v>
       </c>
       <c r="E127" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F127" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G127" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H127">
         <v>5</v>
@@ -5101,15 +5099,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J127" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C128">
         <v>18.2165605095541</v>
@@ -5118,13 +5116,13 @@
         <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F128" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G128" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H128">
         <v>8.1999999999999993</v>
@@ -5136,10 +5134,10 @@
     </row>
     <row r="129" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C129">
         <v>18.2165605095541</v>
@@ -5148,13 +5146,13 @@
         <v>40</v>
       </c>
       <c r="E129" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F129" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G129" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H129">
         <v>8.1999999999999993</v>
@@ -5166,10 +5164,10 @@
     </row>
     <row r="130" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C130">
         <v>18.2165605095541</v>
@@ -5178,13 +5176,13 @@
         <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F130" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G130" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H130">
         <v>8.1</v>
@@ -5196,10 +5194,10 @@
     </row>
     <row r="131" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C131">
         <v>18.2165605095541</v>
@@ -5208,13 +5206,13 @@
         <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F131" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G131" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H131">
         <v>8.1999999999999993</v>
@@ -5226,10 +5224,10 @@
     </row>
     <row r="132" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C132">
         <v>56.8152866242038</v>
@@ -5238,13 +5236,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F132" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G132" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H132">
         <v>8.1</v>
@@ -5256,10 +5254,10 @@
     </row>
     <row r="133" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C133">
         <v>87.388535031847098</v>
@@ -5268,13 +5266,13 @@
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F133" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G133" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H133">
         <v>3.1</v>
@@ -5286,10 +5284,10 @@
     </row>
     <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C134">
         <v>87.388535031847098</v>
@@ -5298,13 +5296,13 @@
         <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F134" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G134" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H134">
         <v>3.1</v>
@@ -5316,10 +5314,10 @@
     </row>
     <row r="135" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C135">
         <v>24.337349397590302</v>
@@ -5328,13 +5326,13 @@
         <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G135" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H135">
         <v>3.2</v>
@@ -5346,10 +5344,10 @@
     </row>
     <row r="136" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C136">
         <v>87.388535031847098</v>
@@ -5358,13 +5356,13 @@
         <v>13</v>
       </c>
       <c r="E136" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G136" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H136">
         <v>3.1</v>
@@ -5376,10 +5374,10 @@
     </row>
     <row r="137" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C137">
         <v>87.388535031847098</v>
@@ -5388,13 +5386,13 @@
         <v>13</v>
       </c>
       <c r="E137" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G137" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H137">
         <v>3.1</v>
@@ -5406,10 +5404,10 @@
     </row>
     <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C138">
         <v>38.313253012048101</v>
@@ -5418,13 +5416,13 @@
         <v>16</v>
       </c>
       <c r="E138" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G138" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H138">
         <v>3.1</v>
@@ -5436,10 +5434,10 @@
     </row>
     <row r="139" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C139">
         <v>54.337349397590302</v>
@@ -5448,13 +5446,13 @@
         <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G139" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H139">
         <v>3.1</v>
@@ -5466,10 +5464,10 @@
     </row>
     <row r="140" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C140">
         <v>59.036144578313198</v>
@@ -5478,13 +5476,13 @@
         <v>23</v>
       </c>
       <c r="E140" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F140" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G140" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H140">
         <v>3.1</v>
@@ -5496,10 +5494,10 @@
     </row>
     <row r="141" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C141">
         <v>87.388535031847098</v>
@@ -5508,13 +5506,13 @@
         <v>38</v>
       </c>
       <c r="E141" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F141" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H141">
         <v>3.1</v>
@@ -5526,10 +5524,10 @@
     </row>
     <row r="142" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C142">
         <v>87.388535031847098</v>
@@ -5538,13 +5536,13 @@
         <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F142" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H142">
         <v>3.1</v>
@@ -5556,10 +5554,10 @@
     </row>
     <row r="143" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C143">
         <v>87.388535031847098</v>
@@ -5568,13 +5566,13 @@
         <v>40</v>
       </c>
       <c r="E143" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F143" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G143" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H143">
         <v>3.1</v>
@@ -5586,10 +5584,10 @@
     </row>
     <row r="144" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C144">
         <v>87.388535031847098</v>
@@ -5598,13 +5596,13 @@
         <v>40</v>
       </c>
       <c r="E144" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F144" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G144" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H144">
         <v>3.1</v>
@@ -5616,10 +5614,10 @@
     </row>
     <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C145">
         <v>87.388535031847098</v>
@@ -5628,13 +5626,13 @@
         <v>44</v>
       </c>
       <c r="E145" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F145" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G145" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H145">
         <v>3.1</v>
@@ -5646,10 +5644,10 @@
     </row>
     <row r="146" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C146">
         <v>87.388535031847098</v>
@@ -5658,13 +5656,13 @@
         <v>44</v>
       </c>
       <c r="E146" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F146" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H146">
         <v>3.1</v>
@@ -5676,10 +5674,10 @@
     </row>
     <row r="147" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C147">
         <v>87.388535031847098</v>
@@ -5688,13 +5686,13 @@
         <v>46</v>
       </c>
       <c r="E147" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F147" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H147">
         <v>3.1</v>
@@ -5706,10 +5704,10 @@
     </row>
     <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C148">
         <v>87.388535031847098</v>
@@ -5718,13 +5716,13 @@
         <v>46</v>
       </c>
       <c r="E148" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F148" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H148">
         <v>3.1</v>
@@ -5736,10 +5734,10 @@
     </row>
     <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C149">
         <v>21.019108280254699</v>
@@ -5748,13 +5746,13 @@
         <v>53</v>
       </c>
       <c r="E149" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F149" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H149">
         <v>3.1</v>
@@ -5766,10 +5764,10 @@
     </row>
     <row r="150" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C150">
         <v>73.375796178343904</v>
@@ -5778,13 +5776,13 @@
         <v>53</v>
       </c>
       <c r="E150" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F150" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H150">
         <v>3.2</v>
@@ -5796,10 +5794,10 @@
     </row>
     <row r="151" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C151">
         <v>53.855421686746901</v>
@@ -5808,13 +5806,13 @@
         <v>54</v>
       </c>
       <c r="E151" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F151" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G151" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H151">
         <v>3.2</v>
@@ -5826,10 +5824,10 @@
     </row>
     <row r="152" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C152">
         <v>54.337349397590302</v>
@@ -5838,13 +5836,13 @@
         <v>18</v>
       </c>
       <c r="E152" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F152" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G152" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H152">
         <v>3.1</v>
@@ -5856,10 +5854,10 @@
     </row>
     <row r="153" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C153">
         <v>53.855421686746901</v>
@@ -5868,13 +5866,13 @@
         <v>54</v>
       </c>
       <c r="E153" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F153" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G153" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H153">
         <v>3.2</v>
@@ -5886,10 +5884,10 @@
     </row>
     <row r="154" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C154">
         <v>59.036144578313198</v>
@@ -5898,13 +5896,13 @@
         <v>54</v>
       </c>
       <c r="E154" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F154" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G154" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H154">
         <v>3.1</v>
@@ -5916,10 +5914,10 @@
     </row>
     <row r="155" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C155">
         <v>59.036144578313198</v>
@@ -5928,13 +5926,13 @@
         <v>54</v>
       </c>
       <c r="E155" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F155" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G155" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H155">
         <v>3.1</v>
@@ -5946,10 +5944,10 @@
     </row>
     <row r="156" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C156">
         <v>72.409638554216798</v>
@@ -5958,13 +5956,13 @@
         <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F156" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G156" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H156">
         <v>3.2</v>
@@ -5976,10 +5974,10 @@
     </row>
     <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C157">
         <v>72.409638554216798</v>
@@ -5988,13 +5986,13 @@
         <v>60</v>
       </c>
       <c r="E157" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F157" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G157" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H157">
         <v>3.2</v>
@@ -6006,10 +6004,10 @@
     </row>
     <row r="158" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C158">
         <v>11.084337349397501</v>
@@ -6018,13 +6016,13 @@
         <v>68</v>
       </c>
       <c r="E158" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F158" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G158" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H158">
         <v>5</v>
@@ -6034,15 +6032,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J158" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C159">
         <v>2.2891566265060201</v>
@@ -6051,13 +6049,13 @@
         <v>70</v>
       </c>
       <c r="E159" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F159" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G159" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H159">
         <v>1.2</v>
@@ -6069,10 +6067,10 @@
     </row>
     <row r="160" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C160">
         <v>11.084337349397501</v>
@@ -6081,13 +6079,13 @@
         <v>73</v>
       </c>
       <c r="E160" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F160" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G160" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H160">
         <v>5</v>
@@ -6097,15 +6095,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J160" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C161">
         <v>4.6987951807228896</v>
@@ -6114,13 +6112,13 @@
         <v>79</v>
       </c>
       <c r="E161" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F161" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G161" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H161">
         <v>1.2</v>
@@ -6132,10 +6130,10 @@
     </row>
     <row r="162" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C162">
         <v>11.084337349397501</v>
@@ -6144,13 +6142,13 @@
         <v>79</v>
       </c>
       <c r="E162" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F162" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G162" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H162">
         <v>4</v>
@@ -6160,15 +6158,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J162" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C163">
         <v>10</v>
@@ -6177,13 +6175,13 @@
         <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G163" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H163">
         <v>4</v>
@@ -6195,10 +6193,10 @@
     </row>
     <row r="164" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C164">
         <v>4.6987951807228896</v>
@@ -6207,13 +6205,13 @@
         <v>79</v>
       </c>
       <c r="E164" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F164" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G164" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H164">
         <v>4</v>
@@ -6225,10 +6223,10 @@
     </row>
     <row r="165" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C165">
         <v>95.301204819277103</v>
@@ -6237,13 +6235,13 @@
         <v>79</v>
       </c>
       <c r="E165" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F165" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G165" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H165">
         <v>1.4</v>
@@ -6255,10 +6253,10 @@
     </row>
     <row r="166" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C166">
         <v>54.4578313253012</v>
@@ -6267,13 +6265,13 @@
         <v>84</v>
       </c>
       <c r="E166" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F166" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G166" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H166">
         <v>6</v>
@@ -6285,10 +6283,10 @@
     </row>
     <row r="167" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C167">
         <v>10</v>
@@ -6297,13 +6295,13 @@
         <v>85</v>
       </c>
       <c r="E167" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F167" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G167" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H167">
         <v>5</v>
@@ -6313,15 +6311,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J167" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C168">
         <v>95.301204819277103</v>
@@ -6330,13 +6328,13 @@
         <v>79</v>
       </c>
       <c r="E168" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F168" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G168" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H168">
         <v>1.4</v>
@@ -6348,10 +6346,10 @@
     </row>
     <row r="169" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C169">
         <v>56.8152866242038</v>
@@ -6360,13 +6358,13 @@
         <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F169" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G169" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H169">
         <v>8.1</v>
@@ -6378,10 +6376,10 @@
     </row>
     <row r="170" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C170">
         <v>10.191082802547699</v>
@@ -6390,13 +6388,13 @@
         <v>53</v>
       </c>
       <c r="E170" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F170" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H170">
         <v>4</v>
@@ -6406,15 +6404,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J170" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C171">
         <v>56.8152866242038</v>
@@ -6423,13 +6421,13 @@
         <v>53</v>
       </c>
       <c r="E171" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F171" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G171" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H171">
         <v>8.1</v>
@@ -6441,10 +6439,10 @@
     </row>
     <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C172">
         <v>10.9554140127388</v>
@@ -6453,13 +6451,13 @@
         <v>59</v>
       </c>
       <c r="E172" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F172" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G172" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H172">
         <v>4</v>
@@ -6469,15 +6467,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J172" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C173">
         <v>56.8152866242038</v>
@@ -6486,13 +6484,13 @@
         <v>60</v>
       </c>
       <c r="E173" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F173" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G173" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H173">
         <v>8.1</v>
@@ -6504,10 +6502,10 @@
     </row>
     <row r="174" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C174">
         <v>10.9554140127388</v>
@@ -6516,13 +6514,13 @@
         <v>61</v>
       </c>
       <c r="E174" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F174" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G174" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H174">
         <v>4</v>
@@ -6532,15 +6530,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J174" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C175">
         <v>10.191082802547699</v>
@@ -6549,13 +6547,13 @@
         <v>70</v>
       </c>
       <c r="E175" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F175" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G175" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H175">
         <v>8.1</v>
@@ -6567,10 +6565,10 @@
     </row>
     <row r="176" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C176">
         <v>56.8152866242038</v>
@@ -6579,13 +6577,13 @@
         <v>70</v>
       </c>
       <c r="E176" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F176" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G176" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H176">
         <v>8.1</v>
@@ -6597,10 +6595,10 @@
     </row>
     <row r="177" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C177">
         <v>10.191082802547699</v>
@@ -6609,13 +6607,13 @@
         <v>82</v>
       </c>
       <c r="E177" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F177" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G177" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H177">
         <v>5</v>
@@ -6625,15 +6623,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J177" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C178">
         <v>56.8152866242038</v>
@@ -6642,13 +6640,13 @@
         <v>84</v>
       </c>
       <c r="E178" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F178" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G178" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H178">
         <v>8.1</v>
@@ -6660,10 +6658,10 @@
     </row>
     <row r="179" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C179">
         <v>56.8152866242038</v>
@@ -6672,13 +6670,13 @@
         <v>87</v>
       </c>
       <c r="E179" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F179" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G179" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H179">
         <v>8.1</v>
@@ -6690,10 +6688,10 @@
     </row>
     <row r="180" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C180">
         <v>10.191082802547699</v>
@@ -6702,13 +6700,13 @@
         <v>38</v>
       </c>
       <c r="E180" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F180" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G180" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H180">
         <v>5</v>
@@ -6718,15 +6716,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J180" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C181">
         <v>56.8152866242038</v>
@@ -6735,13 +6733,13 @@
         <v>38</v>
       </c>
       <c r="E181" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F181" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G181" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H181">
         <v>4</v>
@@ -6751,15 +6749,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J181" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C182">
         <v>18.2165605095541</v>
@@ -6768,13 +6766,13 @@
         <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F182" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G182" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H182">
         <v>8.1999999999999993</v>
@@ -6786,10 +6784,10 @@
     </row>
     <row r="183" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C183">
         <v>56.8152866242038</v>
@@ -6798,13 +6796,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F183" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G183" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H183">
         <v>8.1</v>
@@ -6816,10 +6814,10 @@
     </row>
     <row r="184" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C184">
         <v>56.8152866242038</v>
@@ -6828,13 +6826,13 @@
         <v>53</v>
       </c>
       <c r="E184" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F184" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G184" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H184">
         <v>8.1</v>
@@ -6846,10 +6844,10 @@
     </row>
     <row r="185" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C185">
         <v>10.9554140127388</v>
@@ -6858,13 +6856,13 @@
         <v>59</v>
       </c>
       <c r="E185" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F185" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G185" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H185">
         <v>4</v>
@@ -6874,15 +6872,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J185" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C186">
         <v>56.8152866242038</v>
@@ -6891,13 +6889,13 @@
         <v>60</v>
       </c>
       <c r="E186" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F186" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G186" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H186">
         <v>8.1</v>
@@ -6909,10 +6907,10 @@
     </row>
     <row r="187" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C187">
         <v>56.8152866242038</v>
@@ -6921,13 +6919,13 @@
         <v>70</v>
       </c>
       <c r="E187" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F187" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G187" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H187">
         <v>4</v>
@@ -6937,15 +6935,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J187" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C188">
         <v>56.8152866242038</v>
@@ -6954,13 +6952,13 @@
         <v>84</v>
       </c>
       <c r="E188" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F188" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G188" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H188">
         <v>8.1</v>
@@ -6972,10 +6970,10 @@
     </row>
     <row r="189" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C189">
         <v>56.8152866242038</v>
@@ -6984,13 +6982,13 @@
         <v>87</v>
       </c>
       <c r="E189" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F189" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G189" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H189">
         <v>8.1</v>
@@ -7002,10 +7000,10 @@
     </row>
     <row r="190" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C190">
         <v>59.036144578313198</v>
@@ -7014,13 +7012,13 @@
         <v>22</v>
       </c>
       <c r="E190" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F190" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G190" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H190">
         <v>3.1</v>
@@ -7032,10 +7030,10 @@
     </row>
     <row r="191" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C191">
         <v>59.036144578313198</v>
@@ -7044,13 +7042,13 @@
         <v>23</v>
       </c>
       <c r="E191" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F191" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G191" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H191">
         <v>3.1</v>
@@ -7062,10 +7060,10 @@
     </row>
     <row r="192" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C192">
         <v>24.337349397590302</v>
@@ -7074,13 +7072,13 @@
         <v>68</v>
       </c>
       <c r="E192" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F192" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G192" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H192">
         <v>3.1</v>
@@ -7092,10 +7090,10 @@
     </row>
     <row r="193" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C193">
         <v>24.337349397590302</v>
@@ -7104,13 +7102,13 @@
         <v>68</v>
       </c>
       <c r="E193" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F193" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G193" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H193">
         <v>3.1</v>
@@ -7122,10 +7120,10 @@
     </row>
     <row r="194" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C194">
         <v>54.337349397590302</v>
@@ -7134,13 +7132,13 @@
         <v>68</v>
       </c>
       <c r="E194" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F194" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G194" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H194">
         <v>3.2</v>
@@ -7152,10 +7150,10 @@
     </row>
     <row r="195" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C195">
         <v>21.019108280254699</v>
@@ -7164,13 +7162,13 @@
         <v>70</v>
       </c>
       <c r="E195" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F195" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G195" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H195">
         <v>3.1</v>
@@ -7182,10 +7180,10 @@
     </row>
     <row r="196" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C196">
         <v>72.409638554216798</v>
@@ -7194,13 +7192,13 @@
         <v>73</v>
       </c>
       <c r="E196" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F196" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G196" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H196">
         <v>3.1</v>
@@ -7212,10 +7210,10 @@
     </row>
     <row r="197" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C197">
         <v>72.409638554216798</v>
@@ -7224,13 +7222,13 @@
         <v>48</v>
       </c>
       <c r="E197" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F197" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G197" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H197">
         <v>3.1</v>
@@ -7242,10 +7240,10 @@
     </row>
     <row r="198" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C198">
         <v>87.388535031847098</v>
@@ -7254,13 +7252,13 @@
         <v>74</v>
       </c>
       <c r="E198" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F198" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G198" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H198">
         <v>3.1</v>
@@ -7272,10 +7270,10 @@
     </row>
     <row r="199" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C199">
         <v>87.388535031847098</v>
@@ -7284,13 +7282,13 @@
         <v>74</v>
       </c>
       <c r="E199" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F199" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G199" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H199">
         <v>3.1</v>
@@ -7302,10 +7300,10 @@
     </row>
     <row r="200" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C200">
         <v>27.349397590361399</v>
@@ -7314,13 +7312,13 @@
         <v>79</v>
       </c>
       <c r="E200" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F200" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G200" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H200">
         <v>3.2</v>
@@ -7332,10 +7330,10 @@
     </row>
     <row r="201" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C201">
         <v>53.855421686746901</v>
@@ -7344,13 +7342,13 @@
         <v>79</v>
       </c>
       <c r="E201" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F201" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G201" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H201">
         <v>3.2</v>
@@ -7362,10 +7360,10 @@
     </row>
     <row r="202" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C202">
         <v>53.855421686746901</v>
@@ -7374,13 +7372,13 @@
         <v>79</v>
       </c>
       <c r="E202" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F202" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G202" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H202">
         <v>3.2</v>
@@ -7392,10 +7390,10 @@
     </row>
     <row r="203" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C203">
         <v>59.036144578313198</v>
@@ -7404,13 +7402,13 @@
         <v>79</v>
       </c>
       <c r="E203" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F203" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G203" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H203">
         <v>3.1</v>
@@ -7422,10 +7420,10 @@
     </row>
     <row r="204" spans="1:10" ht="195" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B204" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C204">
         <v>73.493975903614398</v>
@@ -7434,13 +7432,13 @@
         <v>46</v>
       </c>
       <c r="E204" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F204" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G204" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H204">
         <v>7</v>
@@ -7450,15 +7448,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J204" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C205">
         <v>73.493975903614398</v>
@@ -7467,13 +7465,13 @@
         <v>46</v>
       </c>
       <c r="E205" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F205" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G205" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H205">
         <v>2.2000000000000002</v>
@@ -7483,15 +7481,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J205" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B206" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C206">
         <v>73.493975903614398</v>
@@ -7500,13 +7498,13 @@
         <v>48</v>
       </c>
       <c r="E206" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F206" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G206" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H206">
         <v>2.2000000000000002</v>
@@ -7518,10 +7516,10 @@
     </row>
     <row r="207" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C207">
         <v>73.493975903614398</v>
@@ -7530,13 +7528,13 @@
         <v>60</v>
       </c>
       <c r="E207" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F207" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G207" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H207">
         <v>2.2000000000000002</v>
@@ -7546,15 +7544,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J207" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B208" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C208">
         <v>73.493975903614398</v>
@@ -7563,13 +7561,13 @@
         <v>60</v>
       </c>
       <c r="E208" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G208" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H208">
         <v>2.2000000000000002</v>
@@ -7581,10 +7579,10 @@
     </row>
     <row r="209" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B209" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C209">
         <v>73.493975903614398</v>
@@ -7593,13 +7591,13 @@
         <v>69</v>
       </c>
       <c r="E209" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F209" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G209" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H209">
         <v>7</v>
@@ -7609,15 +7607,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J209" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C210">
         <v>73.493975903614398</v>
@@ -7626,13 +7624,13 @@
         <v>68</v>
       </c>
       <c r="E210" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F210" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G210" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H210">
         <v>2.2000000000000002</v>
@@ -7642,15 +7640,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J210" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C211">
         <v>73.493975903614398</v>
@@ -7659,13 +7657,13 @@
         <v>73</v>
       </c>
       <c r="E211" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F211" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G211" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H211">
         <v>2.2000000000000002</v>
@@ -7675,15 +7673,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J211" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C212">
         <v>73.493975903614398</v>
@@ -7692,13 +7690,13 @@
         <v>74</v>
       </c>
       <c r="E212" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F212" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G212" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H212">
         <v>2.2000000000000002</v>
@@ -7708,15 +7706,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J212" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C213">
         <v>73.493975903614398</v>
@@ -7725,13 +7723,13 @@
         <v>95</v>
       </c>
       <c r="E213" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F213" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G213" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H213">
         <v>2.2000000000000002</v>
@@ -7741,15 +7739,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J213" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C214">
         <v>73.493975903614398</v>
@@ -7758,13 +7756,13 @@
         <v>100</v>
       </c>
       <c r="E214" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F214" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G214" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H214">
         <v>2.2000000000000002</v>
@@ -7774,15 +7772,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J214" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B215" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C215">
         <v>73.493975903614398</v>
@@ -7791,13 +7789,13 @@
         <v>73</v>
       </c>
       <c r="E215" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F215" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G215" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H215">
         <v>2.2000000000000002</v>
@@ -7809,10 +7807,10 @@
     </row>
     <row r="216" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B216" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C216">
         <v>73.493975903614398</v>
@@ -7821,13 +7819,13 @@
         <v>74</v>
       </c>
       <c r="E216" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F216" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G216" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H216">
         <v>2.2000000000000002</v>
@@ -7839,10 +7837,10 @@
     </row>
     <row r="217" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B217" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C217">
         <v>73.493975903614398</v>
@@ -7851,13 +7849,13 @@
         <v>95</v>
       </c>
       <c r="E217" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F217" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G217" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H217">
         <v>2.2000000000000002</v>
@@ -7869,10 +7867,10 @@
     </row>
     <row r="218" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C218">
         <v>59.036144578313198</v>
@@ -7881,13 +7879,13 @@
         <v>79</v>
       </c>
       <c r="E218" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F218" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G218" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H218">
         <v>3.1</v>
@@ -7899,10 +7897,10 @@
     </row>
     <row r="219" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C219">
         <v>54.337349397590302</v>
@@ -7911,13 +7909,13 @@
         <v>84</v>
       </c>
       <c r="E219" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F219" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G219" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H219">
         <v>3.1</v>
@@ -7929,10 +7927,10 @@
     </row>
     <row r="220" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C220">
         <v>54.337349397590302</v>
@@ -7941,13 +7939,13 @@
         <v>84</v>
       </c>
       <c r="E220" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F220" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G220" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H220">
         <v>3.1</v>
@@ -7959,10 +7957,10 @@
     </row>
     <row r="221" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C221">
         <v>53.855421686746901</v>
@@ -7971,13 +7969,13 @@
         <v>89</v>
       </c>
       <c r="E221" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F221" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G221" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H221">
         <v>3.1</v>
@@ -7989,10 +7987,10 @@
     </row>
     <row r="222" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C222">
         <v>53.855421686746901</v>
@@ -8001,13 +7999,13 @@
         <v>89</v>
       </c>
       <c r="E222" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F222" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G222" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H222">
         <v>3.1</v>
@@ -8019,10 +8017,10 @@
     </row>
     <row r="223" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C223">
         <v>27.349397590361399</v>
@@ -8031,13 +8029,13 @@
         <v>95</v>
       </c>
       <c r="E223" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F223" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G223" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H223">
         <v>3.2</v>
@@ -8049,10 +8047,10 @@
     </row>
     <row r="224" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C224">
         <v>27.349397590361399</v>
@@ -8061,13 +8059,13 @@
         <v>95</v>
       </c>
       <c r="E224" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F224" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G224" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H224">
         <v>3.2</v>
@@ -8079,10 +8077,10 @@
     </row>
     <row r="225" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C225">
         <v>25.2229299363057</v>
@@ -8091,13 +8089,13 @@
         <v>98</v>
       </c>
       <c r="E225" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F225" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G225" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H225">
         <v>3.1</v>
@@ -8109,10 +8107,10 @@
     </row>
     <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C226">
         <v>73.375796178343904</v>
@@ -8121,13 +8119,13 @@
         <v>98</v>
       </c>
       <c r="E226" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F226" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G226" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H226">
         <v>3.1</v>
@@ -8139,10 +8137,10 @@
     </row>
     <row r="227" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C227">
         <v>73.375796178343904</v>
@@ -8151,13 +8149,13 @@
         <v>98</v>
       </c>
       <c r="E227" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F227" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G227" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H227">
         <v>3.1</v>
@@ -8169,10 +8167,10 @@
     </row>
     <row r="228" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C228">
         <v>38.313253012048101</v>
@@ -8181,13 +8179,13 @@
         <v>101</v>
       </c>
       <c r="E228" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F228" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H228">
         <v>3.1</v>
@@ -8199,10 +8197,10 @@
     </row>
     <row r="229" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C229">
         <v>53.855421686746901</v>
@@ -8211,13 +8209,13 @@
         <v>101</v>
       </c>
       <c r="E229" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F229" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H229">
         <v>3.1</v>
@@ -8229,10 +8227,10 @@
     </row>
     <row r="230" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C230">
         <v>53.855421686746901</v>
@@ -8241,13 +8239,13 @@
         <v>101</v>
       </c>
       <c r="E230" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F230" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G230" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H230">
         <v>3.1</v>
@@ -8259,10 +8257,10 @@
     </row>
     <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C231">
         <v>54.337349397590302</v>
@@ -8271,13 +8269,13 @@
         <v>101</v>
       </c>
       <c r="E231" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F231" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G231" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H231">
         <v>3.1</v>
@@ -8289,10 +8287,10 @@
     </row>
     <row r="232" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C232">
         <v>90.722891566265005</v>
@@ -8301,13 +8299,13 @@
         <v>40</v>
       </c>
       <c r="E232" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F232" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G232" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H232">
         <v>1.4</v>
@@ -8319,10 +8317,10 @@
     </row>
     <row r="233" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C233">
         <v>90.722891566265005</v>
@@ -8331,13 +8329,13 @@
         <v>48</v>
       </c>
       <c r="E233" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F233" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G233" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H233">
         <v>1.4</v>
@@ -8349,10 +8347,10 @@
     </row>
     <row r="234" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C234">
         <v>90.722891566265005</v>
@@ -8361,13 +8359,13 @@
         <v>89</v>
       </c>
       <c r="E234" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F234" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G234" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H234">
         <v>1.4</v>
@@ -8379,10 +8377,10 @@
     </row>
     <row r="235" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C235">
         <v>90.722891566265005</v>
@@ -8391,13 +8389,13 @@
         <v>89</v>
       </c>
       <c r="E235" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F235" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G235" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H235">
         <v>1.4</v>
@@ -8409,10 +8407,10 @@
     </row>
     <row r="236" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C236">
         <v>91.337579617834393</v>
@@ -8421,13 +8419,13 @@
         <v>38</v>
       </c>
       <c r="E236" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F236" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G236" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H236">
         <v>1.4</v>
@@ -8439,10 +8437,10 @@
     </row>
     <row r="237" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C237">
         <v>91.337579617834393</v>
@@ -8451,13 +8449,13 @@
         <v>15</v>
       </c>
       <c r="E237" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F237" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G237" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H237">
         <v>1.4</v>
@@ -8469,10 +8467,10 @@
     </row>
     <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C238">
         <v>91.337579617834393</v>
@@ -8481,13 +8479,13 @@
         <v>20</v>
       </c>
       <c r="E238" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F238" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G238" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H238">
         <v>1.4</v>
@@ -8499,10 +8497,10 @@
     </row>
     <row r="239" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C239">
         <v>91.337579617834393</v>
@@ -8511,13 +8509,13 @@
         <v>38</v>
       </c>
       <c r="E239" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F239" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G239" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H239">
         <v>1.4</v>
@@ -8529,10 +8527,10 @@
     </row>
     <row r="240" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C240">
         <v>93.248407643312106</v>
@@ -8541,13 +8539,13 @@
         <v>37</v>
       </c>
       <c r="E240" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F240" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G240" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H240">
         <v>1.4</v>
@@ -8559,10 +8557,10 @@
     </row>
     <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C241">
         <v>93.248407643312106</v>
@@ -8571,13 +8569,13 @@
         <v>68</v>
       </c>
       <c r="E241" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F241" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G241" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H241">
         <v>1.4</v>
@@ -8589,10 +8587,10 @@
     </row>
     <row r="242" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C242">
         <v>93.248407643312106</v>
@@ -8601,13 +8599,13 @@
         <v>68</v>
       </c>
       <c r="E242" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F242" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G242" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H242">
         <v>1.4</v>
@@ -8619,10 +8617,10 @@
     </row>
     <row r="243" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C243">
         <v>93.248407643312106</v>
@@ -8631,13 +8629,13 @@
         <v>85</v>
       </c>
       <c r="E243" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F243" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G243" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H243">
         <v>1.4</v>
@@ -8649,10 +8647,10 @@
     </row>
     <row r="244" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C244">
         <v>93.855421686746993</v>
@@ -8661,13 +8659,13 @@
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F244" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G244" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H244">
         <v>1.4</v>
@@ -8679,10 +8677,10 @@
     </row>
     <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C245">
         <v>93.855421686746993</v>
@@ -8691,13 +8689,13 @@
         <v>60</v>
       </c>
       <c r="E245" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F245" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G245" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H245">
         <v>1.4</v>
@@ -8709,10 +8707,10 @@
     </row>
     <row r="246" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C246">
         <v>93.855421686746993</v>
@@ -8721,13 +8719,13 @@
         <v>60</v>
       </c>
       <c r="E246" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F246" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G246" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H246">
         <v>1.4</v>
@@ -8739,10 +8737,10 @@
     </row>
     <row r="247" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C247">
         <v>93.975903614457806</v>
@@ -8751,13 +8749,13 @@
         <v>23</v>
       </c>
       <c r="E247" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F247" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G247" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H247">
         <v>1.4</v>
@@ -8769,10 +8767,10 @@
     </row>
     <row r="248" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C248">
         <v>93.975903614457806</v>
@@ -8781,13 +8779,13 @@
         <v>30</v>
       </c>
       <c r="E248" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F248" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G248" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H248">
         <v>1.4</v>
@@ -8799,10 +8797,10 @@
     </row>
     <row r="249" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C249">
         <v>93.975903614457806</v>
@@ -8811,13 +8809,13 @@
         <v>95</v>
       </c>
       <c r="E249" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F249" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G249" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H249">
         <v>1.4</v>
@@ -8829,10 +8827,10 @@
     </row>
     <row r="250" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C250">
         <v>93.975903614457806</v>
@@ -8841,13 +8839,13 @@
         <v>23</v>
       </c>
       <c r="E250" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F250" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G250" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H250">
         <v>1.4</v>
@@ -8859,10 +8857,10 @@
     </row>
     <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C251">
         <v>93.975903614457806</v>
@@ -8871,13 +8869,13 @@
         <v>30</v>
       </c>
       <c r="E251" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F251" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G251" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H251">
         <v>1.4</v>
@@ -8889,10 +8887,10 @@
     </row>
     <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C252">
         <v>93.975903614457806</v>
@@ -8901,13 +8899,13 @@
         <v>95</v>
       </c>
       <c r="E252" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F252" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G252" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H252">
         <v>1.4</v>
@@ -8919,10 +8917,10 @@
     </row>
     <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C253">
         <v>93.975903614457806</v>
@@ -8931,13 +8929,13 @@
         <v>103</v>
       </c>
       <c r="E253" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F253" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G253" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H253">
         <v>1.4</v>
@@ -8949,10 +8947,10 @@
     </row>
     <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C254">
         <v>94.578313253011999</v>
@@ -8961,13 +8959,13 @@
         <v>48</v>
       </c>
       <c r="E254" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F254" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G254" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H254">
         <v>1.4</v>
@@ -8979,10 +8977,10 @@
     </row>
     <row r="255" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C255">
         <v>94.777070063694197</v>
@@ -8991,13 +8989,13 @@
         <v>38</v>
       </c>
       <c r="E255" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F255" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G255" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H255">
         <v>1.4</v>
@@ -9009,10 +9007,10 @@
     </row>
     <row r="256" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C256">
         <v>94.777070063694197</v>
@@ -9021,13 +9019,13 @@
         <v>38</v>
       </c>
       <c r="E256" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F256" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G256" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H256">
         <v>1.4</v>
@@ -9039,10 +9037,10 @@
     </row>
     <row r="257" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C257">
         <v>94.939759036144494</v>
@@ -9051,13 +9049,13 @@
         <v>48</v>
       </c>
       <c r="E257" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F257" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G257" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H257">
         <v>1.4</v>
@@ -9069,10 +9067,10 @@
     </row>
     <row r="258" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C258">
         <v>94.939759036144494</v>
@@ -9081,13 +9079,13 @@
         <v>31</v>
       </c>
       <c r="E258" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F258" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G258" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H258">
         <v>1.4</v>
@@ -9099,10 +9097,10 @@
     </row>
     <row r="259" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C259">
         <v>95.060240963855406</v>
@@ -9111,13 +9109,13 @@
         <v>73</v>
       </c>
       <c r="E259" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F259" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G259" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H259">
         <v>1.4</v>
@@ -9129,10 +9127,10 @@
     </row>
     <row r="260" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C260">
         <v>95.060240963855406</v>
@@ -9141,13 +9139,13 @@
         <v>101</v>
       </c>
       <c r="E260" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F260" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G260" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H260">
         <v>1.4</v>
@@ -9159,10 +9157,10 @@
     </row>
     <row r="261" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C261">
         <v>95.060240963855406</v>
@@ -9171,13 +9169,13 @@
         <v>73</v>
       </c>
       <c r="E261" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F261" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G261" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H261">
         <v>1.4</v>
@@ -9189,10 +9187,10 @@
     </row>
     <row r="262" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C262">
         <v>95.060240963855406</v>
@@ -9201,13 +9199,13 @@
         <v>101</v>
       </c>
       <c r="E262" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F262" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G262" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H262">
         <v>1.4</v>
@@ -9219,10 +9217,10 @@
     </row>
     <row r="263" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C263">
         <v>54.4578313253012</v>
@@ -9231,13 +9229,13 @@
         <v>84</v>
       </c>
       <c r="E263" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F263" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G263" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H263">
         <v>8.1</v>
@@ -9249,10 +9247,10 @@
     </row>
     <row r="264" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C264">
         <v>10</v>
@@ -9261,13 +9259,13 @@
         <v>85</v>
       </c>
       <c r="E264" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F264" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G264" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H264">
         <v>5</v>
@@ -9277,15 +9275,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J264" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C265">
         <v>16.867469879518001</v>
@@ -9294,13 +9292,13 @@
         <v>92</v>
       </c>
       <c r="E265" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F265" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G265" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H265">
         <v>8.1999999999999993</v>
@@ -9312,10 +9310,10 @@
     </row>
     <row r="266" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C266">
         <v>16.867469879518001</v>
@@ -9324,13 +9322,13 @@
         <v>92</v>
       </c>
       <c r="E266" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F266" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G266" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H266">
         <v>8.1999999999999993</v>
@@ -9342,10 +9340,10 @@
     </row>
     <row r="267" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C267">
         <v>10</v>
@@ -9354,13 +9352,13 @@
         <v>95</v>
       </c>
       <c r="E267" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F267" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G267" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H267">
         <v>4</v>
@@ -9372,10 +9370,10 @@
     </row>
     <row r="268" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C268">
         <v>11.084337349397501</v>
@@ -9384,13 +9382,13 @@
         <v>95</v>
       </c>
       <c r="E268" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F268" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G268" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H268">
         <v>4</v>
@@ -9402,10 +9400,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B269" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C269">
         <v>96.050955414012705</v>
@@ -9414,13 +9412,13 @@
         <v>38</v>
       </c>
       <c r="E269" t="s">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="F269" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G269" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H269">
         <v>1.4</v>
@@ -9432,10 +9430,10 @@
     </row>
     <row r="270" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C270">
         <v>96.265060240963805</v>
@@ -9444,13 +9442,13 @@
         <v>53</v>
       </c>
       <c r="E270" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F270" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G270" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H270">
         <v>1.4</v>
@@ -9462,10 +9460,10 @@
     </row>
     <row r="271" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C271">
         <v>96.265060240963805</v>
@@ -9474,13 +9472,13 @@
         <v>73</v>
       </c>
       <c r="E271" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F271" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G271" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H271">
         <v>1.4</v>
@@ -9492,10 +9490,10 @@
     </row>
     <row r="272" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C272">
         <v>96.265060240963805</v>
@@ -9504,13 +9502,13 @@
         <v>78</v>
       </c>
       <c r="E272" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F272" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G272" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H272">
         <v>1.4</v>
@@ -9522,10 +9520,10 @@
     </row>
     <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C273">
         <v>96.265060240963805</v>
@@ -9534,13 +9532,13 @@
         <v>53</v>
       </c>
       <c r="E273" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F273" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G273" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H273">
         <v>1.4</v>
@@ -9552,10 +9550,10 @@
     </row>
     <row r="274" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C274">
         <v>96.942675159235606</v>
@@ -9564,13 +9562,13 @@
         <v>38</v>
       </c>
       <c r="E274" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F274" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G274" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H274">
         <v>1.4</v>
@@ -9582,10 +9580,10 @@
     </row>
     <row r="275" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C275">
         <v>96.942675159235606</v>
@@ -9594,13 +9592,13 @@
         <v>38</v>
       </c>
       <c r="E275" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F275" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G275" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H275">
         <v>1.4</v>
@@ -9612,10 +9610,10 @@
     </row>
     <row r="276" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C276">
         <v>99.235668789808898</v>
@@ -9624,13 +9622,13 @@
         <v>58</v>
       </c>
       <c r="E276" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F276" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G276" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="H276">
         <v>1.4</v>
@@ -9642,10 +9640,10 @@
     </row>
     <row r="277" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C277">
         <v>99.235668789808898</v>
@@ -9654,13 +9652,13 @@
         <v>58</v>
       </c>
       <c r="E277" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="F277" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="G277" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="H277">
         <v>1.4</v>
@@ -9687,10 +9685,10 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -9698,10 +9696,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="O2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -9709,10 +9707,10 @@
         <v>1.2</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -9720,10 +9718,10 @@
         <v>1.3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -9731,10 +9729,10 @@
         <v>1.4</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="O5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -9742,7 +9740,7 @@
         <v>2.1</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -9750,7 +9748,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -9758,7 +9756,7 @@
         <v>3.1</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -9766,7 +9764,7 @@
         <v>3.2</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -9774,7 +9772,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -9782,7 +9780,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -9790,7 +9788,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -9798,7 +9796,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -9806,7 +9804,7 @@
         <v>8.1</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -9814,7 +9812,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -9822,7 +9820,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
+++ b/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\llm-goal-scope\data\qa_dataset\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD800F8-F15E-4E6C-99E3-0B5C24299C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31874166-D90D-4F06-8432-B9048E6B6561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="280">
   <si>
     <t>Sentence</t>
   </si>
@@ -60,9 +60,6 @@
     <t>ML model predicted True_otherChemical but the humans predicted No True_otherChemical.</t>
   </si>
   <si>
-    <t>original</t>
-  </si>
-  <si>
     <t>ML model predicted kg liveweight/head but the humans predicted No kg liveweight/head.</t>
   </si>
   <si>
@@ -858,9 +855,6 @@
     <t>Unclear why % is applied to hides</t>
   </si>
   <si>
-    <t>standardized</t>
-  </si>
-  <si>
     <t>Without RAG</t>
   </si>
   <si>
@@ -877,6 +871,15 @@
   </si>
   <si>
     <t>With RAG</t>
+  </si>
+  <si>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>Original</t>
+  </si>
+  <si>
+    <t>Standardized</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1216,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1231,24 +1234,24 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" t="s">
         <v>73</v>
       </c>
-      <c r="I1" t="s">
-        <v>74</v>
-      </c>
       <c r="J1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1257,13 +1260,13 @@
         <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H2">
         <v>1.1000000000000001</v>
@@ -1275,10 +1278,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1287,13 +1290,13 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H3">
         <v>1.1000000000000001</v>
@@ -1305,10 +1308,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1317,13 +1320,13 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H4">
         <v>1.1000000000000001</v>
@@ -1335,10 +1338,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1347,13 +1350,13 @@
         <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H5">
         <v>1.1000000000000001</v>
@@ -1365,10 +1368,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1377,13 +1380,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H6">
         <v>1.1000000000000001</v>
@@ -1395,10 +1398,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1407,13 +1410,13 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H7">
         <v>1.1000000000000001</v>
@@ -1425,10 +1428,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1437,13 +1440,13 @@
         <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H8">
         <v>1.1000000000000001</v>
@@ -1455,10 +1458,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1467,13 +1470,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H9">
         <v>1.1000000000000001</v>
@@ -1485,10 +1488,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1497,13 +1500,13 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F10" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H10">
         <v>1.1000000000000001</v>
@@ -1515,10 +1518,10 @@
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1527,13 +1530,13 @@
         <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F11" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H11">
         <v>1.1000000000000001</v>
@@ -1545,10 +1548,10 @@
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1557,13 +1560,13 @@
         <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F12" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H12">
         <v>1.1000000000000001</v>
@@ -1575,10 +1578,10 @@
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1587,13 +1590,13 @@
         <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F13" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H13">
         <v>1.1000000000000001</v>
@@ -1605,10 +1608,10 @@
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1617,13 +1620,13 @@
         <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F14" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H14">
         <v>1.1000000000000001</v>
@@ -1635,10 +1638,10 @@
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1647,13 +1650,13 @@
         <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F15" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H15">
         <v>1.1000000000000001</v>
@@ -1665,10 +1668,10 @@
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1677,13 +1680,13 @@
         <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F16" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H16">
         <v>1.1000000000000001</v>
@@ -1695,10 +1698,10 @@
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1707,13 +1710,13 @@
         <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F17" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H17">
         <v>1.1000000000000001</v>
@@ -1725,10 +1728,10 @@
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1737,13 +1740,13 @@
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F18" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H18">
         <v>1.1000000000000001</v>
@@ -1755,10 +1758,10 @@
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1767,13 +1770,13 @@
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F19" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H19">
         <v>1.1000000000000001</v>
@@ -1785,10 +1788,10 @@
     </row>
     <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>0.240963855421686</v>
@@ -1797,13 +1800,13 @@
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F20" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H20">
         <v>1.2</v>
@@ -1815,10 +1818,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>0.48192771084337299</v>
@@ -1827,13 +1830,13 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F21" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H21">
         <v>1.2</v>
@@ -1845,10 +1848,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>0.48192771084337299</v>
@@ -1857,13 +1860,13 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F22" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G22" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H22">
         <v>1.2</v>
@@ -1875,10 +1878,10 @@
     </row>
     <row r="23" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23">
         <v>0.48192771084337299</v>
@@ -1887,13 +1890,13 @@
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F23" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H23">
         <v>1.2</v>
@@ -1903,12 +1906,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>0.48192771084337299</v>
@@ -1917,13 +1920,13 @@
         <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F24" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H24">
         <v>1.2</v>
@@ -1933,12 +1936,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>0.48192771084337299</v>
@@ -1947,13 +1950,13 @@
         <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F25" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H25">
         <v>1.2</v>
@@ -1963,12 +1966,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26">
         <v>1.44578313253012</v>
@@ -1977,13 +1980,13 @@
         <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F26" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H26">
         <v>1.2</v>
@@ -1995,10 +1998,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>1.6867469879518</v>
@@ -2007,13 +2010,13 @@
         <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F27" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H27">
         <v>1.2</v>
@@ -2025,10 +2028,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>1.6867469879518</v>
@@ -2037,13 +2040,13 @@
         <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F28" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H28">
         <v>1.2</v>
@@ -2053,12 +2056,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>1.6867469879518</v>
@@ -2067,13 +2070,13 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F29" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G29" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H29">
         <v>1.2</v>
@@ -2083,12 +2086,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>54.4578313253012</v>
@@ -2097,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F30" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G30" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H30">
         <v>8.1</v>
@@ -2113,15 +2116,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>2.6506024096385499</v>
@@ -2130,13 +2133,13 @@
         <v>79</v>
       </c>
       <c r="E31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F31" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H31">
         <v>1.2</v>
@@ -2146,12 +2149,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>2.6506024096385499</v>
@@ -2160,13 +2163,13 @@
         <v>79</v>
       </c>
       <c r="E32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F32" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G32" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H32">
         <v>1.2</v>
@@ -2176,12 +2179,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33">
         <v>3.13253012048192</v>
@@ -2190,13 +2193,13 @@
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F33" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H33">
         <v>1.2</v>
@@ -2208,10 +2211,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <v>3.13253012048192</v>
@@ -2220,13 +2223,13 @@
         <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F34" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G34" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H34">
         <v>1.2</v>
@@ -2236,12 +2239,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35">
         <v>3.13253012048192</v>
@@ -2250,13 +2253,13 @@
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F35" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H35">
         <v>1.2</v>
@@ -2266,12 +2269,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>3.13253012048192</v>
@@ -2280,13 +2283,13 @@
         <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F36" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G36" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H36">
         <v>1.2</v>
@@ -2296,12 +2299,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37">
         <v>3.13253012048192</v>
@@ -2310,13 +2313,13 @@
         <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F37" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G37" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H37">
         <v>1.2</v>
@@ -2326,12 +2329,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38">
         <v>3.13253012048192</v>
@@ -2340,13 +2343,13 @@
         <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F38" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H38">
         <v>1.2</v>
@@ -2356,12 +2359,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39">
         <v>3.13253012048192</v>
@@ -2370,13 +2373,13 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F39" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H39">
         <v>1.2</v>
@@ -2386,12 +2389,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>54.4578313253012</v>
@@ -2400,13 +2403,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F40" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H40">
         <v>8.1</v>
@@ -2416,15 +2419,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J40" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>16.867469879518001</v>
@@ -2433,13 +2436,13 @@
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F41" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H41">
         <v>8.1999999999999993</v>
@@ -2449,15 +2452,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J41" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>16.867469879518001</v>
@@ -2466,13 +2469,13 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F42" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G42" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H42">
         <v>8.1999999999999993</v>
@@ -2482,15 +2485,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43">
         <v>95.301204819277103</v>
@@ -2499,13 +2502,13 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F43" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G43" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H43">
         <v>1.4</v>
@@ -2515,12 +2518,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>4.96815286624203</v>
@@ -2529,13 +2532,13 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F44" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H44">
         <v>1.2</v>
@@ -2545,12 +2548,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45">
         <v>4.96815286624203</v>
@@ -2559,13 +2562,13 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F45" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G45" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H45">
         <v>1.2</v>
@@ -2575,12 +2578,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>4.96815286624203</v>
@@ -2589,13 +2592,13 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F46" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G46" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H46">
         <v>1.2</v>
@@ -2605,12 +2608,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47">
         <v>4.96815286624203</v>
@@ -2619,13 +2622,13 @@
         <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F47" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G47" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H47">
         <v>1.2</v>
@@ -2635,12 +2638,12 @@
         <v>Label occurs &lt;5% of the time in training samples</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C48">
         <v>5.4216867469879499</v>
@@ -2649,13 +2652,13 @@
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F48" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G48" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H48">
         <v>1.3</v>
@@ -2665,12 +2668,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49">
         <v>5.4216867469879499</v>
@@ -2679,13 +2682,13 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F49" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G49" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H49">
         <v>1.3</v>
@@ -2695,12 +2698,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50">
         <v>5.4216867469879499</v>
@@ -2709,13 +2712,13 @@
         <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F50" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G50" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H50">
         <v>1.3</v>
@@ -2725,12 +2728,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51">
         <v>5.4216867469879499</v>
@@ -2739,13 +2742,13 @@
         <v>79</v>
       </c>
       <c r="E51" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F51" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G51" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H51">
         <v>1.3</v>
@@ -2755,12 +2758,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C52">
         <v>5.4216867469879499</v>
@@ -2769,13 +2772,13 @@
         <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F52" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G52" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H52">
         <v>1.3</v>
@@ -2785,12 +2788,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53">
         <v>5.4216867469879499</v>
@@ -2799,13 +2802,13 @@
         <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F53" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G53" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H53">
         <v>1.3</v>
@@ -2817,10 +2820,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C54">
         <v>6.6242038216560504</v>
@@ -2829,13 +2832,13 @@
         <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F54" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G54" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H54">
         <v>1.3</v>
@@ -2847,10 +2850,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55">
         <v>6.6242038216560504</v>
@@ -2859,13 +2862,13 @@
         <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F55" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H55">
         <v>1.3</v>
@@ -2875,12 +2878,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56">
         <v>8.0254777070063703</v>
@@ -2889,13 +2892,13 @@
         <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F56" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G56" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H56">
         <v>1.3</v>
@@ -2905,12 +2908,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57">
         <v>8.19277108433735</v>
@@ -2919,13 +2922,13 @@
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F57" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H57">
         <v>1.3</v>
@@ -2935,12 +2938,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58">
         <v>8.19277108433735</v>
@@ -2949,13 +2952,13 @@
         <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F58" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G58" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H58">
         <v>1.3</v>
@@ -2965,12 +2968,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C59">
         <v>8.19277108433735</v>
@@ -2979,13 +2982,13 @@
         <v>93</v>
       </c>
       <c r="E59" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F59" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H59">
         <v>1.3</v>
@@ -2995,12 +2998,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60">
         <v>8.19277108433735</v>
@@ -3009,13 +3012,13 @@
         <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F60" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G60" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H60">
         <v>1.3</v>
@@ -3025,12 +3028,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C61">
         <v>8.19277108433735</v>
@@ -3039,13 +3042,13 @@
         <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F61" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G61" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H61">
         <v>1.3</v>
@@ -3055,12 +3058,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62">
         <v>8.19277108433735</v>
@@ -3069,13 +3072,13 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F62" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G62" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H62">
         <v>1.3</v>
@@ -3085,12 +3088,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="300" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <v>8.6746987951807206</v>
@@ -3099,13 +3102,13 @@
         <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F63" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G63" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H63">
         <v>1.3</v>
@@ -3115,12 +3118,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C64">
         <v>8.6746987951807206</v>
@@ -3129,13 +3132,13 @@
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F64" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G64" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H64">
         <v>1.3</v>
@@ -3145,12 +3148,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C65">
         <v>8.6746987951807206</v>
@@ -3159,13 +3162,13 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F65" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G65" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H65">
         <v>1.3</v>
@@ -3175,12 +3178,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66">
         <v>8.6746987951807206</v>
@@ -3189,13 +3192,13 @@
         <v>84</v>
       </c>
       <c r="E66" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F66" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G66" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H66">
         <v>1.3</v>
@@ -3205,12 +3208,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C67">
         <v>8.9171974522292992</v>
@@ -3219,13 +3222,13 @@
         <v>53</v>
       </c>
       <c r="E67" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F67" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G67" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H67">
         <v>1.3</v>
@@ -3235,12 +3238,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>8.9171974522292992</v>
@@ -3249,13 +3252,13 @@
         <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F68" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H68">
         <v>1.3</v>
@@ -3265,12 +3268,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C69">
         <v>8.9171974522292992</v>
@@ -3279,13 +3282,13 @@
         <v>70</v>
       </c>
       <c r="E69" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F69" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H69">
         <v>1.3</v>
@@ -3295,12 +3298,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70">
         <v>8.9171974522292992</v>
@@ -3309,13 +3312,13 @@
         <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F70" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G70" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H70">
         <v>1.3</v>
@@ -3325,12 +3328,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C71">
         <v>8.9171974522292992</v>
@@ -3339,14 +3342,14 @@
         <v>58</v>
       </c>
       <c r="E71" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F71" t="str">
         <f>$F$7</f>
-        <v>standardized</v>
+        <v>Standardized</v>
       </c>
       <c r="G71" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H71">
         <v>1.3</v>
@@ -3356,12 +3359,12 @@
         <v>Label occurs &lt;10% of the time in training samples</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C72">
         <v>8.9171974522292992</v>
@@ -3370,13 +3373,13 @@
         <v>59</v>
       </c>
       <c r="E72" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F72" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G72" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H72">
         <v>1.3</v>
@@ -3388,10 +3391,10 @@
     </row>
     <row r="73" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73">
         <v>54.4578313253012</v>
@@ -3400,13 +3403,13 @@
         <v>25</v>
       </c>
       <c r="E73" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G73" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H73">
         <v>8.1</v>
@@ -3416,12 +3419,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -3430,13 +3433,13 @@
         <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F74" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G74" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H74">
         <v>4</v>
@@ -3446,12 +3449,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75">
         <v>95.301204819277103</v>
@@ -3460,13 +3463,13 @@
         <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F75" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G75" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H75">
         <v>1.4</v>
@@ -3476,12 +3479,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76">
         <v>54.4578313253012</v>
@@ -3490,13 +3493,13 @@
         <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F76" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G76" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H76">
         <v>8.1</v>
@@ -3506,15 +3509,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J76" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77">
         <v>16.867469879518001</v>
@@ -3523,13 +3526,13 @@
         <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F77" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G77" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H77">
         <v>8.1999999999999993</v>
@@ -3539,15 +3542,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J77" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78">
         <v>54.4578313253012</v>
@@ -3556,13 +3559,13 @@
         <v>41</v>
       </c>
       <c r="E78" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F78" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H78">
         <v>8.1</v>
@@ -3572,12 +3575,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C79">
         <v>4.6987951807228896</v>
@@ -3586,13 +3589,13 @@
         <v>54</v>
       </c>
       <c r="E79" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F79" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H79">
         <v>1.2</v>
@@ -3604,10 +3607,10 @@
     </row>
     <row r="80" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80">
         <v>54.4578313253012</v>
@@ -3616,13 +3619,13 @@
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F80" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G80" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H80">
         <v>8.1</v>
@@ -3634,10 +3637,10 @@
     </row>
     <row r="81" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81">
         <v>16.867469879518001</v>
@@ -3646,13 +3649,13 @@
         <v>33</v>
       </c>
       <c r="E81" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F81" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G81" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H81">
         <v>8.1999999999999993</v>
@@ -3664,10 +3667,10 @@
     </row>
     <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -3676,13 +3679,13 @@
         <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F82" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G82" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H82">
         <v>4</v>
@@ -3694,10 +3697,10 @@
     </row>
     <row r="83" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C83">
         <v>18.2165605095541</v>
@@ -3706,13 +3709,13 @@
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F83" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G83" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H83">
         <v>8.1999999999999993</v>
@@ -3724,10 +3727,10 @@
     </row>
     <row r="84" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C84">
         <v>18.2165605095541</v>
@@ -3736,13 +3739,13 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F84" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G84" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H84">
         <v>8.1</v>
@@ -3754,10 +3757,10 @@
     </row>
     <row r="85" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85">
         <v>56.8152866242038</v>
@@ -3766,13 +3769,13 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F85" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G85" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H85">
         <v>8.1</v>
@@ -3784,10 +3787,10 @@
     </row>
     <row r="86" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C86">
         <v>18.2165605095541</v>
@@ -3796,13 +3799,13 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G86" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H86">
         <v>8.1999999999999993</v>
@@ -3814,10 +3817,10 @@
     </row>
     <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87">
         <v>56.8152866242038</v>
@@ -3826,13 +3829,13 @@
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F87" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G87" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H87">
         <v>8.1</v>
@@ -3842,15 +3845,15 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
       <c r="J87" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C88">
         <v>18.2165605095541</v>
@@ -3859,13 +3862,13 @@
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F88" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G88" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H88">
         <v>8.1</v>
@@ -3877,10 +3880,10 @@
     </row>
     <row r="89" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89">
         <v>56.8152866242038</v>
@@ -3889,13 +3892,13 @@
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F89" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G89" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H89">
         <v>8.1</v>
@@ -3907,10 +3910,10 @@
     </row>
     <row r="90" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90">
         <v>56.8152866242038</v>
@@ -3919,13 +3922,13 @@
         <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F90" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G90" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H90">
         <v>8.1</v>
@@ -3937,10 +3940,10 @@
     </row>
     <row r="91" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91">
         <v>54.4578313253012</v>
@@ -3949,13 +3952,13 @@
         <v>41</v>
       </c>
       <c r="E91" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F91" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G91" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H91">
         <v>8.1</v>
@@ -3965,12 +3968,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C92">
         <v>11.084337349397501</v>
@@ -3979,13 +3982,13 @@
         <v>54</v>
       </c>
       <c r="E92" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F92" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G92" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -3995,15 +3998,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J92" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93">
         <v>95.301204819277103</v>
@@ -4012,13 +4015,13 @@
         <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F93" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G93" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H93">
         <v>1.4</v>
@@ -4028,12 +4031,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C94">
         <v>16.867469879518001</v>
@@ -4042,13 +4045,13 @@
         <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F94" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G94" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H94">
         <v>8.1999999999999993</v>
@@ -4058,15 +4061,15 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
       <c r="J94" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C95">
         <v>16.867469879518001</v>
@@ -4075,13 +4078,13 @@
         <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F95" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G95" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H95">
         <v>8.1</v>
@@ -4091,12 +4094,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96">
         <v>54.4578313253012</v>
@@ -4105,13 +4108,13 @@
         <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F96" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G96" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H96">
         <v>8.1</v>
@@ -4121,12 +4124,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C97">
         <v>4.6987951807228896</v>
@@ -4135,13 +4138,13 @@
         <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F97" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G97" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H97">
         <v>1.2</v>
@@ -4153,10 +4156,10 @@
     </row>
     <row r="98" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C98">
         <v>11.084337349397501</v>
@@ -4165,13 +4168,13 @@
         <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F98" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G98" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H98">
         <v>5</v>
@@ -4181,15 +4184,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J98" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C99">
         <v>95.301204819277103</v>
@@ -4198,13 +4201,13 @@
         <v>54</v>
       </c>
       <c r="E99" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F99" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G99" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H99">
         <v>1.4</v>
@@ -4216,10 +4219,10 @@
     </row>
     <row r="100" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100">
         <v>54.4578313253012</v>
@@ -4228,13 +4231,13 @@
         <v>58</v>
       </c>
       <c r="E100" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F100" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G100" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H100">
         <v>8.1</v>
@@ -4244,12 +4247,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C101">
         <v>13.6144578313253</v>
@@ -4258,13 +4261,13 @@
         <v>79</v>
       </c>
       <c r="E101" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F101" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G101" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H101">
         <v>4</v>
@@ -4274,12 +4277,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C102">
         <v>13.6144578313253</v>
@@ -4288,13 +4291,13 @@
         <v>79</v>
       </c>
       <c r="E102" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F102" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G102" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H102">
         <v>4</v>
@@ -4304,12 +4307,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C103">
         <v>13.975903614457801</v>
@@ -4318,13 +4321,13 @@
         <v>41</v>
       </c>
       <c r="E103" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F103" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G103" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H103">
         <v>7</v>
@@ -4334,15 +4337,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J103" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C104">
         <v>13.975903614457801</v>
@@ -4351,13 +4354,13 @@
         <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F104" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H104">
         <v>2.1</v>
@@ -4367,15 +4370,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J104" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C105">
         <v>13.975903614457801</v>
@@ -4384,13 +4387,13 @@
         <v>48</v>
       </c>
       <c r="E105" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F105" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G105" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H105">
         <v>2.1</v>
@@ -4400,15 +4403,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J105" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C106">
         <v>13.975903614457801</v>
@@ -4417,13 +4420,13 @@
         <v>48</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F106" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G106" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H106">
         <v>7</v>
@@ -4433,15 +4436,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J106" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C107">
         <v>13.975903614457801</v>
@@ -4450,13 +4453,13 @@
         <v>60</v>
       </c>
       <c r="E107" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F107" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G107" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H107">
         <v>2.2000000000000002</v>
@@ -4466,15 +4469,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J107" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C108">
         <v>13.975903614457801</v>
@@ -4483,13 +4486,13 @@
         <v>84</v>
       </c>
       <c r="E108" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F108" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G108" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H108">
         <v>2.1</v>
@@ -4499,15 +4502,15 @@
         <v>In Allocation, confused none with none required</v>
       </c>
       <c r="J108" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C109">
         <v>13.975903614457801</v>
@@ -4516,13 +4519,13 @@
         <v>95</v>
       </c>
       <c r="E109" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F109" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G109" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H109">
         <v>2.2000000000000002</v>
@@ -4532,15 +4535,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J109" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C110">
         <v>13.975903614457801</v>
@@ -4549,13 +4552,13 @@
         <v>100</v>
       </c>
       <c r="E110" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F110" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G110" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H110">
         <v>2.2000000000000002</v>
@@ -4565,15 +4568,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J110" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C111">
         <v>13.975903614457801</v>
@@ -4582,13 +4585,13 @@
         <v>84</v>
       </c>
       <c r="E111" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F111" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G111" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H111">
         <v>2.1</v>
@@ -4598,12 +4601,12 @@
         <v>In Allocation, confused none with none required</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C112">
         <v>13.975903614457801</v>
@@ -4612,13 +4615,13 @@
         <v>95</v>
       </c>
       <c r="E112" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F112" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G112" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H112">
         <v>2.2000000000000002</v>
@@ -4630,10 +4633,10 @@
     </row>
     <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C113">
         <v>10</v>
@@ -4642,13 +4645,13 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F113" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G113" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -4658,15 +4661,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J113" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C114">
         <v>11.084337349397501</v>
@@ -4675,13 +4678,13 @@
         <v>63</v>
       </c>
       <c r="E114" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F114" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G114" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H114">
         <v>4</v>
@@ -4691,15 +4694,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J114" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C115">
         <v>16.867469879518001</v>
@@ -4708,13 +4711,13 @@
         <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F115" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H115">
         <v>8.1999999999999993</v>
@@ -4724,12 +4727,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C116">
         <v>10</v>
@@ -4738,13 +4741,13 @@
         <v>60</v>
       </c>
       <c r="E116" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F116" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G116" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -4754,15 +4757,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J116" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C117">
         <v>11.084337349397501</v>
@@ -4771,13 +4774,13 @@
         <v>63</v>
       </c>
       <c r="E117" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F117" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H117">
         <v>4</v>
@@ -4787,15 +4790,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J117" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118">
         <v>16.867469879518001</v>
@@ -4804,13 +4807,13 @@
         <v>66</v>
       </c>
       <c r="E118" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F118" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G118" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H118">
         <v>8.1999999999999993</v>
@@ -4820,12 +4823,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -4834,13 +4837,13 @@
         <v>68</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F119" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G119" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H119">
         <v>4</v>
@@ -4850,12 +4853,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C120">
         <v>11.084337349397501</v>
@@ -4864,13 +4867,13 @@
         <v>68</v>
       </c>
       <c r="E120" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F120" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G120" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H120">
         <v>4</v>
@@ -4880,12 +4883,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C121">
         <v>11.084337349397501</v>
@@ -4894,13 +4897,13 @@
         <v>73</v>
       </c>
       <c r="E121" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F121" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G121" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H121">
         <v>5</v>
@@ -4910,15 +4913,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J121" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -4927,13 +4930,13 @@
         <v>68</v>
       </c>
       <c r="E122" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F122" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G122" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H122">
         <v>5</v>
@@ -4943,15 +4946,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J122" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C123">
         <v>56.8152866242038</v>
@@ -4960,13 +4963,13 @@
         <v>31</v>
       </c>
       <c r="E123" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F123" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G123" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H123">
         <v>8.1</v>
@@ -4978,10 +4981,10 @@
     </row>
     <row r="124" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C124">
         <v>18.2165605095541</v>
@@ -4990,13 +4993,13 @@
         <v>35</v>
       </c>
       <c r="E124" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F124" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G124" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H124">
         <v>8.1999999999999993</v>
@@ -5008,10 +5011,10 @@
     </row>
     <row r="125" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C125">
         <v>56.8152866242038</v>
@@ -5020,13 +5023,13 @@
         <v>36</v>
       </c>
       <c r="E125" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F125" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G125" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H125">
         <v>8.1</v>
@@ -5038,10 +5041,10 @@
     </row>
     <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C126">
         <v>10.191082802547699</v>
@@ -5050,13 +5053,13 @@
         <v>38</v>
       </c>
       <c r="E126" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F126" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G126" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H126">
         <v>5</v>
@@ -5066,15 +5069,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J126" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C127">
         <v>56.8152866242038</v>
@@ -5083,13 +5086,13 @@
         <v>38</v>
       </c>
       <c r="E127" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F127" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G127" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H127">
         <v>5</v>
@@ -5099,15 +5102,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J127" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C128">
         <v>18.2165605095541</v>
@@ -5116,13 +5119,13 @@
         <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F128" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G128" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H128">
         <v>8.1999999999999993</v>
@@ -5132,12 +5135,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C129">
         <v>18.2165605095541</v>
@@ -5146,13 +5149,13 @@
         <v>40</v>
       </c>
       <c r="E129" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F129" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G129" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H129">
         <v>8.1999999999999993</v>
@@ -5162,12 +5165,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C130">
         <v>18.2165605095541</v>
@@ -5176,13 +5179,13 @@
         <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F130" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G130" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H130">
         <v>8.1</v>
@@ -5194,10 +5197,10 @@
     </row>
     <row r="131" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C131">
         <v>18.2165605095541</v>
@@ -5206,13 +5209,13 @@
         <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F131" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G131" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H131">
         <v>8.1999999999999993</v>
@@ -5224,10 +5227,10 @@
     </row>
     <row r="132" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C132">
         <v>56.8152866242038</v>
@@ -5236,13 +5239,13 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F132" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G132" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H132">
         <v>8.1</v>
@@ -5252,12 +5255,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C133">
         <v>87.388535031847098</v>
@@ -5266,13 +5269,13 @@
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F133" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G133" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H133">
         <v>3.1</v>
@@ -5282,12 +5285,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C134">
         <v>87.388535031847098</v>
@@ -5296,13 +5299,13 @@
         <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F134" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G134" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H134">
         <v>3.1</v>
@@ -5312,12 +5315,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C135">
         <v>24.337349397590302</v>
@@ -5326,13 +5329,13 @@
         <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F135" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G135" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H135">
         <v>3.2</v>
@@ -5342,12 +5345,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C136">
         <v>87.388535031847098</v>
@@ -5356,13 +5359,13 @@
         <v>13</v>
       </c>
       <c r="E136" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F136" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G136" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H136">
         <v>3.1</v>
@@ -5372,12 +5375,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C137">
         <v>87.388535031847098</v>
@@ -5386,13 +5389,13 @@
         <v>13</v>
       </c>
       <c r="E137" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F137" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G137" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H137">
         <v>3.1</v>
@@ -5402,12 +5405,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C138">
         <v>38.313253012048101</v>
@@ -5416,13 +5419,13 @@
         <v>16</v>
       </c>
       <c r="E138" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F138" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G138" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H138">
         <v>3.1</v>
@@ -5432,12 +5435,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C139">
         <v>54.337349397590302</v>
@@ -5446,13 +5449,13 @@
         <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F139" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G139" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H139">
         <v>3.1</v>
@@ -5462,12 +5465,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C140">
         <v>59.036144578313198</v>
@@ -5476,13 +5479,13 @@
         <v>23</v>
       </c>
       <c r="E140" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F140" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G140" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H140">
         <v>3.1</v>
@@ -5492,12 +5495,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C141">
         <v>87.388535031847098</v>
@@ -5506,13 +5509,13 @@
         <v>38</v>
       </c>
       <c r="E141" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F141" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G141" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H141">
         <v>3.1</v>
@@ -5522,12 +5525,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C142">
         <v>87.388535031847098</v>
@@ -5536,13 +5539,13 @@
         <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F142" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G142" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H142">
         <v>3.1</v>
@@ -5552,12 +5555,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C143">
         <v>87.388535031847098</v>
@@ -5566,13 +5569,13 @@
         <v>40</v>
       </c>
       <c r="E143" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F143" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G143" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H143">
         <v>3.1</v>
@@ -5582,12 +5585,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C144">
         <v>87.388535031847098</v>
@@ -5596,13 +5599,13 @@
         <v>40</v>
       </c>
       <c r="E144" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F144" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G144" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H144">
         <v>3.1</v>
@@ -5612,12 +5615,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C145">
         <v>87.388535031847098</v>
@@ -5626,13 +5629,13 @@
         <v>44</v>
       </c>
       <c r="E145" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F145" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G145" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H145">
         <v>3.1</v>
@@ -5642,12 +5645,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C146">
         <v>87.388535031847098</v>
@@ -5656,13 +5659,13 @@
         <v>44</v>
       </c>
       <c r="E146" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F146" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G146" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H146">
         <v>3.1</v>
@@ -5672,12 +5675,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C147">
         <v>87.388535031847098</v>
@@ -5686,13 +5689,13 @@
         <v>46</v>
       </c>
       <c r="E147" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F147" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G147" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H147">
         <v>3.1</v>
@@ -5702,12 +5705,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C148">
         <v>87.388535031847098</v>
@@ -5716,13 +5719,13 @@
         <v>46</v>
       </c>
       <c r="E148" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F148" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G148" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H148">
         <v>3.1</v>
@@ -5732,12 +5735,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C149">
         <v>21.019108280254699</v>
@@ -5746,13 +5749,13 @@
         <v>53</v>
       </c>
       <c r="E149" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F149" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G149" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H149">
         <v>3.1</v>
@@ -5762,12 +5765,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C150">
         <v>73.375796178343904</v>
@@ -5776,13 +5779,13 @@
         <v>53</v>
       </c>
       <c r="E150" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F150" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G150" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H150">
         <v>3.2</v>
@@ -5792,12 +5795,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C151">
         <v>53.855421686746901</v>
@@ -5806,13 +5809,13 @@
         <v>54</v>
       </c>
       <c r="E151" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F151" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G151" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H151">
         <v>3.2</v>
@@ -5822,12 +5825,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C152">
         <v>54.337349397590302</v>
@@ -5836,13 +5839,13 @@
         <v>18</v>
       </c>
       <c r="E152" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F152" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G152" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H152">
         <v>3.1</v>
@@ -5852,12 +5855,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C153">
         <v>53.855421686746901</v>
@@ -5866,13 +5869,13 @@
         <v>54</v>
       </c>
       <c r="E153" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F153" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G153" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H153">
         <v>3.2</v>
@@ -5882,12 +5885,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C154">
         <v>59.036144578313198</v>
@@ -5896,13 +5899,13 @@
         <v>54</v>
       </c>
       <c r="E154" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F154" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G154" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H154">
         <v>3.1</v>
@@ -5912,12 +5915,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C155">
         <v>59.036144578313198</v>
@@ -5926,13 +5929,13 @@
         <v>54</v>
       </c>
       <c r="E155" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F155" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G155" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H155">
         <v>3.1</v>
@@ -5942,12 +5945,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C156">
         <v>72.409638554216798</v>
@@ -5956,13 +5959,13 @@
         <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F156" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G156" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H156">
         <v>3.2</v>
@@ -5972,12 +5975,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C157">
         <v>72.409638554216798</v>
@@ -5986,13 +5989,13 @@
         <v>60</v>
       </c>
       <c r="E157" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F157" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G157" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H157">
         <v>3.2</v>
@@ -6004,10 +6007,10 @@
     </row>
     <row r="158" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C158">
         <v>11.084337349397501</v>
@@ -6016,13 +6019,13 @@
         <v>68</v>
       </c>
       <c r="E158" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F158" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G158" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H158">
         <v>5</v>
@@ -6032,15 +6035,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J158" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C159">
         <v>2.2891566265060201</v>
@@ -6049,13 +6052,13 @@
         <v>70</v>
       </c>
       <c r="E159" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F159" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G159" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H159">
         <v>1.2</v>
@@ -6067,10 +6070,10 @@
     </row>
     <row r="160" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C160">
         <v>11.084337349397501</v>
@@ -6079,13 +6082,13 @@
         <v>73</v>
       </c>
       <c r="E160" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F160" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G160" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H160">
         <v>5</v>
@@ -6095,15 +6098,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J160" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C161">
         <v>4.6987951807228896</v>
@@ -6112,13 +6115,13 @@
         <v>79</v>
       </c>
       <c r="E161" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F161" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G161" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H161">
         <v>1.2</v>
@@ -6130,10 +6133,10 @@
     </row>
     <row r="162" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C162">
         <v>11.084337349397501</v>
@@ -6142,13 +6145,13 @@
         <v>79</v>
       </c>
       <c r="E162" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F162" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G162" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H162">
         <v>4</v>
@@ -6158,15 +6161,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J162" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C163">
         <v>10</v>
@@ -6175,13 +6178,13 @@
         <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F163" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G163" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H163">
         <v>4</v>
@@ -6191,12 +6194,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C164">
         <v>4.6987951807228896</v>
@@ -6205,13 +6208,13 @@
         <v>79</v>
       </c>
       <c r="E164" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F164" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G164" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H164">
         <v>4</v>
@@ -6221,12 +6224,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C165">
         <v>95.301204819277103</v>
@@ -6235,13 +6238,13 @@
         <v>79</v>
       </c>
       <c r="E165" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F165" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G165" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H165">
         <v>1.4</v>
@@ -6251,12 +6254,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C166">
         <v>54.4578313253012</v>
@@ -6265,13 +6268,13 @@
         <v>84</v>
       </c>
       <c r="E166" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F166" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G166" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H166">
         <v>6</v>
@@ -6281,12 +6284,12 @@
         <v>Unclear</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C167">
         <v>10</v>
@@ -6295,13 +6298,13 @@
         <v>85</v>
       </c>
       <c r="E167" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F167" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G167" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H167">
         <v>5</v>
@@ -6311,15 +6314,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J167" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C168">
         <v>95.301204819277103</v>
@@ -6328,13 +6331,13 @@
         <v>79</v>
       </c>
       <c r="E168" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F168" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G168" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H168">
         <v>1.4</v>
@@ -6346,10 +6349,10 @@
     </row>
     <row r="169" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C169">
         <v>56.8152866242038</v>
@@ -6358,13 +6361,13 @@
         <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F169" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G169" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H169">
         <v>8.1</v>
@@ -6376,10 +6379,10 @@
     </row>
     <row r="170" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C170">
         <v>10.191082802547699</v>
@@ -6388,13 +6391,13 @@
         <v>53</v>
       </c>
       <c r="E170" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F170" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G170" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H170">
         <v>4</v>
@@ -6404,15 +6407,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J170" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C171">
         <v>56.8152866242038</v>
@@ -6421,13 +6424,13 @@
         <v>53</v>
       </c>
       <c r="E171" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F171" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G171" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H171">
         <v>8.1</v>
@@ -6439,10 +6442,10 @@
     </row>
     <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C172">
         <v>10.9554140127388</v>
@@ -6451,13 +6454,13 @@
         <v>59</v>
       </c>
       <c r="E172" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F172" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G172" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H172">
         <v>4</v>
@@ -6467,15 +6470,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J172" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173">
         <v>56.8152866242038</v>
@@ -6484,13 +6487,13 @@
         <v>60</v>
       </c>
       <c r="E173" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F173" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G173" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H173">
         <v>8.1</v>
@@ -6502,10 +6505,10 @@
     </row>
     <row r="174" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C174">
         <v>10.9554140127388</v>
@@ -6514,13 +6517,13 @@
         <v>61</v>
       </c>
       <c r="E174" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F174" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G174" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H174">
         <v>4</v>
@@ -6530,15 +6533,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J174" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C175">
         <v>10.191082802547699</v>
@@ -6547,13 +6550,13 @@
         <v>70</v>
       </c>
       <c r="E175" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F175" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G175" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H175">
         <v>8.1</v>
@@ -6565,10 +6568,10 @@
     </row>
     <row r="176" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C176">
         <v>56.8152866242038</v>
@@ -6577,13 +6580,13 @@
         <v>70</v>
       </c>
       <c r="E176" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F176" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G176" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H176">
         <v>8.1</v>
@@ -6595,10 +6598,10 @@
     </row>
     <row r="177" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C177">
         <v>10.191082802547699</v>
@@ -6607,13 +6610,13 @@
         <v>82</v>
       </c>
       <c r="E177" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F177" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G177" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H177">
         <v>5</v>
@@ -6623,15 +6626,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J177" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C178">
         <v>56.8152866242038</v>
@@ -6640,13 +6643,13 @@
         <v>84</v>
       </c>
       <c r="E178" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F178" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G178" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H178">
         <v>8.1</v>
@@ -6656,12 +6659,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C179">
         <v>56.8152866242038</v>
@@ -6670,13 +6673,13 @@
         <v>87</v>
       </c>
       <c r="E179" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F179" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G179" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H179">
         <v>8.1</v>
@@ -6688,10 +6691,10 @@
     </row>
     <row r="180" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C180">
         <v>10.191082802547699</v>
@@ -6700,13 +6703,13 @@
         <v>38</v>
       </c>
       <c r="E180" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F180" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G180" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H180">
         <v>5</v>
@@ -6716,15 +6719,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J180" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C181">
         <v>56.8152866242038</v>
@@ -6733,13 +6736,13 @@
         <v>38</v>
       </c>
       <c r="E181" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F181" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G181" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H181">
         <v>4</v>
@@ -6749,15 +6752,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J181" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C182">
         <v>18.2165605095541</v>
@@ -6766,13 +6769,13 @@
         <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F182" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G182" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H182">
         <v>8.1999999999999993</v>
@@ -6784,10 +6787,10 @@
     </row>
     <row r="183" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C183">
         <v>56.8152866242038</v>
@@ -6796,13 +6799,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F183" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G183" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H183">
         <v>8.1</v>
@@ -6814,10 +6817,10 @@
     </row>
     <row r="184" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C184">
         <v>56.8152866242038</v>
@@ -6826,13 +6829,13 @@
         <v>53</v>
       </c>
       <c r="E184" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F184" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G184" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H184">
         <v>8.1</v>
@@ -6844,10 +6847,10 @@
     </row>
     <row r="185" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C185">
         <v>10.9554140127388</v>
@@ -6856,13 +6859,13 @@
         <v>59</v>
       </c>
       <c r="E185" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F185" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G185" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H185">
         <v>4</v>
@@ -6872,15 +6875,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J185" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C186">
         <v>56.8152866242038</v>
@@ -6889,13 +6892,13 @@
         <v>60</v>
       </c>
       <c r="E186" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F186" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G186" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H186">
         <v>8.1</v>
@@ -6907,10 +6910,10 @@
     </row>
     <row r="187" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C187">
         <v>56.8152866242038</v>
@@ -6919,13 +6922,13 @@
         <v>70</v>
       </c>
       <c r="E187" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F187" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G187" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H187">
         <v>4</v>
@@ -6935,15 +6938,15 @@
         <v>AI model likely incorrect</v>
       </c>
       <c r="J187" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C188">
         <v>56.8152866242038</v>
@@ -6952,13 +6955,13 @@
         <v>84</v>
       </c>
       <c r="E188" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F188" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G188" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H188">
         <v>8.1</v>
@@ -6970,10 +6973,10 @@
     </row>
     <row r="189" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C189">
         <v>56.8152866242038</v>
@@ -6982,13 +6985,13 @@
         <v>87</v>
       </c>
       <c r="E189" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F189" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G189" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H189">
         <v>8.1</v>
@@ -6998,12 +7001,12 @@
         <v>In FU, labeler only includes relative while AI model adds other categories</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C190">
         <v>59.036144578313198</v>
@@ -7012,13 +7015,13 @@
         <v>22</v>
       </c>
       <c r="E190" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F190" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G190" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H190">
         <v>3.1</v>
@@ -7028,12 +7031,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C191">
         <v>59.036144578313198</v>
@@ -7042,13 +7045,13 @@
         <v>23</v>
       </c>
       <c r="E191" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F191" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G191" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H191">
         <v>3.1</v>
@@ -7058,12 +7061,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C192">
         <v>24.337349397590302</v>
@@ -7072,13 +7075,13 @@
         <v>68</v>
       </c>
       <c r="E192" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F192" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G192" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H192">
         <v>3.1</v>
@@ -7088,12 +7091,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C193">
         <v>24.337349397590302</v>
@@ -7102,13 +7105,13 @@
         <v>68</v>
       </c>
       <c r="E193" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F193" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G193" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H193">
         <v>3.1</v>
@@ -7118,12 +7121,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C194">
         <v>54.337349397590302</v>
@@ -7132,13 +7135,13 @@
         <v>68</v>
       </c>
       <c r="E194" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F194" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G194" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H194">
         <v>3.2</v>
@@ -7148,12 +7151,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C195">
         <v>21.019108280254699</v>
@@ -7162,13 +7165,13 @@
         <v>70</v>
       </c>
       <c r="E195" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F195" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G195" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H195">
         <v>3.1</v>
@@ -7178,12 +7181,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C196">
         <v>72.409638554216798</v>
@@ -7192,13 +7195,13 @@
         <v>73</v>
       </c>
       <c r="E196" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F196" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G196" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H196">
         <v>3.1</v>
@@ -7208,12 +7211,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C197">
         <v>72.409638554216798</v>
@@ -7222,13 +7225,13 @@
         <v>48</v>
       </c>
       <c r="E197" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F197" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G197" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H197">
         <v>3.1</v>
@@ -7238,12 +7241,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C198">
         <v>87.388535031847098</v>
@@ -7252,13 +7255,13 @@
         <v>74</v>
       </c>
       <c r="E198" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F198" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G198" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H198">
         <v>3.1</v>
@@ -7268,12 +7271,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C199">
         <v>87.388535031847098</v>
@@ -7282,13 +7285,13 @@
         <v>74</v>
       </c>
       <c r="E199" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F199" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G199" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H199">
         <v>3.1</v>
@@ -7298,12 +7301,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C200">
         <v>27.349397590361399</v>
@@ -7312,13 +7315,13 @@
         <v>79</v>
       </c>
       <c r="E200" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F200" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G200" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H200">
         <v>3.2</v>
@@ -7328,12 +7331,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C201">
         <v>53.855421686746901</v>
@@ -7342,13 +7345,13 @@
         <v>79</v>
       </c>
       <c r="E201" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F201" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G201" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H201">
         <v>3.2</v>
@@ -7358,12 +7361,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C202">
         <v>53.855421686746901</v>
@@ -7372,13 +7375,13 @@
         <v>79</v>
       </c>
       <c r="E202" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F202" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G202" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H202">
         <v>3.2</v>
@@ -7388,12 +7391,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C203">
         <v>59.036144578313198</v>
@@ -7402,13 +7405,13 @@
         <v>79</v>
       </c>
       <c r="E203" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F203" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G203" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H203">
         <v>3.1</v>
@@ -7418,12 +7421,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B204" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C204">
         <v>73.493975903614398</v>
@@ -7432,13 +7435,13 @@
         <v>46</v>
       </c>
       <c r="E204" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F204" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G204" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H204">
         <v>7</v>
@@ -7448,15 +7451,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J204" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C205">
         <v>73.493975903614398</v>
@@ -7465,13 +7468,13 @@
         <v>46</v>
       </c>
       <c r="E205" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F205" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G205" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H205">
         <v>2.2000000000000002</v>
@@ -7481,15 +7484,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J205" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B206" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C206">
         <v>73.493975903614398</v>
@@ -7498,13 +7501,13 @@
         <v>48</v>
       </c>
       <c r="E206" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F206" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G206" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H206">
         <v>2.2000000000000002</v>
@@ -7514,12 +7517,12 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C207">
         <v>73.493975903614398</v>
@@ -7528,13 +7531,13 @@
         <v>60</v>
       </c>
       <c r="E207" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F207" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G207" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H207">
         <v>2.2000000000000002</v>
@@ -7544,15 +7547,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J207" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B208" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C208">
         <v>73.493975903614398</v>
@@ -7561,13 +7564,13 @@
         <v>60</v>
       </c>
       <c r="E208" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F208" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G208" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H208">
         <v>2.2000000000000002</v>
@@ -7577,12 +7580,12 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B209" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C209">
         <v>73.493975903614398</v>
@@ -7591,13 +7594,13 @@
         <v>69</v>
       </c>
       <c r="E209" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F209" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G209" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H209">
         <v>7</v>
@@ -7607,15 +7610,15 @@
         <v>RAG Added Misinformation</v>
       </c>
       <c r="J209" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C210">
         <v>73.493975903614398</v>
@@ -7624,13 +7627,13 @@
         <v>68</v>
       </c>
       <c r="E210" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F210" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G210" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H210">
         <v>2.2000000000000002</v>
@@ -7640,15 +7643,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J210" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C211">
         <v>73.493975903614398</v>
@@ -7657,13 +7660,13 @@
         <v>73</v>
       </c>
       <c r="E211" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F211" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G211" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H211">
         <v>2.2000000000000002</v>
@@ -7673,15 +7676,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J211" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C212">
         <v>73.493975903614398</v>
@@ -7690,13 +7693,13 @@
         <v>74</v>
       </c>
       <c r="E212" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F212" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G212" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H212">
         <v>2.2000000000000002</v>
@@ -7706,15 +7709,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J212" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C213">
         <v>73.493975903614398</v>
@@ -7723,13 +7726,13 @@
         <v>95</v>
       </c>
       <c r="E213" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F213" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G213" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H213">
         <v>2.2000000000000002</v>
@@ -7739,15 +7742,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J213" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C214">
         <v>73.493975903614398</v>
@@ -7756,13 +7759,13 @@
         <v>100</v>
       </c>
       <c r="E214" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F214" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G214" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H214">
         <v>2.2000000000000002</v>
@@ -7772,15 +7775,15 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
       <c r="J214" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C215">
         <v>73.493975903614398</v>
@@ -7789,13 +7792,13 @@
         <v>73</v>
       </c>
       <c r="E215" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F215" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G215" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H215">
         <v>2.2000000000000002</v>
@@ -7805,12 +7808,12 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B216" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C216">
         <v>73.493975903614398</v>
@@ -7819,13 +7822,13 @@
         <v>74</v>
       </c>
       <c r="E216" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F216" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G216" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H216">
         <v>2.2000000000000002</v>
@@ -7835,12 +7838,12 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B217" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C217">
         <v>73.493975903614398</v>
@@ -7849,13 +7852,13 @@
         <v>95</v>
       </c>
       <c r="E217" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F217" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G217" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H217">
         <v>2.2000000000000002</v>
@@ -7865,12 +7868,12 @@
         <v>In Allocation, chose economic when the humans chose a more specific label</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C218">
         <v>59.036144578313198</v>
@@ -7879,13 +7882,13 @@
         <v>79</v>
       </c>
       <c r="E218" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F218" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G218" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H218">
         <v>3.1</v>
@@ -7895,12 +7898,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C219">
         <v>54.337349397590302</v>
@@ -7909,13 +7912,13 @@
         <v>84</v>
       </c>
       <c r="E219" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F219" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G219" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H219">
         <v>3.1</v>
@@ -7925,12 +7928,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C220">
         <v>54.337349397590302</v>
@@ -7939,13 +7942,13 @@
         <v>84</v>
       </c>
       <c r="E220" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F220" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G220" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H220">
         <v>3.1</v>
@@ -7955,12 +7958,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C221">
         <v>53.855421686746901</v>
@@ -7969,13 +7972,13 @@
         <v>89</v>
       </c>
       <c r="E221" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F221" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H221">
         <v>3.1</v>
@@ -7985,12 +7988,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C222">
         <v>53.855421686746901</v>
@@ -7999,13 +8002,13 @@
         <v>89</v>
       </c>
       <c r="E222" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F222" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G222" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H222">
         <v>3.1</v>
@@ -8015,12 +8018,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C223">
         <v>27.349397590361399</v>
@@ -8029,13 +8032,13 @@
         <v>95</v>
       </c>
       <c r="E223" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F223" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G223" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H223">
         <v>3.2</v>
@@ -8045,12 +8048,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C224">
         <v>27.349397590361399</v>
@@ -8059,13 +8062,13 @@
         <v>95</v>
       </c>
       <c r="E224" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F224" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G224" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H224">
         <v>3.2</v>
@@ -8075,12 +8078,12 @@
         <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C225">
         <v>25.2229299363057</v>
@@ -8089,13 +8092,13 @@
         <v>98</v>
       </c>
       <c r="E225" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F225" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G225" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H225">
         <v>3.1</v>
@@ -8105,12 +8108,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C226">
         <v>73.375796178343904</v>
@@ -8119,13 +8122,13 @@
         <v>98</v>
       </c>
       <c r="E226" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F226" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G226" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H226">
         <v>3.1</v>
@@ -8135,12 +8138,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C227">
         <v>73.375796178343904</v>
@@ -8149,13 +8152,13 @@
         <v>98</v>
       </c>
       <c r="E227" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F227" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G227" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H227">
         <v>3.1</v>
@@ -8165,12 +8168,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C228">
         <v>38.313253012048101</v>
@@ -8179,13 +8182,13 @@
         <v>101</v>
       </c>
       <c r="E228" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F228" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G228" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H228">
         <v>3.1</v>
@@ -8195,12 +8198,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C229">
         <v>53.855421686746901</v>
@@ -8209,13 +8212,13 @@
         <v>101</v>
       </c>
       <c r="E229" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F229" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G229" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H229">
         <v>3.1</v>
@@ -8225,12 +8228,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C230">
         <v>53.855421686746901</v>
@@ -8239,13 +8242,13 @@
         <v>101</v>
       </c>
       <c r="E230" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F230" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G230" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H230">
         <v>3.1</v>
@@ -8255,12 +8258,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C231">
         <v>54.337349397590302</v>
@@ -8269,13 +8272,13 @@
         <v>101</v>
       </c>
       <c r="E231" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F231" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G231" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H231">
         <v>3.1</v>
@@ -8285,12 +8288,12 @@
         <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C232">
         <v>90.722891566265005</v>
@@ -8299,13 +8302,13 @@
         <v>40</v>
       </c>
       <c r="E232" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F232" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G232" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H232">
         <v>1.4</v>
@@ -8315,12 +8318,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C233">
         <v>90.722891566265005</v>
@@ -8329,13 +8332,13 @@
         <v>48</v>
       </c>
       <c r="E233" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F233" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G233" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H233">
         <v>1.4</v>
@@ -8345,12 +8348,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C234">
         <v>90.722891566265005</v>
@@ -8359,13 +8362,13 @@
         <v>89</v>
       </c>
       <c r="E234" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F234" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G234" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H234">
         <v>1.4</v>
@@ -8375,12 +8378,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C235">
         <v>90.722891566265005</v>
@@ -8389,13 +8392,13 @@
         <v>89</v>
       </c>
       <c r="E235" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F235" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G235" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H235">
         <v>1.4</v>
@@ -8405,12 +8408,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C236">
         <v>91.337579617834393</v>
@@ -8419,13 +8422,13 @@
         <v>38</v>
       </c>
       <c r="E236" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F236" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G236" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H236">
         <v>1.4</v>
@@ -8435,12 +8438,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C237">
         <v>91.337579617834393</v>
@@ -8449,13 +8452,13 @@
         <v>15</v>
       </c>
       <c r="E237" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F237" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G237" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H237">
         <v>1.4</v>
@@ -8465,12 +8468,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C238">
         <v>91.337579617834393</v>
@@ -8479,13 +8482,13 @@
         <v>20</v>
       </c>
       <c r="E238" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F238" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G238" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H238">
         <v>1.4</v>
@@ -8495,12 +8498,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C239">
         <v>91.337579617834393</v>
@@ -8509,13 +8512,13 @@
         <v>38</v>
       </c>
       <c r="E239" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F239" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G239" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H239">
         <v>1.4</v>
@@ -8525,12 +8528,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C240">
         <v>93.248407643312106</v>
@@ -8539,13 +8542,13 @@
         <v>37</v>
       </c>
       <c r="E240" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F240" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G240" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H240">
         <v>1.4</v>
@@ -8555,12 +8558,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C241">
         <v>93.248407643312106</v>
@@ -8569,13 +8572,13 @@
         <v>68</v>
       </c>
       <c r="E241" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F241" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G241" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H241">
         <v>1.4</v>
@@ -8585,12 +8588,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C242">
         <v>93.248407643312106</v>
@@ -8599,13 +8602,13 @@
         <v>68</v>
       </c>
       <c r="E242" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F242" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G242" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H242">
         <v>1.4</v>
@@ -8615,12 +8618,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C243">
         <v>93.248407643312106</v>
@@ -8629,13 +8632,13 @@
         <v>85</v>
       </c>
       <c r="E243" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F243" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G243" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H243">
         <v>1.4</v>
@@ -8645,9 +8648,9 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>5</v>
@@ -8659,13 +8662,13 @@
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F244" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G244" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H244">
         <v>1.4</v>
@@ -8675,9 +8678,9 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>5</v>
@@ -8689,13 +8692,13 @@
         <v>60</v>
       </c>
       <c r="E245" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F245" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G245" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H245">
         <v>1.4</v>
@@ -8705,9 +8708,9 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>5</v>
@@ -8719,13 +8722,13 @@
         <v>60</v>
       </c>
       <c r="E246" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F246" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G246" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H246">
         <v>1.4</v>
@@ -8735,12 +8738,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C247">
         <v>93.975903614457806</v>
@@ -8749,13 +8752,13 @@
         <v>23</v>
       </c>
       <c r="E247" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F247" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G247" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H247">
         <v>1.4</v>
@@ -8765,12 +8768,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C248">
         <v>93.975903614457806</v>
@@ -8779,13 +8782,13 @@
         <v>30</v>
       </c>
       <c r="E248" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F248" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G248" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H248">
         <v>1.4</v>
@@ -8795,12 +8798,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C249">
         <v>93.975903614457806</v>
@@ -8809,13 +8812,13 @@
         <v>95</v>
       </c>
       <c r="E249" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F249" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G249" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H249">
         <v>1.4</v>
@@ -8825,12 +8828,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C250">
         <v>93.975903614457806</v>
@@ -8839,13 +8842,13 @@
         <v>23</v>
       </c>
       <c r="E250" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F250" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G250" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H250">
         <v>1.4</v>
@@ -8855,12 +8858,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C251">
         <v>93.975903614457806</v>
@@ -8869,13 +8872,13 @@
         <v>30</v>
       </c>
       <c r="E251" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F251" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G251" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H251">
         <v>1.4</v>
@@ -8885,12 +8888,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C252">
         <v>93.975903614457806</v>
@@ -8899,13 +8902,13 @@
         <v>95</v>
       </c>
       <c r="E252" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F252" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G252" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H252">
         <v>1.4</v>
@@ -8915,12 +8918,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C253">
         <v>93.975903614457806</v>
@@ -8929,13 +8932,13 @@
         <v>103</v>
       </c>
       <c r="E253" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F253" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G253" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H253">
         <v>1.4</v>
@@ -8945,12 +8948,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C254">
         <v>94.578313253011999</v>
@@ -8959,13 +8962,13 @@
         <v>48</v>
       </c>
       <c r="E254" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F254" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G254" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H254">
         <v>1.4</v>
@@ -8975,12 +8978,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C255">
         <v>94.777070063694197</v>
@@ -8989,13 +8992,13 @@
         <v>38</v>
       </c>
       <c r="E255" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F255" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G255" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H255">
         <v>1.4</v>
@@ -9005,12 +9008,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C256">
         <v>94.777070063694197</v>
@@ -9019,13 +9022,13 @@
         <v>38</v>
       </c>
       <c r="E256" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F256" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G256" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H256">
         <v>1.4</v>
@@ -9035,12 +9038,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C257">
         <v>94.939759036144494</v>
@@ -9049,13 +9052,13 @@
         <v>48</v>
       </c>
       <c r="E257" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F257" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G257" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H257">
         <v>1.4</v>
@@ -9065,12 +9068,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C258">
         <v>94.939759036144494</v>
@@ -9079,13 +9082,13 @@
         <v>31</v>
       </c>
       <c r="E258" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F258" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G258" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H258">
         <v>1.4</v>
@@ -9095,12 +9098,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C259">
         <v>95.060240963855406</v>
@@ -9109,13 +9112,13 @@
         <v>73</v>
       </c>
       <c r="E259" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F259" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G259" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H259">
         <v>1.4</v>
@@ -9125,12 +9128,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C260">
         <v>95.060240963855406</v>
@@ -9139,13 +9142,13 @@
         <v>101</v>
       </c>
       <c r="E260" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F260" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G260" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H260">
         <v>1.4</v>
@@ -9155,12 +9158,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C261">
         <v>95.060240963855406</v>
@@ -9169,13 +9172,13 @@
         <v>73</v>
       </c>
       <c r="E261" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F261" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G261" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H261">
         <v>1.4</v>
@@ -9185,12 +9188,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C262">
         <v>95.060240963855406</v>
@@ -9199,13 +9202,13 @@
         <v>101</v>
       </c>
       <c r="E262" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F262" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G262" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H262">
         <v>1.4</v>
@@ -9217,10 +9220,10 @@
     </row>
     <row r="263" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C263">
         <v>54.4578313253012</v>
@@ -9229,13 +9232,13 @@
         <v>84</v>
       </c>
       <c r="E263" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F263" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G263" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H263">
         <v>8.1</v>
@@ -9247,10 +9250,10 @@
     </row>
     <row r="264" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C264">
         <v>10</v>
@@ -9259,13 +9262,13 @@
         <v>85</v>
       </c>
       <c r="E264" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F264" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G264" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H264">
         <v>5</v>
@@ -9275,15 +9278,15 @@
         <v>AI model has justifiable response</v>
       </c>
       <c r="J264" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C265">
         <v>16.867469879518001</v>
@@ -9292,13 +9295,13 @@
         <v>92</v>
       </c>
       <c r="E265" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F265" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G265" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H265">
         <v>8.1999999999999993</v>
@@ -9308,12 +9311,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C266">
         <v>16.867469879518001</v>
@@ -9322,13 +9325,13 @@
         <v>92</v>
       </c>
       <c r="E266" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F266" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G266" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H266">
         <v>8.1999999999999993</v>
@@ -9338,12 +9341,12 @@
         <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C267">
         <v>10</v>
@@ -9352,13 +9355,13 @@
         <v>95</v>
       </c>
       <c r="E267" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F267" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G267" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H267">
         <v>4</v>
@@ -9368,12 +9371,12 @@
         <v>AI model likely incorrect</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C268">
         <v>11.084337349397501</v>
@@ -9382,13 +9385,13 @@
         <v>95</v>
       </c>
       <c r="E268" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F268" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G268" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H268">
         <v>4</v>
@@ -9400,10 +9403,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C269">
         <v>96.050955414012705</v>
@@ -9412,13 +9415,13 @@
         <v>38</v>
       </c>
       <c r="E269" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F269" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G269" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H269">
         <v>1.4</v>
@@ -9428,12 +9431,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C270">
         <v>96.265060240963805</v>
@@ -9442,13 +9445,13 @@
         <v>53</v>
       </c>
       <c r="E270" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F270" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G270" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H270">
         <v>1.4</v>
@@ -9458,12 +9461,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C271">
         <v>96.265060240963805</v>
@@ -9472,13 +9475,13 @@
         <v>73</v>
       </c>
       <c r="E271" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F271" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G271" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H271">
         <v>1.4</v>
@@ -9488,12 +9491,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C272">
         <v>96.265060240963805</v>
@@ -9502,13 +9505,13 @@
         <v>78</v>
       </c>
       <c r="E272" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F272" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G272" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H272">
         <v>1.4</v>
@@ -9518,12 +9521,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C273">
         <v>96.265060240963805</v>
@@ -9532,13 +9535,13 @@
         <v>53</v>
       </c>
       <c r="E273" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F273" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G273" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H273">
         <v>1.4</v>
@@ -9548,12 +9551,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C274">
         <v>96.942675159235606</v>
@@ -9562,13 +9565,13 @@
         <v>38</v>
       </c>
       <c r="E274" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F274" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G274" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H274">
         <v>1.4</v>
@@ -9578,12 +9581,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C275">
         <v>96.942675159235606</v>
@@ -9592,13 +9595,13 @@
         <v>38</v>
       </c>
       <c r="E275" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F275" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G275" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H275">
         <v>1.4</v>
@@ -9608,12 +9611,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C276">
         <v>99.235668789808898</v>
@@ -9622,13 +9625,13 @@
         <v>58</v>
       </c>
       <c r="E276" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F276" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G276" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H276">
         <v>1.4</v>
@@ -9638,12 +9641,12 @@
         <v>Label occurs &gt;90% of the time in training samples</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C277">
         <v>99.235668789808898</v>
@@ -9652,13 +9655,13 @@
         <v>58</v>
       </c>
       <c r="E277" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F277" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G277" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H277">
         <v>1.4</v>
@@ -9685,10 +9688,10 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -9696,10 +9699,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -9707,10 +9710,10 @@
         <v>1.2</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -9718,10 +9721,10 @@
         <v>1.3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -9729,10 +9732,10 @@
         <v>1.4</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -9740,7 +9743,7 @@
         <v>2.1</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -9748,7 +9751,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -9756,7 +9759,7 @@
         <v>3.1</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -9764,7 +9767,7 @@
         <v>3.2</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -9772,7 +9775,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -9780,7 +9783,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -9788,7 +9791,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -9796,7 +9799,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -9804,7 +9807,7 @@
         <v>8.1</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -9812,7 +9815,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -9820,7 +9823,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
+++ b/data/qa_dataset/results/All_Discrepancies_Coded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\llm-goal-scope\data\qa_dataset\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31874166-D90D-4F06-8432-B9048E6B6561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86734B9E-6AAA-420F-ABE4-E4D5C84CFB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Errors" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Errors'!$A$1:$J$277</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Encoding Errors'!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="295">
   <si>
     <t>Sentence</t>
   </si>
@@ -237,9 +238,6 @@
     <t>ML model predicted energy but the humans predicted No energy.</t>
   </si>
   <si>
-    <t>Table of Rationale</t>
-  </si>
-  <si>
     <t>Label not in training data</t>
   </si>
   <si>
@@ -723,12 +721,6 @@
     <t>Discrepancy between cold carcass weight/head and liveweight/head</t>
   </si>
   <si>
-    <t>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</t>
-  </si>
-  <si>
-    <t>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</t>
-  </si>
-  <si>
     <t>Difference between none and none required</t>
   </si>
   <si>
@@ -738,9 +730,6 @@
     <t>Model predicts both economic and no allocation at the same time</t>
   </si>
   <si>
-    <t>Human authors/labelers appear to have made a mistake</t>
-  </si>
-  <si>
     <t>Unclear why model predicts Fat and Protein Corrected Milk has an economic allocation instead of biophysical</t>
   </si>
   <si>
@@ -753,12 +742,6 @@
     <t>Model wants economic allocation when humans want none for chicken production</t>
   </si>
   <si>
-    <t>In Allocation, confused none with none required</t>
-  </si>
-  <si>
-    <t>In Allocation, chose economic when the humans chose a more specific label</t>
-  </si>
-  <si>
     <t>Notes (4, 5, 7, 9)</t>
   </si>
   <si>
@@ -798,12 +781,6 @@
     <t>Milk processes are commonly encoded as % in Hestia, but not always.</t>
   </si>
   <si>
-    <t>In FU, labeler only includes relative while AI model adds other categories</t>
-  </si>
-  <si>
-    <t>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</t>
-  </si>
-  <si>
     <t>Unclear why labeler included days</t>
   </si>
   <si>
@@ -880,6 +857,75 @@
   </si>
   <si>
     <t>Standardized</t>
+  </si>
+  <si>
+    <t>Old Code</t>
+  </si>
+  <si>
+    <t>New Code</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>A.1</t>
+  </si>
+  <si>
+    <t>A.2</t>
+  </si>
+  <si>
+    <t>A.3</t>
+  </si>
+  <si>
+    <t>B.1</t>
+  </si>
+  <si>
+    <t>C.1</t>
+  </si>
+  <si>
+    <t>E.1</t>
+  </si>
+  <si>
+    <t>In the Allocation task, chose economic when the humans chose a more specific label</t>
+  </si>
+  <si>
+    <t>In the Allocation task, confused none with none required</t>
+  </si>
+  <si>
+    <t>C.2</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>In the Functional Unit task, labeler only includes relative while AI model adds other categories</t>
+  </si>
+  <si>
+    <t>In the System Boundary task, the labeler of the study did not report an item the AI model wants to consider</t>
+  </si>
+  <si>
+    <t>In the System Boundary task, the AI model does not want to report an item the labeler of the study did report</t>
+  </si>
+  <si>
+    <t>F.1</t>
+  </si>
+  <si>
+    <t>F.2</t>
+  </si>
+  <si>
+    <t>In the Functional Unit task, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</t>
+  </si>
+  <si>
+    <t>G.1</t>
+  </si>
+  <si>
+    <t>G.2</t>
+  </si>
+  <si>
+    <t>C.3</t>
+  </si>
+  <si>
+    <t>C.4</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1262,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1234,21 +1280,21 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" t="s">
         <v>72</v>
       </c>
-      <c r="I1" t="s">
-        <v>73</v>
-      </c>
       <c r="J1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
@@ -1260,25 +1306,25 @@
         <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H2">
         <v>1.1000000000000001</v>
       </c>
       <c r="I2" t="str">
-        <f>VLOOKUP(H2,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H2,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -1290,25 +1336,25 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H3">
         <v>1.1000000000000001</v>
       </c>
       <c r="I3" t="str">
-        <f>VLOOKUP(H3,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H3,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -1320,25 +1366,25 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H4">
         <v>1.1000000000000001</v>
       </c>
       <c r="I4" t="str">
-        <f>VLOOKUP(H4,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H4,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -1350,25 +1396,25 @@
         <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G5" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H5">
         <v>1.1000000000000001</v>
       </c>
       <c r="I5" t="str">
-        <f>VLOOKUP(H5,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H5,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -1380,25 +1426,25 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G6" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H6">
         <v>1.1000000000000001</v>
       </c>
       <c r="I6" t="str">
-        <f>VLOOKUP(H6,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H6,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -1410,25 +1456,25 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F7" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G7" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H7">
         <v>1.1000000000000001</v>
       </c>
       <c r="I7" t="str">
-        <f>VLOOKUP(H7,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H7,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -1440,25 +1486,25 @@
         <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G8" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H8">
         <v>1.1000000000000001</v>
       </c>
       <c r="I8" t="str">
-        <f>VLOOKUP(H8,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H8,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
@@ -1470,25 +1516,25 @@
         <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H9">
         <v>1.1000000000000001</v>
       </c>
       <c r="I9" t="str">
-        <f>VLOOKUP(H9,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H9,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
@@ -1500,25 +1546,25 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F10" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G10" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H10">
         <v>1.1000000000000001</v>
       </c>
       <c r="I10" t="str">
-        <f>VLOOKUP(H10,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H10,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>35</v>
@@ -1530,25 +1576,25 @@
         <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F11" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H11">
         <v>1.1000000000000001</v>
       </c>
       <c r="I11" t="str">
-        <f>VLOOKUP(H11,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H11,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>38</v>
@@ -1560,25 +1606,25 @@
         <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H12">
         <v>1.1000000000000001</v>
       </c>
       <c r="I12" t="str">
-        <f>VLOOKUP(H12,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H12,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>41</v>
@@ -1590,25 +1636,25 @@
         <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F13" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G13" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H13">
         <v>1.1000000000000001</v>
       </c>
       <c r="I13" t="str">
-        <f>VLOOKUP(H13,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H13,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>43</v>
@@ -1620,25 +1666,25 @@
         <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G14" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H14">
         <v>1.1000000000000001</v>
       </c>
       <c r="I14" t="str">
-        <f>VLOOKUP(H14,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H14,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>43</v>
@@ -1650,25 +1696,25 @@
         <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H15">
         <v>1.1000000000000001</v>
       </c>
       <c r="I15" t="str">
-        <f>VLOOKUP(H15,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H15,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>52</v>
@@ -1680,25 +1726,25 @@
         <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F16" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G16" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H16">
         <v>1.1000000000000001</v>
       </c>
       <c r="I16" t="str">
-        <f>VLOOKUP(H16,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H16,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>53</v>
@@ -1710,25 +1756,25 @@
         <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F17" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G17" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H17">
         <v>1.1000000000000001</v>
       </c>
       <c r="I17" t="str">
-        <f>VLOOKUP(H17,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H17,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>53</v>
@@ -1740,25 +1786,25 @@
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F18" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G18" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H18">
         <v>1.1000000000000001</v>
       </c>
       <c r="I18" t="str">
-        <f>VLOOKUP(H18,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H18,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>52</v>
@@ -1770,25 +1816,25 @@
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F19" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G19" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H19">
         <v>1.1000000000000001</v>
       </c>
       <c r="I19" t="str">
-        <f>VLOOKUP(H19,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label not in training data</v>
+        <f>VLOOKUP(H19,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.1</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
         <v>64</v>
@@ -1800,25 +1846,25 @@
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G20" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H20">
         <v>1.2</v>
       </c>
       <c r="I20" t="str">
-        <f>VLOOKUP(H20,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H20,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
@@ -1830,25 +1876,25 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F21" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G21" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H21">
         <v>1.2</v>
       </c>
       <c r="I21" t="str">
-        <f>VLOOKUP(H21,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H21,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
@@ -1860,25 +1906,25 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F22" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G22" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H22">
         <v>1.2</v>
       </c>
       <c r="I22" t="str">
-        <f>VLOOKUP(H22,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H22,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>60</v>
@@ -1890,25 +1936,25 @@
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G23" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H23">
         <v>1.2</v>
       </c>
       <c r="I23" t="str">
-        <f>VLOOKUP(H23,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H23,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>42</v>
@@ -1920,25 +1966,25 @@
         <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F24" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G24" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H24">
         <v>1.2</v>
       </c>
       <c r="I24" t="str">
-        <f>VLOOKUP(H24,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H24,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>42</v>
@@ -1950,25 +1996,25 @@
         <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F25" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G25" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H25">
         <v>1.2</v>
       </c>
       <c r="I25" t="str">
-        <f>VLOOKUP(H25,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H25,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>59</v>
@@ -1980,25 +2026,25 @@
         <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G26" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H26">
         <v>1.2</v>
       </c>
       <c r="I26" t="str">
-        <f>VLOOKUP(H26,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H26,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -2010,25 +2056,25 @@
         <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F27" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G27" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H27">
         <v>1.2</v>
       </c>
       <c r="I27" t="str">
-        <f>VLOOKUP(H27,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H27,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -2040,25 +2086,25 @@
         <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F28" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G28" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H28">
         <v>1.2</v>
       </c>
       <c r="I28" t="str">
-        <f>VLOOKUP(H28,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H28,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>36</v>
@@ -2070,25 +2116,25 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F29" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G29" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H29">
         <v>1.2</v>
       </c>
       <c r="I29" t="str">
-        <f>VLOOKUP(H29,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H29,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
@@ -2100,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F30" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G30" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H30">
         <v>8.1</v>
       </c>
       <c r="I30" t="str">
-        <f>VLOOKUP(H30,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H30,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
       <c r="J30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2133,25 +2179,25 @@
         <v>79</v>
       </c>
       <c r="E31" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F31" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G31" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H31">
         <v>1.2</v>
       </c>
       <c r="I31" t="str">
-        <f>VLOOKUP(H31,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H31,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>37</v>
@@ -2163,25 +2209,25 @@
         <v>79</v>
       </c>
       <c r="E32" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F32" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G32" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H32">
         <v>1.2</v>
       </c>
       <c r="I32" t="str">
-        <f>VLOOKUP(H32,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H32,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2193,25 +2239,25 @@
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F33" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H33">
         <v>1.2</v>
       </c>
       <c r="I33" t="str">
-        <f>VLOOKUP(H33,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H33,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2223,25 +2269,25 @@
         <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F34" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G34" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H34">
         <v>1.2</v>
       </c>
       <c r="I34" t="str">
-        <f>VLOOKUP(H34,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H34,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>17</v>
@@ -2253,25 +2299,25 @@
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F35" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G35" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H35">
         <v>1.2</v>
       </c>
       <c r="I35" t="str">
-        <f>VLOOKUP(H35,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H35,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
         <v>63</v>
@@ -2283,25 +2329,25 @@
         <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F36" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G36" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H36">
         <v>1.2</v>
       </c>
       <c r="I36" t="str">
-        <f>VLOOKUP(H36,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H36,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>17</v>
@@ -2313,25 +2359,25 @@
         <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F37" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G37" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H37">
         <v>1.2</v>
       </c>
       <c r="I37" t="str">
-        <f>VLOOKUP(H37,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H37,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -2343,25 +2389,25 @@
         <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F38" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G38" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H38">
         <v>1.2</v>
       </c>
       <c r="I38" t="str">
-        <f>VLOOKUP(H38,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H38,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2373,25 +2419,25 @@
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F39" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G39" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H39">
         <v>1.2</v>
       </c>
       <c r="I39" t="str">
-        <f>VLOOKUP(H39,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H39,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
@@ -2403,28 +2449,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F40" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G40" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H40">
         <v>8.1</v>
       </c>
       <c r="I40" t="str">
-        <f>VLOOKUP(H40,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H40,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
       <c r="J40" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -2436,28 +2482,28 @@
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F41" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G41" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H41">
         <v>8.1999999999999993</v>
       </c>
       <c r="I41" t="str">
-        <f>VLOOKUP(H41,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H41,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
       <c r="J41" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -2469,28 +2515,28 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F42" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G42" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H42">
         <v>8.1999999999999993</v>
       </c>
       <c r="I42" t="str">
-        <f>VLOOKUP(H42,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H42,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
       <c r="J42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>12</v>
@@ -2502,25 +2548,25 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F43" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G43" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H43">
         <v>1.4</v>
       </c>
       <c r="I43" t="str">
-        <f>VLOOKUP(H43,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H43,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>49</v>
@@ -2532,25 +2578,25 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F44" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G44" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H44">
         <v>1.2</v>
       </c>
       <c r="I44" t="str">
-        <f>VLOOKUP(H44,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H44,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>49</v>
@@ -2562,25 +2608,25 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F45" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G45" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H45">
         <v>1.2</v>
       </c>
       <c r="I45" t="str">
-        <f>VLOOKUP(H45,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H45,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>49</v>
@@ -2592,25 +2638,25 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F46" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G46" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H46">
         <v>1.2</v>
       </c>
       <c r="I46" t="str">
-        <f>VLOOKUP(H46,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H46,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
@@ -2622,25 +2668,25 @@
         <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F47" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G47" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H47">
         <v>1.2</v>
       </c>
       <c r="I47" t="str">
-        <f>VLOOKUP(H47,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H47,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>21</v>
@@ -2652,25 +2698,25 @@
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G48" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H48">
         <v>1.3</v>
       </c>
       <c r="I48" t="str">
-        <f>VLOOKUP(H48,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H48,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -2682,25 +2728,25 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F49" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G49" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H49">
         <v>1.3</v>
       </c>
       <c r="I49" t="str">
-        <f>VLOOKUP(H49,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H49,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>21</v>
@@ -2712,25 +2758,25 @@
         <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F50" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G50" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H50">
         <v>1.3</v>
       </c>
       <c r="I50" t="str">
-        <f>VLOOKUP(H50,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H50,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>21</v>
@@ -2742,25 +2788,25 @@
         <v>79</v>
       </c>
       <c r="E51" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F51" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G51" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H51">
         <v>1.3</v>
       </c>
       <c r="I51" t="str">
-        <f>VLOOKUP(H51,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H51,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>21</v>
@@ -2772,25 +2818,25 @@
         <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F52" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G52" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H52">
         <v>1.3</v>
       </c>
       <c r="I52" t="str">
-        <f>VLOOKUP(H52,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H52,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>21</v>
@@ -2802,25 +2848,25 @@
         <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F53" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G53" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H53">
         <v>1.3</v>
       </c>
       <c r="I53" t="str">
-        <f>VLOOKUP(H53,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H53,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
         <v>51</v>
@@ -2832,25 +2878,25 @@
         <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F54" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G54" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H54">
         <v>1.3</v>
       </c>
       <c r="I54" t="str">
-        <f>VLOOKUP(H54,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H54,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
         <v>51</v>
@@ -2862,25 +2908,25 @@
         <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F55" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G55" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H55">
         <v>1.3</v>
       </c>
       <c r="I55" t="str">
-        <f>VLOOKUP(H55,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H55,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>56</v>
@@ -2892,25 +2938,25 @@
         <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F56" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G56" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H56">
         <v>1.3</v>
       </c>
       <c r="I56" t="str">
-        <f>VLOOKUP(H56,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H56,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
@@ -2922,25 +2968,25 @@
         <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F57" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G57" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H57">
         <v>1.3</v>
       </c>
       <c r="I57" t="str">
-        <f>VLOOKUP(H57,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H57,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>23</v>
@@ -2952,25 +2998,25 @@
         <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F58" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G58" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H58">
         <v>1.3</v>
       </c>
       <c r="I58" t="str">
-        <f>VLOOKUP(H58,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H58,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -2982,25 +3028,25 @@
         <v>93</v>
       </c>
       <c r="E59" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F59" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G59" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H59">
         <v>1.3</v>
       </c>
       <c r="I59" t="str">
-        <f>VLOOKUP(H59,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H59,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>23</v>
@@ -3012,25 +3058,25 @@
         <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F60" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G60" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H60">
         <v>1.3</v>
       </c>
       <c r="I60" t="str">
-        <f>VLOOKUP(H60,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H60,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -3042,25 +3088,25 @@
         <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F61" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G61" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H61">
         <v>1.3</v>
       </c>
       <c r="I61" t="str">
-        <f>VLOOKUP(H61,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H61,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>23</v>
@@ -3072,25 +3118,25 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F62" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G62" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H62">
         <v>1.3</v>
       </c>
       <c r="I62" t="str">
-        <f>VLOOKUP(H62,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H62,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="300" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s">
         <v>19</v>
@@ -3102,25 +3148,25 @@
         <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F63" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G63" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H63">
         <v>1.3</v>
       </c>
       <c r="I63" t="str">
-        <f>VLOOKUP(H63,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H63,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>19</v>
@@ -3132,25 +3178,25 @@
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F64" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G64" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H64">
         <v>1.3</v>
       </c>
       <c r="I64" t="str">
-        <f>VLOOKUP(H64,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H64,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
         <v>44</v>
@@ -3162,25 +3208,25 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F65" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G65" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H65">
         <v>1.3</v>
       </c>
       <c r="I65" t="str">
-        <f>VLOOKUP(H65,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H65,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>44</v>
@@ -3192,25 +3238,25 @@
         <v>84</v>
       </c>
       <c r="E66" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F66" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G66" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H66">
         <v>1.3</v>
       </c>
       <c r="I66" t="str">
-        <f>VLOOKUP(H66,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H66,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>23</v>
@@ -3222,25 +3268,25 @@
         <v>53</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F67" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G67" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H67">
         <v>1.3</v>
       </c>
       <c r="I67" t="str">
-        <f>VLOOKUP(H67,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H67,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>28</v>
@@ -3252,25 +3298,25 @@
         <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F68" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G68" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H68">
         <v>1.3</v>
       </c>
       <c r="I68" t="str">
-        <f>VLOOKUP(H68,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H68,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>23</v>
@@ -3282,25 +3328,25 @@
         <v>70</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F69" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G69" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H69">
         <v>1.3</v>
       </c>
       <c r="I69" t="str">
-        <f>VLOOKUP(H69,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H69,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>23</v>
@@ -3312,25 +3358,25 @@
         <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F70" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G70" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H70">
         <v>1.3</v>
       </c>
       <c r="I70" t="str">
-        <f>VLOOKUP(H70,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H70,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>23</v>
@@ -3342,26 +3388,26 @@
         <v>58</v>
       </c>
       <c r="E71" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F71" t="str">
         <f>$F$7</f>
         <v>Standardized</v>
       </c>
       <c r="G71" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H71">
         <v>1.3</v>
       </c>
       <c r="I71" t="str">
-        <f>VLOOKUP(H71,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H71,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -3373,25 +3419,25 @@
         <v>59</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F72" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G72" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H72">
         <v>1.3</v>
       </c>
       <c r="I72" t="str">
-        <f>VLOOKUP(H72,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;10% of the time in training samples</v>
+        <f>VLOOKUP(H72,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.3</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>6</v>
@@ -3403,25 +3449,25 @@
         <v>25</v>
       </c>
       <c r="E73" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F73" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G73" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H73">
         <v>8.1</v>
       </c>
       <c r="I73" t="str">
-        <f>VLOOKUP(H73,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H73,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>14</v>
@@ -3433,25 +3479,25 @@
         <v>23</v>
       </c>
       <c r="E74" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F74" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G74" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H74">
         <v>4</v>
       </c>
       <c r="I74" t="str">
-        <f>VLOOKUP(H74,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H74,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -3463,25 +3509,25 @@
         <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F75" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G75" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H75">
         <v>1.4</v>
       </c>
       <c r="I75" t="str">
-        <f>VLOOKUP(H75,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H75,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>6</v>
@@ -3493,28 +3539,28 @@
         <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G76" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H76">
         <v>8.1</v>
       </c>
       <c r="I76" t="str">
-        <f>VLOOKUP(H76,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H76,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
       <c r="J76" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
@@ -3526,28 +3572,28 @@
         <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F77" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G77" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H77">
         <v>8.1999999999999993</v>
       </c>
       <c r="I77" t="str">
-        <f>VLOOKUP(H77,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H77,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
       <c r="J77" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>6</v>
@@ -3559,25 +3605,25 @@
         <v>41</v>
       </c>
       <c r="E78" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G78" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H78">
         <v>8.1</v>
       </c>
       <c r="I78" t="str">
-        <f>VLOOKUP(H78,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H78,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>25</v>
@@ -3589,25 +3635,25 @@
         <v>54</v>
       </c>
       <c r="E79" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F79" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G79" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H79">
         <v>1.2</v>
       </c>
       <c r="I79" t="str">
-        <f>VLOOKUP(H79,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H79,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>6</v>
@@ -3619,25 +3665,25 @@
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F80" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G80" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H80">
         <v>8.1</v>
       </c>
       <c r="I80" t="str">
-        <f>VLOOKUP(H80,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H80,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
@@ -3649,25 +3695,25 @@
         <v>33</v>
       </c>
       <c r="E81" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F81" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G81" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H81">
         <v>8.1999999999999993</v>
       </c>
       <c r="I81" t="str">
-        <f>VLOOKUP(H81,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H81,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>14</v>
@@ -3679,25 +3725,25 @@
         <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F82" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G82" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H82">
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f>VLOOKUP(H82,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H82,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>47</v>
@@ -3709,25 +3755,25 @@
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F83" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G83" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H83">
         <v>8.1999999999999993</v>
       </c>
       <c r="I83" t="str">
-        <f>VLOOKUP(H83,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H83,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>47</v>
@@ -3739,25 +3785,25 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F84" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G84" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H84">
         <v>8.1</v>
       </c>
       <c r="I84" t="str">
-        <f>VLOOKUP(H84,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H84,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>6</v>
@@ -3769,25 +3815,25 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F85" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G85" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H85">
         <v>8.1</v>
       </c>
       <c r="I85" t="str">
-        <f>VLOOKUP(H85,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H85,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>47</v>
@@ -3799,25 +3845,25 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F86" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G86" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H86">
         <v>8.1999999999999993</v>
       </c>
       <c r="I86" t="str">
-        <f>VLOOKUP(H86,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H86,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>6</v>
@@ -3829,28 +3875,28 @@
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F87" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G87" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H87">
         <v>8.1</v>
       </c>
       <c r="I87" t="str">
-        <f>VLOOKUP(H87,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H87,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
       <c r="J87" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>47</v>
@@ -3862,25 +3908,25 @@
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F88" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G88" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H88">
         <v>8.1</v>
       </c>
       <c r="I88" t="str">
-        <f>VLOOKUP(H88,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H88,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>6</v>
@@ -3892,25 +3938,25 @@
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F89" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G89" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H89">
         <v>8.1</v>
       </c>
       <c r="I89" t="str">
-        <f>VLOOKUP(H89,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H89,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>6</v>
@@ -3922,25 +3968,25 @@
         <v>31</v>
       </c>
       <c r="E90" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F90" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G90" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H90">
         <v>8.1</v>
       </c>
       <c r="I90" t="str">
-        <f>VLOOKUP(H90,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H90,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>6</v>
@@ -3952,25 +3998,25 @@
         <v>41</v>
       </c>
       <c r="E91" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F91" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G91" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H91">
         <v>8.1</v>
       </c>
       <c r="I91" t="str">
-        <f>VLOOKUP(H91,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H91,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>26</v>
@@ -3982,28 +4028,28 @@
         <v>54</v>
       </c>
       <c r="E92" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F92" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G92" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H92">
         <v>5</v>
       </c>
       <c r="I92" t="str">
-        <f>VLOOKUP(H92,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H92,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J92" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>12</v>
@@ -4015,25 +4061,25 @@
         <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F93" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G93" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H93">
         <v>1.4</v>
       </c>
       <c r="I93" t="str">
-        <f>VLOOKUP(H93,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H93,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>47</v>
@@ -4045,28 +4091,28 @@
         <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F94" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G94" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H94">
         <v>8.1999999999999993</v>
       </c>
       <c r="I94" t="str">
-        <f>VLOOKUP(H94,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H94,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
       <c r="J94" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>47</v>
@@ -4078,25 +4124,25 @@
         <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F95" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G95" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H95">
         <v>8.1</v>
       </c>
       <c r="I95" t="str">
-        <f>VLOOKUP(H95,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H95,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>6</v>
@@ -4108,25 +4154,25 @@
         <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F96" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G96" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H96">
         <v>8.1</v>
       </c>
       <c r="I96" t="str">
-        <f>VLOOKUP(H96,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H96,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>25</v>
@@ -4138,25 +4184,25 @@
         <v>54</v>
       </c>
       <c r="E97" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F97" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G97" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H97">
         <v>1.2</v>
       </c>
       <c r="I97" t="str">
-        <f>VLOOKUP(H97,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H97,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>26</v>
@@ -4168,28 +4214,28 @@
         <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F98" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G98" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H98">
         <v>5</v>
       </c>
       <c r="I98" t="str">
-        <f>VLOOKUP(H98,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H98,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J98" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>12</v>
@@ -4201,25 +4247,25 @@
         <v>54</v>
       </c>
       <c r="E99" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F99" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G99" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H99">
         <v>1.4</v>
       </c>
       <c r="I99" t="str">
-        <f>VLOOKUP(H99,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H99,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>6</v>
@@ -4231,25 +4277,25 @@
         <v>58</v>
       </c>
       <c r="E100" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F100" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G100" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H100">
         <v>8.1</v>
       </c>
       <c r="I100" t="str">
-        <f>VLOOKUP(H100,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H100,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" t="s">
         <v>39</v>
@@ -4261,25 +4307,25 @@
         <v>79</v>
       </c>
       <c r="E101" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F101" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G101" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H101">
         <v>4</v>
       </c>
       <c r="I101" t="str">
-        <f>VLOOKUP(H101,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H101,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>39</v>
@@ -4291,25 +4337,25 @@
         <v>79</v>
       </c>
       <c r="E102" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F102" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G102" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H102">
         <v>4</v>
       </c>
       <c r="I102" t="str">
-        <f>VLOOKUP(H102,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H102,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
@@ -4321,28 +4367,28 @@
         <v>41</v>
       </c>
       <c r="E103" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F103" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G103" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H103">
         <v>7</v>
       </c>
       <c r="I103" t="str">
-        <f>VLOOKUP(H103,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>RAG Added Misinformation</v>
+        <f>VLOOKUP(H103,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>G.1</v>
       </c>
       <c r="J103" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>15</v>
@@ -4354,28 +4400,28 @@
         <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F104" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G104" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H104">
         <v>2.1</v>
       </c>
       <c r="I104" t="str">
-        <f>VLOOKUP(H104,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, confused none with none required</v>
+        <f>VLOOKUP(H104,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.1</v>
       </c>
       <c r="J104" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>18</v>
@@ -4387,28 +4433,28 @@
         <v>48</v>
       </c>
       <c r="E105" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F105" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G105" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H105">
         <v>2.1</v>
       </c>
       <c r="I105" t="str">
-        <f>VLOOKUP(H105,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, confused none with none required</v>
+        <f>VLOOKUP(H105,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.1</v>
       </c>
       <c r="J105" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B106" t="s">
         <v>18</v>
@@ -4420,28 +4466,28 @@
         <v>48</v>
       </c>
       <c r="E106" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F106" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G106" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H106">
         <v>7</v>
       </c>
       <c r="I106" t="str">
-        <f>VLOOKUP(H106,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>RAG Added Misinformation</v>
+        <f>VLOOKUP(H106,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>G.1</v>
       </c>
       <c r="J106" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>18</v>
@@ -4453,28 +4499,28 @@
         <v>60</v>
       </c>
       <c r="E107" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F107" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G107" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H107">
         <v>2.2000000000000002</v>
       </c>
       <c r="I107" t="str">
-        <f>VLOOKUP(H107,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H107,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J107" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>15</v>
@@ -4486,28 +4532,28 @@
         <v>84</v>
       </c>
       <c r="E108" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F108" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G108" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H108">
         <v>2.1</v>
       </c>
       <c r="I108" t="str">
-        <f>VLOOKUP(H108,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, confused none with none required</v>
+        <f>VLOOKUP(H108,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.1</v>
       </c>
       <c r="J108" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>18</v>
@@ -4519,28 +4565,28 @@
         <v>95</v>
       </c>
       <c r="E109" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F109" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G109" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H109">
         <v>2.2000000000000002</v>
       </c>
       <c r="I109" t="str">
-        <f>VLOOKUP(H109,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H109,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J109" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>18</v>
@@ -4552,28 +4598,28 @@
         <v>100</v>
       </c>
       <c r="E110" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F110" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G110" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H110">
         <v>2.2000000000000002</v>
       </c>
       <c r="I110" t="str">
-        <f>VLOOKUP(H110,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H110,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J110" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -4585,25 +4631,25 @@
         <v>84</v>
       </c>
       <c r="E111" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F111" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H111">
         <v>2.1</v>
       </c>
       <c r="I111" t="str">
-        <f>VLOOKUP(H111,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, confused none with none required</v>
+        <f>VLOOKUP(H111,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.1</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
@@ -4615,25 +4661,25 @@
         <v>95</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F112" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G112" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H112">
         <v>2.2000000000000002</v>
       </c>
       <c r="I112" t="str">
-        <f>VLOOKUP(H112,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H112,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>30</v>
@@ -4645,28 +4691,28 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G113" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H113">
         <v>5</v>
       </c>
       <c r="I113" t="str">
-        <f>VLOOKUP(H113,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H113,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J113" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>26</v>
@@ -4678,28 +4724,28 @@
         <v>63</v>
       </c>
       <c r="E114" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F114" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G114" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H114">
         <v>4</v>
       </c>
       <c r="I114" t="str">
-        <f>VLOOKUP(H114,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H114,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J114" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
@@ -4711,25 +4757,25 @@
         <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F115" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G115" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H115">
         <v>8.1999999999999993</v>
       </c>
       <c r="I115" t="str">
-        <f>VLOOKUP(H115,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H115,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>30</v>
@@ -4741,28 +4787,28 @@
         <v>60</v>
       </c>
       <c r="E116" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F116" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G116" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H116">
         <v>5</v>
       </c>
       <c r="I116" t="str">
-        <f>VLOOKUP(H116,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H116,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J116" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>26</v>
@@ -4774,28 +4820,28 @@
         <v>63</v>
       </c>
       <c r="E117" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F117" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G117" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H117">
         <v>4</v>
       </c>
       <c r="I117" t="str">
-        <f>VLOOKUP(H117,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H117,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J117" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>7</v>
@@ -4807,25 +4853,25 @@
         <v>66</v>
       </c>
       <c r="E118" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F118" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G118" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H118">
         <v>8.1999999999999993</v>
       </c>
       <c r="I118" t="str">
-        <f>VLOOKUP(H118,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H118,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>14</v>
@@ -4837,25 +4883,25 @@
         <v>68</v>
       </c>
       <c r="E119" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F119" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G119" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H119">
         <v>4</v>
       </c>
       <c r="I119" t="str">
-        <f>VLOOKUP(H119,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H119,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>32</v>
@@ -4867,25 +4913,25 @@
         <v>68</v>
       </c>
       <c r="E120" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F120" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G120" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H120">
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <f>VLOOKUP(H120,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H120,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>26</v>
@@ -4897,28 +4943,28 @@
         <v>73</v>
       </c>
       <c r="E121" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F121" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G121" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H121">
         <v>5</v>
       </c>
       <c r="I121" t="str">
-        <f>VLOOKUP(H121,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H121,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J121" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>14</v>
@@ -4930,28 +4976,28 @@
         <v>68</v>
       </c>
       <c r="E122" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G122" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H122">
         <v>5</v>
       </c>
       <c r="I122" t="str">
-        <f>VLOOKUP(H122,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H122,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J122" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>6</v>
@@ -4963,25 +5009,25 @@
         <v>31</v>
       </c>
       <c r="E123" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F123" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G123" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H123">
         <v>8.1</v>
       </c>
       <c r="I123" t="str">
-        <f>VLOOKUP(H123,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H123,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
@@ -4993,25 +5039,25 @@
         <v>35</v>
       </c>
       <c r="E124" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F124" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G124" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H124">
         <v>8.1999999999999993</v>
       </c>
       <c r="I124" t="str">
-        <f>VLOOKUP(H124,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H124,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>6</v>
@@ -5023,25 +5069,25 @@
         <v>36</v>
       </c>
       <c r="E125" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F125" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G125" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H125">
         <v>8.1</v>
       </c>
       <c r="I125" t="str">
-        <f>VLOOKUP(H125,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H125,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>30</v>
@@ -5053,28 +5099,28 @@
         <v>38</v>
       </c>
       <c r="E126" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F126" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G126" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H126">
         <v>5</v>
       </c>
       <c r="I126" t="str">
-        <f>VLOOKUP(H126,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H126,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J126" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>50</v>
@@ -5086,28 +5132,28 @@
         <v>38</v>
       </c>
       <c r="E127" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F127" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G127" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H127">
         <v>5</v>
       </c>
       <c r="I127" t="str">
-        <f>VLOOKUP(H127,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H127,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J127" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>47</v>
@@ -5119,25 +5165,25 @@
         <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F128" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G128" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H128">
         <v>8.1999999999999993</v>
       </c>
       <c r="I128" t="str">
-        <f>VLOOKUP(H128,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H128,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>47</v>
@@ -5149,25 +5195,25 @@
         <v>40</v>
       </c>
       <c r="E129" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F129" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G129" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H129">
         <v>8.1999999999999993</v>
       </c>
       <c r="I129" t="str">
-        <f>VLOOKUP(H129,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H129,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>47</v>
@@ -5179,25 +5225,25 @@
         <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F130" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G130" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H130">
         <v>8.1</v>
       </c>
       <c r="I130" t="str">
-        <f>VLOOKUP(H130,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H130,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
@@ -5209,25 +5255,25 @@
         <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F131" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G131" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H131">
         <v>8.1999999999999993</v>
       </c>
       <c r="I131" t="str">
-        <f>VLOOKUP(H131,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H131,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>6</v>
@@ -5239,25 +5285,25 @@
         <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F132" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G132" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H132">
         <v>8.1</v>
       </c>
       <c r="I132" t="str">
-        <f>VLOOKUP(H132,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H132,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>46</v>
@@ -5269,25 +5315,25 @@
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F133" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G133" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H133">
         <v>3.1</v>
       </c>
       <c r="I133" t="str">
-        <f>VLOOKUP(H133,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H133,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>46</v>
@@ -5299,25 +5345,25 @@
         <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F134" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G134" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H134">
         <v>3.1</v>
       </c>
       <c r="I134" t="str">
-        <f>VLOOKUP(H134,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H134,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>10</v>
@@ -5329,25 +5375,25 @@
         <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F135" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G135" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H135">
         <v>3.2</v>
       </c>
       <c r="I135" t="str">
-        <f>VLOOKUP(H135,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H135,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>46</v>
@@ -5359,25 +5405,25 @@
         <v>13</v>
       </c>
       <c r="E136" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F136" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G136" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H136">
         <v>3.1</v>
       </c>
       <c r="I136" t="str">
-        <f>VLOOKUP(H136,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H136,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>46</v>
@@ -5389,25 +5435,25 @@
         <v>13</v>
       </c>
       <c r="E137" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F137" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G137" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H137">
         <v>3.1</v>
       </c>
       <c r="I137" t="str">
-        <f>VLOOKUP(H137,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H137,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>58</v>
@@ -5419,25 +5465,25 @@
         <v>16</v>
       </c>
       <c r="E138" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F138" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G138" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H138">
         <v>3.1</v>
       </c>
       <c r="I138" t="str">
-        <f>VLOOKUP(H138,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H138,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>8</v>
@@ -5449,25 +5495,25 @@
         <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F139" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G139" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H139">
         <v>3.1</v>
       </c>
       <c r="I139" t="str">
-        <f>VLOOKUP(H139,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H139,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
@@ -5479,25 +5525,25 @@
         <v>23</v>
       </c>
       <c r="E140" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F140" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G140" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H140">
         <v>3.1</v>
       </c>
       <c r="I140" t="str">
-        <f>VLOOKUP(H140,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H140,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>46</v>
@@ -5509,25 +5555,25 @@
         <v>38</v>
       </c>
       <c r="E141" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F141" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G141" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H141">
         <v>3.1</v>
       </c>
       <c r="I141" t="str">
-        <f>VLOOKUP(H141,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H141,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>46</v>
@@ -5539,25 +5585,25 @@
         <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F142" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G142" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H142">
         <v>3.1</v>
       </c>
       <c r="I142" t="str">
-        <f>VLOOKUP(H142,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H142,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>46</v>
@@ -5569,25 +5615,25 @@
         <v>40</v>
       </c>
       <c r="E143" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F143" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H143">
         <v>3.1</v>
       </c>
       <c r="I143" t="str">
-        <f>VLOOKUP(H143,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H143,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>46</v>
@@ -5599,25 +5645,25 @@
         <v>40</v>
       </c>
       <c r="E144" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F144" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G144" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H144">
         <v>3.1</v>
       </c>
       <c r="I144" t="str">
-        <f>VLOOKUP(H144,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H144,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>46</v>
@@ -5629,25 +5675,25 @@
         <v>44</v>
       </c>
       <c r="E145" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F145" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H145">
         <v>3.1</v>
       </c>
       <c r="I145" t="str">
-        <f>VLOOKUP(H145,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H145,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>46</v>
@@ -5659,25 +5705,25 @@
         <v>44</v>
       </c>
       <c r="E146" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F146" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G146" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H146">
         <v>3.1</v>
       </c>
       <c r="I146" t="str">
-        <f>VLOOKUP(H146,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H146,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>46</v>
@@ -5689,25 +5735,25 @@
         <v>46</v>
       </c>
       <c r="E147" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F147" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G147" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H147">
         <v>3.1</v>
       </c>
       <c r="I147" t="str">
-        <f>VLOOKUP(H147,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H147,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>46</v>
@@ -5719,25 +5765,25 @@
         <v>46</v>
       </c>
       <c r="E148" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F148" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G148" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H148">
         <v>3.1</v>
       </c>
       <c r="I148" t="str">
-        <f>VLOOKUP(H148,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H148,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>31</v>
@@ -5749,25 +5795,25 @@
         <v>53</v>
       </c>
       <c r="E149" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F149" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G149" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H149">
         <v>3.1</v>
       </c>
       <c r="I149" t="str">
-        <f>VLOOKUP(H149,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H149,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>29</v>
@@ -5779,25 +5825,25 @@
         <v>53</v>
       </c>
       <c r="E150" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F150" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G150" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H150">
         <v>3.2</v>
       </c>
       <c r="I150" t="str">
-        <f>VLOOKUP(H150,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H150,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>27</v>
@@ -5809,25 +5855,25 @@
         <v>54</v>
       </c>
       <c r="E151" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F151" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G151" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H151">
         <v>3.2</v>
       </c>
       <c r="I151" t="str">
-        <f>VLOOKUP(H151,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H151,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>8</v>
@@ -5839,25 +5885,25 @@
         <v>18</v>
       </c>
       <c r="E152" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F152" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G152" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H152">
         <v>3.1</v>
       </c>
       <c r="I152" t="str">
-        <f>VLOOKUP(H152,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H152,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>27</v>
@@ -5869,25 +5915,25 @@
         <v>54</v>
       </c>
       <c r="E153" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F153" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G153" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H153">
         <v>3.2</v>
       </c>
       <c r="I153" t="str">
-        <f>VLOOKUP(H153,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H153,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>9</v>
@@ -5899,25 +5945,25 @@
         <v>54</v>
       </c>
       <c r="E154" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F154" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G154" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H154">
         <v>3.1</v>
       </c>
       <c r="I154" t="str">
-        <f>VLOOKUP(H154,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H154,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>9</v>
@@ -5929,25 +5975,25 @@
         <v>54</v>
       </c>
       <c r="E155" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F155" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G155" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H155">
         <v>3.1</v>
       </c>
       <c r="I155" t="str">
-        <f>VLOOKUP(H155,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H155,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>29</v>
@@ -5959,25 +6005,25 @@
         <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F156" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G156" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H156">
         <v>3.2</v>
       </c>
       <c r="I156" t="str">
-        <f>VLOOKUP(H156,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H156,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>29</v>
@@ -5989,25 +6035,25 @@
         <v>60</v>
       </c>
       <c r="E157" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F157" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G157" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H157">
         <v>3.2</v>
       </c>
       <c r="I157" t="str">
-        <f>VLOOKUP(H157,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H157,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>32</v>
@@ -6019,28 +6065,28 @@
         <v>68</v>
       </c>
       <c r="E158" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F158" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G158" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H158">
         <v>5</v>
       </c>
       <c r="I158" t="str">
-        <f>VLOOKUP(H158,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H158,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J158" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>33</v>
@@ -6052,25 +6098,25 @@
         <v>70</v>
       </c>
       <c r="E159" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F159" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G159" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H159">
         <v>1.2</v>
       </c>
       <c r="I159" t="str">
-        <f>VLOOKUP(H159,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H159,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>26</v>
@@ -6082,28 +6128,28 @@
         <v>73</v>
       </c>
       <c r="E160" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F160" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G160" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H160">
         <v>5</v>
       </c>
       <c r="I160" t="str">
-        <f>VLOOKUP(H160,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H160,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J160" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>25</v>
@@ -6115,25 +6161,25 @@
         <v>79</v>
       </c>
       <c r="E161" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F161" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G161" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H161">
         <v>1.2</v>
       </c>
       <c r="I161" t="str">
-        <f>VLOOKUP(H161,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &lt;5% of the time in training samples</v>
+        <f>VLOOKUP(H161,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>A.2</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>26</v>
@@ -6145,28 +6191,28 @@
         <v>79</v>
       </c>
       <c r="E162" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F162" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G162" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H162">
         <v>4</v>
       </c>
       <c r="I162" t="str">
-        <f>VLOOKUP(H162,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H162,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J162" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>14</v>
@@ -6178,25 +6224,25 @@
         <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F163" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G163" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H163">
         <v>4</v>
       </c>
       <c r="I163" t="str">
-        <f>VLOOKUP(H163,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H163,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>25</v>
@@ -6208,25 +6254,25 @@
         <v>79</v>
       </c>
       <c r="E164" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F164" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G164" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H164">
         <v>4</v>
       </c>
       <c r="I164" t="str">
-        <f>VLOOKUP(H164,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H164,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>12</v>
@@ -6238,25 +6284,25 @@
         <v>79</v>
       </c>
       <c r="E165" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F165" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G165" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H165">
         <v>1.4</v>
       </c>
       <c r="I165" t="str">
-        <f>VLOOKUP(H165,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H165,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>6</v>
@@ -6268,25 +6314,25 @@
         <v>84</v>
       </c>
       <c r="E166" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F166" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G166" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H166">
         <v>6</v>
       </c>
       <c r="I166" t="str">
-        <f>VLOOKUP(H166,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Unclear</v>
+        <f>VLOOKUP(H166,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>G.2</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>30</v>
@@ -6298,28 +6344,28 @@
         <v>85</v>
       </c>
       <c r="E167" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F167" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G167" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H167">
         <v>5</v>
       </c>
       <c r="I167" t="str">
-        <f>VLOOKUP(H167,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H167,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J167" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>12</v>
@@ -6331,25 +6377,25 @@
         <v>79</v>
       </c>
       <c r="E168" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F168" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G168" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H168">
         <v>1.4</v>
       </c>
       <c r="I168" t="str">
-        <f>VLOOKUP(H168,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H168,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>6</v>
@@ -6361,25 +6407,25 @@
         <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F169" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G169" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H169">
         <v>8.1</v>
       </c>
       <c r="I169" t="str">
-        <f>VLOOKUP(H169,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H169,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>14</v>
@@ -6391,28 +6437,28 @@
         <v>53</v>
       </c>
       <c r="E170" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F170" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G170" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H170">
         <v>4</v>
       </c>
       <c r="I170" t="str">
-        <f>VLOOKUP(H170,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H170,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J170" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>6</v>
@@ -6424,25 +6470,25 @@
         <v>53</v>
       </c>
       <c r="E171" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F171" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G171" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H171">
         <v>8.1</v>
       </c>
       <c r="I171" t="str">
-        <f>VLOOKUP(H171,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H171,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>32</v>
@@ -6454,28 +6500,28 @@
         <v>59</v>
       </c>
       <c r="E172" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F172" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G172" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H172">
         <v>4</v>
       </c>
       <c r="I172" t="str">
-        <f>VLOOKUP(H172,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H172,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J172" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>6</v>
@@ -6487,25 +6533,25 @@
         <v>60</v>
       </c>
       <c r="E173" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F173" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G173" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H173">
         <v>8.1</v>
       </c>
       <c r="I173" t="str">
-        <f>VLOOKUP(H173,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H173,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>26</v>
@@ -6517,28 +6563,28 @@
         <v>61</v>
       </c>
       <c r="E174" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F174" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G174" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H174">
         <v>4</v>
       </c>
       <c r="I174" t="str">
-        <f>VLOOKUP(H174,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H174,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J174" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>14</v>
@@ -6550,25 +6596,25 @@
         <v>70</v>
       </c>
       <c r="E175" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F175" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G175" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H175">
         <v>8.1</v>
       </c>
       <c r="I175" t="str">
-        <f>VLOOKUP(H175,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H175,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>6</v>
@@ -6580,25 +6626,25 @@
         <v>70</v>
       </c>
       <c r="E176" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F176" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G176" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H176">
         <v>8.1</v>
       </c>
       <c r="I176" t="str">
-        <f>VLOOKUP(H176,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H176,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>30</v>
@@ -6610,28 +6656,28 @@
         <v>82</v>
       </c>
       <c r="E177" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F177" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G177" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H177">
         <v>5</v>
       </c>
       <c r="I177" t="str">
-        <f>VLOOKUP(H177,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H177,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J177" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>6</v>
@@ -6643,25 +6689,25 @@
         <v>84</v>
       </c>
       <c r="E178" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F178" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G178" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H178">
         <v>8.1</v>
       </c>
       <c r="I178" t="str">
-        <f>VLOOKUP(H178,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H178,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>6</v>
@@ -6673,25 +6719,25 @@
         <v>87</v>
       </c>
       <c r="E179" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F179" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G179" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H179">
         <v>8.1</v>
       </c>
       <c r="I179" t="str">
-        <f>VLOOKUP(H179,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H179,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>30</v>
@@ -6703,28 +6749,28 @@
         <v>38</v>
       </c>
       <c r="E180" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F180" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G180" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H180">
         <v>5</v>
       </c>
       <c r="I180" t="str">
-        <f>VLOOKUP(H180,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H180,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J180" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>50</v>
@@ -6736,28 +6782,28 @@
         <v>38</v>
       </c>
       <c r="E181" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F181" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G181" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H181">
         <v>4</v>
       </c>
       <c r="I181" t="str">
-        <f>VLOOKUP(H181,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H181,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J181" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>47</v>
@@ -6769,25 +6815,25 @@
         <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F182" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G182" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H182">
         <v>8.1999999999999993</v>
       </c>
       <c r="I182" t="str">
-        <f>VLOOKUP(H182,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H182,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>6</v>
@@ -6799,25 +6845,25 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F183" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G183" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H183">
         <v>8.1</v>
       </c>
       <c r="I183" t="str">
-        <f>VLOOKUP(H183,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H183,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>6</v>
@@ -6829,25 +6875,25 @@
         <v>53</v>
       </c>
       <c r="E184" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F184" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G184" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H184">
         <v>8.1</v>
       </c>
       <c r="I184" t="str">
-        <f>VLOOKUP(H184,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H184,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>32</v>
@@ -6859,28 +6905,28 @@
         <v>59</v>
       </c>
       <c r="E185" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F185" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G185" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H185">
         <v>4</v>
       </c>
       <c r="I185" t="str">
-        <f>VLOOKUP(H185,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H185,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J185" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>6</v>
@@ -6892,25 +6938,25 @@
         <v>60</v>
       </c>
       <c r="E186" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F186" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G186" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H186">
         <v>8.1</v>
       </c>
       <c r="I186" t="str">
-        <f>VLOOKUP(H186,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H186,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>6</v>
@@ -6922,28 +6968,28 @@
         <v>70</v>
       </c>
       <c r="E187" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F187" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G187" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H187">
         <v>4</v>
       </c>
       <c r="I187" t="str">
-        <f>VLOOKUP(H187,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H187,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
       <c r="J187" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>6</v>
@@ -6955,25 +7001,25 @@
         <v>84</v>
       </c>
       <c r="E188" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F188" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G188" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H188">
         <v>8.1</v>
       </c>
       <c r="I188" t="str">
-        <f>VLOOKUP(H188,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H188,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>6</v>
@@ -6985,25 +7031,25 @@
         <v>87</v>
       </c>
       <c r="E189" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F189" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G189" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H189">
         <v>8.1</v>
       </c>
       <c r="I189" t="str">
-        <f>VLOOKUP(H189,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H189,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>9</v>
@@ -7015,25 +7061,25 @@
         <v>22</v>
       </c>
       <c r="E190" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F190" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G190" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H190">
         <v>3.1</v>
       </c>
       <c r="I190" t="str">
-        <f>VLOOKUP(H190,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H190,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>9</v>
@@ -7045,25 +7091,25 @@
         <v>23</v>
       </c>
       <c r="E191" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F191" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G191" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H191">
         <v>3.1</v>
       </c>
       <c r="I191" t="str">
-        <f>VLOOKUP(H191,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H191,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>31</v>
@@ -7075,25 +7121,25 @@
         <v>68</v>
       </c>
       <c r="E192" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F192" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G192" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H192">
         <v>3.1</v>
       </c>
       <c r="I192" t="str">
-        <f>VLOOKUP(H192,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H192,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>31</v>
@@ -7105,25 +7151,25 @@
         <v>68</v>
       </c>
       <c r="E193" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F193" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G193" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H193">
         <v>3.1</v>
       </c>
       <c r="I193" t="str">
-        <f>VLOOKUP(H193,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H193,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>62</v>
@@ -7135,25 +7181,25 @@
         <v>68</v>
       </c>
       <c r="E194" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F194" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G194" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H194">
         <v>3.2</v>
       </c>
       <c r="I194" t="str">
-        <f>VLOOKUP(H194,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H194,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>31</v>
@@ -7165,25 +7211,25 @@
         <v>70</v>
       </c>
       <c r="E195" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F195" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G195" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H195">
         <v>3.1</v>
       </c>
       <c r="I195" t="str">
-        <f>VLOOKUP(H195,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H195,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>22</v>
@@ -7195,25 +7241,25 @@
         <v>73</v>
       </c>
       <c r="E196" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F196" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G196" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H196">
         <v>3.1</v>
       </c>
       <c r="I196" t="str">
-        <f>VLOOKUP(H196,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H196,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>22</v>
@@ -7225,25 +7271,25 @@
         <v>48</v>
       </c>
       <c r="E197" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F197" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G197" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H197">
         <v>3.1</v>
       </c>
       <c r="I197" t="str">
-        <f>VLOOKUP(H197,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H197,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>46</v>
@@ -7255,25 +7301,25 @@
         <v>74</v>
       </c>
       <c r="E198" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F198" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G198" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H198">
         <v>3.1</v>
       </c>
       <c r="I198" t="str">
-        <f>VLOOKUP(H198,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H198,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>46</v>
@@ -7285,25 +7331,25 @@
         <v>74</v>
       </c>
       <c r="E199" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F199" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G199" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H199">
         <v>3.1</v>
       </c>
       <c r="I199" t="str">
-        <f>VLOOKUP(H199,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H199,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>48</v>
@@ -7315,25 +7361,25 @@
         <v>79</v>
       </c>
       <c r="E200" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F200" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G200" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H200">
         <v>3.2</v>
       </c>
       <c r="I200" t="str">
-        <f>VLOOKUP(H200,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H200,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>27</v>
@@ -7345,25 +7391,25 @@
         <v>79</v>
       </c>
       <c r="E201" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F201" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G201" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H201">
         <v>3.2</v>
       </c>
       <c r="I201" t="str">
-        <f>VLOOKUP(H201,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H201,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>27</v>
@@ -7375,25 +7421,25 @@
         <v>79</v>
       </c>
       <c r="E202" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F202" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G202" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H202">
         <v>3.2</v>
       </c>
       <c r="I202" t="str">
-        <f>VLOOKUP(H202,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H202,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>9</v>
@@ -7405,25 +7451,25 @@
         <v>79</v>
       </c>
       <c r="E203" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F203" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G203" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H203">
         <v>3.1</v>
       </c>
       <c r="I203" t="str">
-        <f>VLOOKUP(H203,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H203,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="360" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B204" t="s">
         <v>16</v>
@@ -7435,28 +7481,28 @@
         <v>46</v>
       </c>
       <c r="E204" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F204" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G204" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H204">
         <v>7</v>
       </c>
       <c r="I204" t="str">
-        <f>VLOOKUP(H204,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>RAG Added Misinformation</v>
+        <f>VLOOKUP(H204,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>G.1</v>
       </c>
       <c r="J204" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>16</v>
@@ -7468,28 +7514,28 @@
         <v>46</v>
       </c>
       <c r="E205" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F205" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G205" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H205">
         <v>2.2000000000000002</v>
       </c>
       <c r="I205" t="str">
-        <f>VLOOKUP(H205,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H205,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J205" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B206" t="s">
         <v>16</v>
@@ -7501,25 +7547,25 @@
         <v>48</v>
       </c>
       <c r="E206" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F206" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G206" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H206">
         <v>2.2000000000000002</v>
       </c>
       <c r="I206" t="str">
-        <f>VLOOKUP(H206,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H206,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>16</v>
@@ -7531,28 +7577,28 @@
         <v>60</v>
       </c>
       <c r="E207" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F207" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G207" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H207">
         <v>2.2000000000000002</v>
       </c>
       <c r="I207" t="str">
-        <f>VLOOKUP(H207,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H207,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J207" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B208" t="s">
         <v>16</v>
@@ -7564,25 +7610,25 @@
         <v>60</v>
       </c>
       <c r="E208" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F208" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G208" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H208">
         <v>2.2000000000000002</v>
       </c>
       <c r="I208" t="str">
-        <f>VLOOKUP(H208,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H208,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="270" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B209" t="s">
         <v>16</v>
@@ -7594,28 +7640,28 @@
         <v>69</v>
       </c>
       <c r="E209" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F209" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G209" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H209">
         <v>7</v>
       </c>
       <c r="I209" t="str">
-        <f>VLOOKUP(H209,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>RAG Added Misinformation</v>
+        <f>VLOOKUP(H209,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>G.1</v>
       </c>
       <c r="J209" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>16</v>
@@ -7627,28 +7673,28 @@
         <v>68</v>
       </c>
       <c r="E210" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F210" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G210" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H210">
         <v>2.2000000000000002</v>
       </c>
       <c r="I210" t="str">
-        <f>VLOOKUP(H210,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H210,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J210" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>16</v>
@@ -7660,28 +7706,28 @@
         <v>73</v>
       </c>
       <c r="E211" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F211" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G211" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H211">
         <v>2.2000000000000002</v>
       </c>
       <c r="I211" t="str">
-        <f>VLOOKUP(H211,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H211,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J211" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>16</v>
@@ -7693,28 +7739,28 @@
         <v>74</v>
       </c>
       <c r="E212" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F212" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G212" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H212">
         <v>2.2000000000000002</v>
       </c>
       <c r="I212" t="str">
-        <f>VLOOKUP(H212,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H212,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J212" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>16</v>
@@ -7726,28 +7772,28 @@
         <v>95</v>
       </c>
       <c r="E213" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F213" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G213" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H213">
         <v>2.2000000000000002</v>
       </c>
       <c r="I213" t="str">
-        <f>VLOOKUP(H213,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H213,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J213" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>16</v>
@@ -7759,28 +7805,28 @@
         <v>100</v>
       </c>
       <c r="E214" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F214" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G214" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H214">
         <v>2.2000000000000002</v>
       </c>
       <c r="I214" t="str">
-        <f>VLOOKUP(H214,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H214,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
       <c r="J214" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B215" t="s">
         <v>16</v>
@@ -7792,25 +7838,25 @@
         <v>73</v>
       </c>
       <c r="E215" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F215" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G215" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H215">
         <v>2.2000000000000002</v>
       </c>
       <c r="I215" t="str">
-        <f>VLOOKUP(H215,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H215,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B216" t="s">
         <v>16</v>
@@ -7822,25 +7868,25 @@
         <v>74</v>
       </c>
       <c r="E216" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F216" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G216" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H216">
         <v>2.2000000000000002</v>
       </c>
       <c r="I216" t="str">
-        <f>VLOOKUP(H216,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H216,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B217" t="s">
         <v>16</v>
@@ -7852,25 +7898,25 @@
         <v>95</v>
       </c>
       <c r="E217" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F217" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G217" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H217">
         <v>2.2000000000000002</v>
       </c>
       <c r="I217" t="str">
-        <f>VLOOKUP(H217,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In Allocation, chose economic when the humans chose a more specific label</v>
+        <f>VLOOKUP(H217,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.2</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>9</v>
@@ -7882,25 +7928,25 @@
         <v>79</v>
       </c>
       <c r="E218" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F218" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G218" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H218">
         <v>3.1</v>
       </c>
       <c r="I218" t="str">
-        <f>VLOOKUP(H218,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H218,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>8</v>
@@ -7912,25 +7958,25 @@
         <v>84</v>
       </c>
       <c r="E219" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F219" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G219" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H219">
         <v>3.1</v>
       </c>
       <c r="I219" t="str">
-        <f>VLOOKUP(H219,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H219,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>8</v>
@@ -7942,25 +7988,25 @@
         <v>84</v>
       </c>
       <c r="E220" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F220" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G220" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H220">
         <v>3.1</v>
       </c>
       <c r="I220" t="str">
-        <f>VLOOKUP(H220,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H220,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>46</v>
@@ -7972,25 +8018,25 @@
         <v>89</v>
       </c>
       <c r="E221" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F221" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G221" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H221">
         <v>3.1</v>
       </c>
       <c r="I221" t="str">
-        <f>VLOOKUP(H221,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H221,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>46</v>
@@ -8002,25 +8048,25 @@
         <v>89</v>
       </c>
       <c r="E222" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F222" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G222" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H222">
         <v>3.1</v>
       </c>
       <c r="I222" t="str">
-        <f>VLOOKUP(H222,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H222,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>48</v>
@@ -8032,25 +8078,25 @@
         <v>95</v>
       </c>
       <c r="E223" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F223" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G223" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H223">
         <v>3.2</v>
       </c>
       <c r="I223" t="str">
-        <f>VLOOKUP(H223,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H223,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>48</v>
@@ -8062,25 +8108,25 @@
         <v>95</v>
       </c>
       <c r="E224" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F224" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G224" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H224">
         <v>3.2</v>
       </c>
       <c r="I224" t="str">
-        <f>VLOOKUP(H224,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the AI model does not want to report an item the authors of the study did report for completeness</v>
+        <f>VLOOKUP(H224,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.2</v>
       </c>
     </row>
     <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>57</v>
@@ -8092,25 +8138,25 @@
         <v>98</v>
       </c>
       <c r="E225" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F225" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G225" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H225">
         <v>3.1</v>
       </c>
       <c r="I225" t="str">
-        <f>VLOOKUP(H225,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H225,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>22</v>
@@ -8122,25 +8168,25 @@
         <v>98</v>
       </c>
       <c r="E226" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F226" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H226">
         <v>3.1</v>
       </c>
       <c r="I226" t="str">
-        <f>VLOOKUP(H226,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H226,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>22</v>
@@ -8152,25 +8198,25 @@
         <v>98</v>
       </c>
       <c r="E227" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F227" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G227" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H227">
         <v>3.1</v>
       </c>
       <c r="I227" t="str">
-        <f>VLOOKUP(H227,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H227,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="228" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>58</v>
@@ -8182,25 +8228,25 @@
         <v>101</v>
       </c>
       <c r="E228" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F228" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G228" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H228">
         <v>3.1</v>
       </c>
       <c r="I228" t="str">
-        <f>VLOOKUP(H228,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H228,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>46</v>
@@ -8212,25 +8258,25 @@
         <v>101</v>
       </c>
       <c r="E229" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F229" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G229" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H229">
         <v>3.1</v>
       </c>
       <c r="I229" t="str">
-        <f>VLOOKUP(H229,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H229,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>46</v>
@@ -8242,25 +8288,25 @@
         <v>101</v>
       </c>
       <c r="E230" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F230" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G230" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H230">
         <v>3.1</v>
       </c>
       <c r="I230" t="str">
-        <f>VLOOKUP(H230,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H230,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>8</v>
@@ -8272,25 +8318,25 @@
         <v>101</v>
       </c>
       <c r="E231" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F231" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G231" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H231">
         <v>3.1</v>
       </c>
       <c r="I231" t="str">
-        <f>VLOOKUP(H231,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In the system boundary, the authors of the study did not report an item the AI model wants to consider for completeness</v>
+        <f>VLOOKUP(H231,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>F.1</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>13</v>
@@ -8302,25 +8348,25 @@
         <v>40</v>
       </c>
       <c r="E232" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F232" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G232" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H232">
         <v>1.4</v>
       </c>
       <c r="I232" t="str">
-        <f>VLOOKUP(H232,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H232,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>13</v>
@@ -8332,25 +8378,25 @@
         <v>48</v>
       </c>
       <c r="E233" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F233" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G233" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H233">
         <v>1.4</v>
       </c>
       <c r="I233" t="str">
-        <f>VLOOKUP(H233,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H233,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>45</v>
@@ -8362,25 +8408,25 @@
         <v>89</v>
       </c>
       <c r="E234" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F234" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G234" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H234">
         <v>1.4</v>
       </c>
       <c r="I234" t="str">
-        <f>VLOOKUP(H234,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H234,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>45</v>
@@ -8392,25 +8438,25 @@
         <v>89</v>
       </c>
       <c r="E235" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F235" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G235" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H235">
         <v>1.4</v>
       </c>
       <c r="I235" t="str">
-        <f>VLOOKUP(H235,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H235,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>13</v>
@@ -8422,25 +8468,25 @@
         <v>38</v>
       </c>
       <c r="E236" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F236" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G236" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H236">
         <v>1.4</v>
       </c>
       <c r="I236" t="str">
-        <f>VLOOKUP(H236,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H236,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>13</v>
@@ -8452,25 +8498,25 @@
         <v>15</v>
       </c>
       <c r="E237" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F237" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G237" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H237">
         <v>1.4</v>
       </c>
       <c r="I237" t="str">
-        <f>VLOOKUP(H237,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H237,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>13</v>
@@ -8482,25 +8528,25 @@
         <v>20</v>
       </c>
       <c r="E238" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F238" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G238" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H238">
         <v>1.4</v>
       </c>
       <c r="I238" t="str">
-        <f>VLOOKUP(H238,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H238,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="239" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>13</v>
@@ -8512,25 +8558,25 @@
         <v>38</v>
       </c>
       <c r="E239" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F239" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G239" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H239">
         <v>1.4</v>
       </c>
       <c r="I239" t="str">
-        <f>VLOOKUP(H239,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H239,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>11</v>
@@ -8542,25 +8588,25 @@
         <v>37</v>
       </c>
       <c r="E240" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F240" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G240" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H240">
         <v>1.4</v>
       </c>
       <c r="I240" t="str">
-        <f>VLOOKUP(H240,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H240,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>55</v>
@@ -8572,25 +8618,25 @@
         <v>68</v>
       </c>
       <c r="E241" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F241" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G241" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H241">
         <v>1.4</v>
       </c>
       <c r="I241" t="str">
-        <f>VLOOKUP(H241,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H241,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>55</v>
@@ -8602,25 +8648,25 @@
         <v>68</v>
       </c>
       <c r="E242" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F242" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G242" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H242">
         <v>1.4</v>
       </c>
       <c r="I242" t="str">
-        <f>VLOOKUP(H242,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H242,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>11</v>
@@ -8632,25 +8678,25 @@
         <v>85</v>
       </c>
       <c r="E243" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F243" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G243" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H243">
         <v>1.4</v>
       </c>
       <c r="I243" t="str">
-        <f>VLOOKUP(H243,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H243,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>5</v>
@@ -8662,25 +8708,25 @@
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F244" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G244" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H244">
         <v>1.4</v>
       </c>
       <c r="I244" t="str">
-        <f>VLOOKUP(H244,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H244,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>5</v>
@@ -8692,25 +8738,25 @@
         <v>60</v>
       </c>
       <c r="E245" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F245" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G245" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H245">
         <v>1.4</v>
       </c>
       <c r="I245" t="str">
-        <f>VLOOKUP(H245,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H245,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>5</v>
@@ -8722,25 +8768,25 @@
         <v>60</v>
       </c>
       <c r="E246" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F246" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G246" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H246">
         <v>1.4</v>
       </c>
       <c r="I246" t="str">
-        <f>VLOOKUP(H246,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H246,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>11</v>
@@ -8752,25 +8798,25 @@
         <v>23</v>
       </c>
       <c r="E247" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F247" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G247" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H247">
         <v>1.4</v>
       </c>
       <c r="I247" t="str">
-        <f>VLOOKUP(H247,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H247,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>11</v>
@@ -8782,25 +8828,25 @@
         <v>30</v>
       </c>
       <c r="E248" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F248" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G248" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H248">
         <v>1.4</v>
       </c>
       <c r="I248" t="str">
-        <f>VLOOKUP(H248,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H248,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>11</v>
@@ -8812,25 +8858,25 @@
         <v>95</v>
       </c>
       <c r="E249" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F249" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G249" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H249">
         <v>1.4</v>
       </c>
       <c r="I249" t="str">
-        <f>VLOOKUP(H249,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H249,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>11</v>
@@ -8842,25 +8888,25 @@
         <v>23</v>
       </c>
       <c r="E250" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F250" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G250" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H250">
         <v>1.4</v>
       </c>
       <c r="I250" t="str">
-        <f>VLOOKUP(H250,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H250,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>11</v>
@@ -8872,25 +8918,25 @@
         <v>30</v>
       </c>
       <c r="E251" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F251" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G251" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H251">
         <v>1.4</v>
       </c>
       <c r="I251" t="str">
-        <f>VLOOKUP(H251,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H251,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>11</v>
@@ -8902,25 +8948,25 @@
         <v>95</v>
       </c>
       <c r="E252" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F252" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G252" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H252">
         <v>1.4</v>
       </c>
       <c r="I252" t="str">
-        <f>VLOOKUP(H252,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H252,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>11</v>
@@ -8932,25 +8978,25 @@
         <v>103</v>
       </c>
       <c r="E253" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F253" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G253" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H253">
         <v>1.4</v>
       </c>
       <c r="I253" t="str">
-        <f>VLOOKUP(H253,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H253,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>61</v>
@@ -8962,25 +9008,25 @@
         <v>48</v>
       </c>
       <c r="E254" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F254" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G254" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H254">
         <v>1.4</v>
       </c>
       <c r="I254" t="str">
-        <f>VLOOKUP(H254,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H254,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>34</v>
@@ -8992,25 +9038,25 @@
         <v>38</v>
       </c>
       <c r="E255" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F255" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G255" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H255">
         <v>1.4</v>
       </c>
       <c r="I255" t="str">
-        <f>VLOOKUP(H255,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H255,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>34</v>
@@ -9022,25 +9068,25 @@
         <v>38</v>
       </c>
       <c r="E256" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F256" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G256" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H256">
         <v>1.4</v>
       </c>
       <c r="I256" t="str">
-        <f>VLOOKUP(H256,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H256,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>20</v>
@@ -9052,25 +9098,25 @@
         <v>48</v>
       </c>
       <c r="E257" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F257" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G257" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H257">
         <v>1.4</v>
       </c>
       <c r="I257" t="str">
-        <f>VLOOKUP(H257,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H257,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>20</v>
@@ -9082,25 +9128,25 @@
         <v>31</v>
       </c>
       <c r="E258" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F258" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G258" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H258">
         <v>1.4</v>
       </c>
       <c r="I258" t="str">
-        <f>VLOOKUP(H258,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H258,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>34</v>
@@ -9112,25 +9158,25 @@
         <v>73</v>
       </c>
       <c r="E259" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F259" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G259" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H259">
         <v>1.4</v>
       </c>
       <c r="I259" t="str">
-        <f>VLOOKUP(H259,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H259,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>34</v>
@@ -9142,25 +9188,25 @@
         <v>101</v>
       </c>
       <c r="E260" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F260" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G260" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H260">
         <v>1.4</v>
       </c>
       <c r="I260" t="str">
-        <f>VLOOKUP(H260,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H260,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>34</v>
@@ -9172,25 +9218,25 @@
         <v>73</v>
       </c>
       <c r="E261" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F261" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G261" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H261">
         <v>1.4</v>
       </c>
       <c r="I261" t="str">
-        <f>VLOOKUP(H261,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H261,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>34</v>
@@ -9202,25 +9248,25 @@
         <v>101</v>
       </c>
       <c r="E262" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F262" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G262" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H262">
         <v>1.4</v>
       </c>
       <c r="I262" t="str">
-        <f>VLOOKUP(H262,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H262,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>6</v>
@@ -9232,25 +9278,25 @@
         <v>84</v>
       </c>
       <c r="E263" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F263" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G263" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H263">
         <v>8.1</v>
       </c>
       <c r="I263" t="str">
-        <f>VLOOKUP(H263,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, labeler only includes relative while AI model adds other categories</v>
+        <f>VLOOKUP(H263,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>D.1</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>30</v>
@@ -9262,28 +9308,28 @@
         <v>85</v>
       </c>
       <c r="E264" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F264" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G264" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H264">
         <v>5</v>
       </c>
       <c r="I264" t="str">
-        <f>VLOOKUP(H264,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model has justifiable response</v>
+        <f>VLOOKUP(H264,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.4</v>
       </c>
       <c r="J264" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>47</v>
@@ -9295,25 +9341,25 @@
         <v>92</v>
       </c>
       <c r="E265" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F265" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G265" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H265">
         <v>8.1999999999999993</v>
       </c>
       <c r="I265" t="str">
-        <f>VLOOKUP(H265,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H265,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>47</v>
@@ -9325,25 +9371,25 @@
         <v>92</v>
       </c>
       <c r="E266" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F266" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G266" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H266">
         <v>8.1999999999999993</v>
       </c>
       <c r="I266" t="str">
-        <f>VLOOKUP(H266,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>In FU, AI model confuses cold carcass weight, cold dressed carcass weight, and liveweight</v>
+        <f>VLOOKUP(H266,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>C.3</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>14</v>
@@ -9355,25 +9401,25 @@
         <v>95</v>
       </c>
       <c r="E267" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F267" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G267" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H267">
         <v>4</v>
       </c>
       <c r="I267" t="str">
-        <f>VLOOKUP(H267,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H267,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>26</v>
@@ -9385,25 +9431,25 @@
         <v>95</v>
       </c>
       <c r="E268" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F268" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G268" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H268">
         <v>4</v>
       </c>
       <c r="I268" t="str">
-        <f>VLOOKUP(H268,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>AI model likely incorrect</v>
+        <f>VLOOKUP(H268,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>E.1</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B269" t="s">
         <v>12</v>
@@ -9415,25 +9461,25 @@
         <v>38</v>
       </c>
       <c r="E269" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F269" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G269" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H269">
         <v>1.4</v>
       </c>
       <c r="I269" t="str">
-        <f>VLOOKUP(H269,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H269,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>24</v>
@@ -9445,25 +9491,25 @@
         <v>53</v>
       </c>
       <c r="E270" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F270" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G270" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H270">
         <v>1.4</v>
       </c>
       <c r="I270" t="str">
-        <f>VLOOKUP(H270,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H270,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>24</v>
@@ -9475,25 +9521,25 @@
         <v>73</v>
       </c>
       <c r="E271" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F271" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G271" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H271">
         <v>1.4</v>
       </c>
       <c r="I271" t="str">
-        <f>VLOOKUP(H271,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H271,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>24</v>
@@ -9505,25 +9551,25 @@
         <v>78</v>
       </c>
       <c r="E272" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F272" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G272" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H272">
         <v>1.4</v>
       </c>
       <c r="I272" t="str">
-        <f>VLOOKUP(H272,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H272,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>24</v>
@@ -9535,25 +9581,25 @@
         <v>53</v>
       </c>
       <c r="E273" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F273" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G273" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H273">
         <v>1.4</v>
       </c>
       <c r="I273" t="str">
-        <f>VLOOKUP(H273,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H273,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>24</v>
@@ -9565,25 +9611,25 @@
         <v>38</v>
       </c>
       <c r="E274" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F274" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G274" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H274">
         <v>1.4</v>
       </c>
       <c r="I274" t="str">
-        <f>VLOOKUP(H274,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H274,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>24</v>
@@ -9595,25 +9641,25 @@
         <v>38</v>
       </c>
       <c r="E275" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F275" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G275" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H275">
         <v>1.4</v>
       </c>
       <c r="I275" t="str">
-        <f>VLOOKUP(H275,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H275,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>54</v>
@@ -9625,25 +9671,25 @@
         <v>58</v>
       </c>
       <c r="E276" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F276" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G276" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H276">
         <v>1.4</v>
       </c>
       <c r="I276" t="str">
-        <f>VLOOKUP(H276,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H276,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>54</v>
@@ -9655,20 +9701,20 @@
         <v>58</v>
       </c>
       <c r="E277" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F277" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G277" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H277">
         <v>1.4</v>
       </c>
       <c r="I277" t="str">
-        <f>VLOOKUP(H277,'Encoding Errors'!$A$2:$B$16,2,FALSE)</f>
-        <v>Label occurs &gt;90% of the time in training samples</v>
+        <f>VLOOKUP(H277,'Encoding Errors'!$A$2:$C$16,2,FALSE)</f>
+        <v>B.1</v>
       </c>
     </row>
   </sheetData>
@@ -9683,150 +9729,195 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474CB28B-CC9F-4671-8502-6BD53C4F1E92}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="B1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" t="s">
+        <v>274</v>
+      </c>
+      <c r="P1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1.2</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.3</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1.4</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
-      </c>
-      <c r="O5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="C5" t="s">
+        <v>238</v>
+      </c>
+      <c r="P5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2.1</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="C6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2.2000000000000002</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="C7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8.1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>3.1</v>
       </c>
-      <c r="B8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>3.2</v>
       </c>
-      <c r="B9" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>8.1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="B15" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>232</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{474CB28B-CC9F-4671-8502-6BD53C4F1E92}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C15">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>